--- a/database/event/2150/event_2150_evp_summary.xlsx
+++ b/database/event/2150/event_2150_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>1.0589</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0203</v>
+        <v>2.9502</v>
       </c>
       <c r="E2" t="n">
         <v>8.519399999999999</v>
@@ -548,7 +548,7 @@
         <v>1.049</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9882</v>
+        <v>2.9185</v>
       </c>
       <c r="E3" t="n">
         <v>8.4399</v>
@@ -594,7 +594,7 @@
         <v>0.868</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4</v>
+        <v>2.3385</v>
       </c>
       <c r="E4" t="n">
         <v>6.984</v>
@@ -640,7 +640,7 @@
         <v>0.7198</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9181</v>
+        <v>1.8633</v>
       </c>
       <c r="E5" t="n">
         <v>5.7911</v>
@@ -686,7 +686,7 @@
         <v>0.7108</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8889</v>
+        <v>1.8344</v>
       </c>
       <c r="E6" t="n">
         <v>5.7187</v>
@@ -732,7 +732,7 @@
         <v>0.5666</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4202</v>
+        <v>1.3722</v>
       </c>
       <c r="E7" t="n">
         <v>4.5586</v>
@@ -778,7 +778,7 @@
         <v>0.5646</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4138</v>
+        <v>1.3659</v>
       </c>
       <c r="E8" t="n">
         <v>4.5427</v>
@@ -824,7 +824,7 @@
         <v>0.5368000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3233</v>
+        <v>1.2766</v>
       </c>
       <c r="E9" t="n">
         <v>4.3186</v>
@@ -870,7 +870,7 @@
         <v>0.5105</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2379</v>
+        <v>1.1924</v>
       </c>
       <c r="E10" t="n">
         <v>4.1073</v>
@@ -916,7 +916,7 @@
         <v>0.4726</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1147</v>
+        <v>1.0709</v>
       </c>
       <c r="E11" t="n">
         <v>3.8023</v>
@@ -962,7 +962,7 @@
         <v>0.4668</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0958</v>
+        <v>1.0523</v>
       </c>
       <c r="E12" t="n">
         <v>3.7555</v>
@@ -1008,7 +1008,7 @@
         <v>0.4551</v>
       </c>
       <c r="D13" t="n">
-        <v>1.058</v>
+        <v>1.015</v>
       </c>
       <c r="E13" t="n">
         <v>3.662</v>
@@ -1054,7 +1054,7 @@
         <v>0.2873</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5123</v>
+        <v>0.4769</v>
       </c>
       <c r="E14" t="n">
         <v>2.3112</v>
@@ -1100,7 +1100,7 @@
         <v>0.2681</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4501</v>
+        <v>0.4156</v>
       </c>
       <c r="E15" t="n">
         <v>2.1573</v>
@@ -1146,7 +1146,7 @@
         <v>0.2503</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3921</v>
+        <v>0.3583</v>
       </c>
       <c r="E16" t="n">
         <v>2.0137</v>
@@ -1192,7 +1192,7 @@
         <v>0.2333</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3369</v>
+        <v>0.3039</v>
       </c>
       <c r="E17" t="n">
         <v>1.877</v>
@@ -1238,7 +1238,7 @@
         <v>0.2283</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3208</v>
+        <v>0.288</v>
       </c>
       <c r="E18" t="n">
         <v>1.8371</v>
@@ -1284,7 +1284,7 @@
         <v>0.2186</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2892</v>
+        <v>0.2568</v>
       </c>
       <c r="E19" t="n">
         <v>1.7589</v>
@@ -1330,7 +1330,7 @@
         <v>0.2037</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2406</v>
+        <v>0.2089</v>
       </c>
       <c r="E20" t="n">
         <v>1.6387</v>
@@ -1376,7 +1376,7 @@
         <v>0.179</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1604</v>
+        <v>0.1298</v>
       </c>
       <c r="E21" t="n">
         <v>1.4401</v>
@@ -1422,7 +1422,7 @@
         <v>0.1555</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.0545</v>
       </c>
       <c r="E22" t="n">
         <v>1.251</v>
@@ -1468,7 +1468,7 @@
         <v>0.1454</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0513</v>
+        <v>0.0222</v>
       </c>
       <c r="E23" t="n">
         <v>1.1699</v>
@@ -1514,7 +1514,7 @@
         <v>0.1334</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0123</v>
+        <v>-0.0162</v>
       </c>
       <c r="E24" t="n">
         <v>1.0735</v>
@@ -1560,7 +1560,7 @@
         <v>0.114</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0507</v>
+        <v>-0.0784</v>
       </c>
       <c r="E25" t="n">
         <v>0.9175</v>
@@ -1606,7 +1606,7 @@
         <v>0.1097</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0649</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="E26" t="n">
         <v>0.8825</v>
@@ -1652,7 +1652,7 @@
         <v>0.1043</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0825</v>
+        <v>-0.1097</v>
       </c>
       <c r="E27" t="n">
         <v>0.8388</v>
@@ -1698,7 +1698,7 @@
         <v>0.076</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1744</v>
+        <v>-0.2004</v>
       </c>
       <c r="E28" t="n">
         <v>0.6113</v>
@@ -1744,7 +1744,7 @@
         <v>0.0485</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.2638</v>
+        <v>-0.2885</v>
       </c>
       <c r="E29" t="n">
         <v>0.3901</v>
@@ -1790,7 +1790,7 @@
         <v>-0.0318</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.5458</v>
       </c>
       <c r="E30" t="n">
         <v>-0.2557</v>
@@ -1836,7 +1836,7 @@
         <v>-0.0365</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5399</v>
+        <v>-0.5608</v>
       </c>
       <c r="E31" t="n">
         <v>-0.2934</v>
@@ -1882,7 +1882,7 @@
         <v>-0.0452</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5683</v>
+        <v>-0.5888</v>
       </c>
       <c r="E32" t="n">
         <v>-0.3637</v>
@@ -1928,7 +1928,7 @@
         <v>-0.1032</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7568</v>
+        <v>-0.7747000000000001</v>
       </c>
       <c r="E33" t="n">
         <v>-0.8303</v>
@@ -1974,7 +1974,7 @@
         <v>-0.1078</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-0.7894</v>
       </c>
       <c r="E34" t="n">
         <v>-0.8671</v>
@@ -2020,7 +2020,7 @@
         <v>-0.1447</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8915999999999999</v>
+        <v>-0.9076</v>
       </c>
       <c r="E35" t="n">
         <v>-1.164</v>
@@ -2066,7 +2066,7 @@
         <v>-0.1522</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.916</v>
+        <v>-0.9318</v>
       </c>
       <c r="E36" t="n">
         <v>-1.2245</v>
@@ -2112,7 +2112,7 @@
         <v>-0.1548</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9244</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E37" t="n">
         <v>-1.2451</v>
@@ -2158,7 +2158,7 @@
         <v>-0.1853</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0238</v>
+        <v>-1.038</v>
       </c>
       <c r="E38" t="n">
         <v>-1.4912</v>
@@ -2204,7 +2204,7 @@
         <v>-0.1869</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0288</v>
+        <v>-1.043</v>
       </c>
       <c r="E39" t="n">
         <v>-1.5037</v>
@@ -2250,7 +2250,7 @@
         <v>-0.1876</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.031</v>
+        <v>-1.0451</v>
       </c>
       <c r="E40" t="n">
         <v>-1.509</v>
@@ -2296,7 +2296,7 @@
         <v>-0.2068</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.0936</v>
+        <v>-1.1069</v>
       </c>
       <c r="E41" t="n">
         <v>-1.6641</v>

--- a/database/event/2150/event_2150_evp_summary.xlsx
+++ b/database/event/2150/event_2150_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.519399999999999</v>
+        <v>7.9963</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0589</v>
+        <v>0.9939</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9502</v>
+        <v>2.9719</v>
       </c>
       <c r="E2" t="n">
-        <v>8.519399999999999</v>
+        <v>7.9963</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0179</v>
+        <v>3.0313</v>
       </c>
       <c r="G2" t="n">
-        <v>5.5015</v>
+        <v>4.965</v>
       </c>
       <c r="H2" t="n">
-        <v>3.0179</v>
+        <v>5.1941</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4461</v>
+        <v>2.7007</v>
       </c>
       <c r="J2" t="n">
-        <v>5.5015</v>
+        <v>4.965</v>
       </c>
       <c r="K2" t="n">
         <v>136</v>
@@ -529,7 +529,7 @@
         <v>230</v>
       </c>
       <c r="M2" t="n">
-        <v>7.9476</v>
+        <v>7.665699999999999</v>
       </c>
       <c r="N2" t="n">
         <v>366</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.4399</v>
+        <v>7.153</v>
       </c>
       <c r="C3" t="n">
-        <v>1.049</v>
+        <v>0.889</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9185</v>
+        <v>2.5912</v>
       </c>
       <c r="E3" t="n">
-        <v>8.4399</v>
+        <v>7.153</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6528</v>
+        <v>3.1124</v>
       </c>
       <c r="G3" t="n">
-        <v>4.7871</v>
+        <v>4.0406</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6528</v>
+        <v>5.4799</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9607</v>
+        <v>2.8493</v>
       </c>
       <c r="J3" t="n">
-        <v>4.7871</v>
+        <v>4.0406</v>
       </c>
       <c r="K3" t="n">
         <v>136</v>
@@ -575,7 +575,7 @@
         <v>230</v>
       </c>
       <c r="M3" t="n">
-        <v>7.7478</v>
+        <v>6.889900000000001</v>
       </c>
       <c r="N3" t="n">
         <v>366</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.984</v>
+        <v>6.5064</v>
       </c>
       <c r="C4" t="n">
-        <v>0.868</v>
+        <v>0.8087</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3385</v>
+        <v>2.2993</v>
       </c>
       <c r="E4" t="n">
-        <v>6.984</v>
+        <v>6.5064</v>
       </c>
       <c r="F4" t="n">
-        <v>4.2361</v>
+        <v>3.9393</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7479</v>
+        <v>2.5671</v>
       </c>
       <c r="H4" t="n">
-        <v>4.4824</v>
+        <v>8.3934</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6331</v>
+        <v>4.3642</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7479</v>
+        <v>2.5671</v>
       </c>
       <c r="K4" t="n">
         <v>132</v>
@@ -621,7 +621,7 @@
         <v>181</v>
       </c>
       <c r="M4" t="n">
-        <v>6.381</v>
+        <v>6.9313</v>
       </c>
       <c r="N4" t="n">
         <v>313</v>
@@ -630,35 +630,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>Pimp</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.7911</v>
+        <v>6.1528</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7198</v>
+        <v>0.7647</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8633</v>
+        <v>2.1397</v>
       </c>
       <c r="E5" t="n">
-        <v>5.7911</v>
+        <v>6.1528</v>
       </c>
       <c r="F5" t="n">
-        <v>4.351</v>
+        <v>2.6702</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4401</v>
+        <v>3.4826</v>
       </c>
       <c r="H5" t="n">
-        <v>4.9445</v>
+        <v>3.9219</v>
       </c>
       <c r="I5" t="n">
-        <v>4.0076</v>
+        <v>2.0392</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4401</v>
+        <v>3.4826</v>
       </c>
       <c r="K5" t="n">
         <v>132</v>
@@ -667,7 +667,7 @@
         <v>181</v>
       </c>
       <c r="M5" t="n">
-        <v>5.4477</v>
+        <v>5.521800000000001</v>
       </c>
       <c r="N5" t="n">
         <v>313</v>
@@ -676,35 +676,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pimp</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.7187</v>
+        <v>5.7143</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7108</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8344</v>
+        <v>1.9417</v>
       </c>
       <c r="E6" t="n">
-        <v>5.7187</v>
+        <v>5.7143</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2139</v>
+        <v>4.2123</v>
       </c>
       <c r="G6" t="n">
-        <v>3.5048</v>
+        <v>1.502</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2139</v>
+        <v>9.3553</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7944</v>
+        <v>4.8643</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5048</v>
+        <v>1.502</v>
       </c>
       <c r="K6" t="n">
         <v>132</v>
@@ -713,7 +713,7 @@
         <v>181</v>
       </c>
       <c r="M6" t="n">
-        <v>5.2992</v>
+        <v>6.3663</v>
       </c>
       <c r="N6" t="n">
         <v>313</v>
@@ -722,185 +722,185 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.5586</v>
+        <v>4.3357</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5666</v>
+        <v>0.5389</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3722</v>
+        <v>1.3193</v>
       </c>
       <c r="E7" t="n">
-        <v>4.5586</v>
+        <v>4.3357</v>
       </c>
       <c r="F7" t="n">
-        <v>3.5405</v>
+        <v>3.9962</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0181</v>
+        <v>0.3395</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5405</v>
+        <v>8.5936</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8696</v>
+        <v>4.4683</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0181</v>
+        <v>0.3395</v>
       </c>
       <c r="K7" t="n">
-        <v>187</v>
+        <v>124</v>
       </c>
       <c r="L7" t="n">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8877</v>
+        <v>4.8078</v>
       </c>
       <c r="N7" t="n">
-        <v>311</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>AcilioN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.5427</v>
+        <v>4.315</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5646</v>
+        <v>0.5363</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3659</v>
+        <v>1.31</v>
       </c>
       <c r="E8" t="n">
-        <v>4.5427</v>
+        <v>4.315</v>
       </c>
       <c r="F8" t="n">
-        <v>4.3548</v>
+        <v>3.2445</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1879</v>
+        <v>1.0705</v>
       </c>
       <c r="H8" t="n">
-        <v>4.9598</v>
+        <v>5.9453</v>
       </c>
       <c r="I8" t="n">
-        <v>4.0201</v>
+        <v>3.0913</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1879</v>
+        <v>1.0705</v>
       </c>
       <c r="K8" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="L8" t="n">
-        <v>75</v>
+        <v>181</v>
       </c>
       <c r="M8" t="n">
-        <v>4.208</v>
+        <v>4.161799999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>199</v>
+        <v>313</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AcilioN</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.3186</v>
+        <v>4.1257</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.5128</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2766</v>
+        <v>1.2245</v>
       </c>
       <c r="E9" t="n">
-        <v>4.3186</v>
+        <v>4.1257</v>
       </c>
       <c r="F9" t="n">
-        <v>3.1534</v>
+        <v>3.2411</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1653</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>3.1534</v>
+        <v>5.9334</v>
       </c>
       <c r="I9" t="n">
-        <v>2.5559</v>
+        <v>3.0851</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1653</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>132</v>
+        <v>187</v>
       </c>
       <c r="L9" t="n">
-        <v>181</v>
+        <v>124</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7212</v>
+        <v>3.9697</v>
       </c>
       <c r="N9" t="n">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.1073</v>
+        <v>4.0301</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5105</v>
+        <v>0.5009</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1924</v>
+        <v>1.1814</v>
       </c>
       <c r="E10" t="n">
-        <v>4.1073</v>
+        <v>4.0301</v>
       </c>
       <c r="F10" t="n">
-        <v>4.2612</v>
+        <v>0.9001</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1539</v>
+        <v>3.13</v>
       </c>
       <c r="H10" t="n">
-        <v>4.5834</v>
+        <v>0.9001</v>
       </c>
       <c r="I10" t="n">
-        <v>3.715</v>
+        <v>0.468</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1539</v>
+        <v>3.13</v>
       </c>
       <c r="K10" t="n">
-        <v>187</v>
+        <v>136</v>
       </c>
       <c r="L10" t="n">
-        <v>124</v>
+        <v>230</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5611</v>
+        <v>3.598</v>
       </c>
       <c r="N10" t="n">
-        <v>311</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.8023</v>
+        <v>4.0118</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4726</v>
+        <v>0.4986</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0709</v>
+        <v>1.1731</v>
       </c>
       <c r="E11" t="n">
-        <v>3.8023</v>
+        <v>4.0118</v>
       </c>
       <c r="F11" t="n">
-        <v>2.9194</v>
+        <v>3.2371</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8829</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>2.9194</v>
+        <v>5.9192</v>
       </c>
       <c r="I11" t="n">
-        <v>2.3662</v>
+        <v>3.0777</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8829</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="K11" t="n">
         <v>132</v>
@@ -943,7 +943,7 @@
         <v>181</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2491</v>
+        <v>3.8524</v>
       </c>
       <c r="N11" t="n">
         <v>313</v>
@@ -952,35 +952,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.7555</v>
+        <v>3.9272</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4668</v>
+        <v>0.4881</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0523</v>
+        <v>1.1349</v>
       </c>
       <c r="E12" t="n">
-        <v>3.7555</v>
+        <v>3.9272</v>
       </c>
       <c r="F12" t="n">
-        <v>3.21</v>
+        <v>3.8424</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5455</v>
+        <v>0.0848</v>
       </c>
       <c r="H12" t="n">
-        <v>3.21</v>
+        <v>8.0519</v>
       </c>
       <c r="I12" t="n">
-        <v>2.6018</v>
+        <v>4.1866</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5455</v>
+        <v>0.0848</v>
       </c>
       <c r="K12" t="n">
         <v>187</v>
@@ -989,7 +989,7 @@
         <v>124</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1473</v>
+        <v>4.271400000000001</v>
       </c>
       <c r="N12" t="n">
         <v>311</v>
@@ -998,47 +998,47 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.662</v>
+        <v>3.7354</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4551</v>
+        <v>0.4643</v>
       </c>
       <c r="D13" t="n">
-        <v>1.015</v>
+        <v>1.0483</v>
       </c>
       <c r="E13" t="n">
-        <v>3.662</v>
+        <v>3.7354</v>
       </c>
       <c r="F13" t="n">
-        <v>0.389</v>
+        <v>3.0846</v>
       </c>
       <c r="G13" t="n">
-        <v>3.273</v>
+        <v>0.6508</v>
       </c>
       <c r="H13" t="n">
-        <v>0.389</v>
+        <v>5.3818</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3153</v>
+        <v>2.7983</v>
       </c>
       <c r="J13" t="n">
-        <v>3.273</v>
+        <v>0.6508</v>
       </c>
       <c r="K13" t="n">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="L13" t="n">
-        <v>230</v>
+        <v>124</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5883</v>
+        <v>3.4491</v>
       </c>
       <c r="N13" t="n">
-        <v>366</v>
+        <v>311</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3112</v>
+        <v>3.609</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2873</v>
+        <v>0.4486</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4769</v>
+        <v>0.9913</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3112</v>
+        <v>3.609</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1436</v>
+        <v>2.2457</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1676</v>
+        <v>1.3633</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1436</v>
+        <v>2.426</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9268999999999999</v>
+        <v>1.2614</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1676</v>
+        <v>1.3633</v>
       </c>
       <c r="K14" t="n">
         <v>136</v>
@@ -1081,7 +1081,7 @@
         <v>230</v>
       </c>
       <c r="M14" t="n">
-        <v>2.0945</v>
+        <v>2.6247</v>
       </c>
       <c r="N14" t="n">
         <v>366</v>
@@ -1090,173 +1090,173 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SHOOWTiME</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.1573</v>
+        <v>2.8697</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2681</v>
+        <v>0.3567</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4156</v>
+        <v>0.6575</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1573</v>
+        <v>2.8697</v>
       </c>
       <c r="F15" t="n">
-        <v>4.1573</v>
+        <v>2.8697</v>
       </c>
       <c r="G15" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1651</v>
+        <v>2.9417</v>
       </c>
       <c r="I15" t="n">
-        <v>3.3759</v>
+        <v>2.9417</v>
       </c>
       <c r="J15" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>136</v>
+        <v>175</v>
       </c>
       <c r="L15" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.3759</v>
+        <v>2.9417</v>
       </c>
       <c r="N15" t="n">
-        <v>366</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.0137</v>
+        <v>2.5389</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2503</v>
+        <v>0.3156</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3583</v>
+        <v>0.5082</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0137</v>
+        <v>2.5389</v>
       </c>
       <c r="F16" t="n">
-        <v>3.0137</v>
+        <v>2.5389</v>
       </c>
       <c r="G16" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.0137</v>
+        <v>2.5389</v>
       </c>
       <c r="I16" t="n">
-        <v>2.4427</v>
+        <v>2.5389</v>
       </c>
       <c r="J16" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>124</v>
+        <v>184</v>
       </c>
       <c r="L16" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4427</v>
+        <v>2.5389</v>
       </c>
       <c r="N16" t="n">
-        <v>199</v>
+        <v>184</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>ANGE1</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.877</v>
+        <v>2.3855</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2333</v>
+        <v>0.2965</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3039</v>
+        <v>0.4389</v>
       </c>
       <c r="E17" t="n">
-        <v>1.877</v>
+        <v>2.3855</v>
       </c>
       <c r="F17" t="n">
-        <v>1.877</v>
+        <v>2.7958</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.4103</v>
       </c>
       <c r="H17" t="n">
-        <v>1.877</v>
+        <v>4.3642</v>
       </c>
       <c r="I17" t="n">
-        <v>1.877</v>
+        <v>2.2692</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.4103</v>
       </c>
       <c r="K17" t="n">
-        <v>184</v>
+        <v>124</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M17" t="n">
-        <v>1.877</v>
+        <v>1.8589</v>
       </c>
       <c r="N17" t="n">
-        <v>184</v>
+        <v>199</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ANGE1</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8371</v>
+        <v>2.2429</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2283</v>
+        <v>0.2788</v>
       </c>
       <c r="D18" t="n">
-        <v>0.288</v>
+        <v>0.3745</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8371</v>
+        <v>2.2429</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5654</v>
+        <v>2.9647</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-0.7218</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5654</v>
+        <v>4.9593</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0793</v>
+        <v>2.5786</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-0.7218</v>
       </c>
       <c r="K18" t="n">
         <v>124</v>
@@ -1265,7 +1265,7 @@
         <v>75</v>
       </c>
       <c r="M18" t="n">
-        <v>1.351</v>
+        <v>1.8568</v>
       </c>
       <c r="N18" t="n">
         <v>199</v>
@@ -1274,185 +1274,185 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.7589</v>
+        <v>2.1164</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2186</v>
+        <v>0.263</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2568</v>
+        <v>0.3174</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7589</v>
+        <v>2.1164</v>
       </c>
       <c r="F19" t="n">
-        <v>2.7589</v>
+        <v>2.1164</v>
       </c>
       <c r="G19" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7589</v>
+        <v>2.1164</v>
       </c>
       <c r="I19" t="n">
-        <v>2.2362</v>
+        <v>2.1164</v>
       </c>
       <c r="J19" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>124</v>
+        <v>184</v>
       </c>
       <c r="L19" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2362</v>
+        <v>2.1164</v>
       </c>
       <c r="N19" t="n">
-        <v>199</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.6387</v>
+        <v>2.1058</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2037</v>
+        <v>0.2617</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2089</v>
+        <v>0.3126</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6387</v>
+        <v>2.1058</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6387</v>
+        <v>3.1058</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6387</v>
+        <v>5.4564</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6387</v>
+        <v>2.8371</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K20" t="n">
-        <v>175</v>
+        <v>124</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M20" t="n">
-        <v>1.6387</v>
+        <v>1.8371</v>
       </c>
       <c r="N20" t="n">
-        <v>175</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TENZKI</t>
+          <t>Zero</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4401</v>
+        <v>2.066</v>
       </c>
       <c r="C21" t="n">
-        <v>0.179</v>
+        <v>0.2568</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1298</v>
+        <v>0.2947</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4401</v>
+        <v>2.066</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4401</v>
+        <v>2.2539</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.1879</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4401</v>
+        <v>2.455</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4401</v>
+        <v>1.2765</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.1879</v>
       </c>
       <c r="K21" t="n">
-        <v>175</v>
+        <v>124</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4401</v>
+        <v>1.0886</v>
       </c>
       <c r="N21" t="n">
-        <v>175</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.251</v>
+        <v>2.0213</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1555</v>
+        <v>0.2512</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0545</v>
+        <v>0.2745</v>
       </c>
       <c r="E22" t="n">
-        <v>1.251</v>
+        <v>2.0213</v>
       </c>
       <c r="F22" t="n">
-        <v>1.251</v>
+        <v>1.5678</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.4535</v>
       </c>
       <c r="H22" t="n">
-        <v>1.251</v>
+        <v>1.5678</v>
       </c>
       <c r="I22" t="n">
-        <v>1.251</v>
+        <v>0.8152</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.4535</v>
       </c>
       <c r="K22" t="n">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M22" t="n">
-        <v>1.251</v>
+        <v>1.2687</v>
       </c>
       <c r="N22" t="n">
-        <v>175</v>
+        <v>311</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1699</v>
+        <v>1.913</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1454</v>
+        <v>0.2378</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0222</v>
+        <v>0.2256</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1699</v>
+        <v>1.913</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1699</v>
+        <v>1.913</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.1699</v>
+        <v>1.913</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1699</v>
+        <v>1.913</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1699</v>
+        <v>1.913</v>
       </c>
       <c r="N23" t="n">
         <v>184</v>
@@ -1504,507 +1504,507 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DAVEY</t>
+          <t>TENZKI</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.0735</v>
+        <v>1.9007</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1334</v>
+        <v>0.2362</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0162</v>
+        <v>0.2201</v>
       </c>
       <c r="E24" t="n">
-        <v>1.0735</v>
+        <v>1.9007</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0735</v>
+        <v>1.9007</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.0735</v>
+        <v>1.9007</v>
       </c>
       <c r="I24" t="n">
-        <v>1.0735</v>
+        <v>1.9007</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.0735</v>
+        <v>1.9007</v>
       </c>
       <c r="N24" t="n">
-        <v>155</v>
+        <v>175</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>RUBINO</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9175</v>
+        <v>1.7337</v>
       </c>
       <c r="C25" t="n">
-        <v>0.114</v>
+        <v>0.2155</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0784</v>
+        <v>0.1447</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9175</v>
+        <v>1.7337</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9175</v>
+        <v>1.7337</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9175</v>
+        <v>1.7337</v>
       </c>
       <c r="I25" t="n">
-        <v>0.9175</v>
+        <v>1.7337</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.9175</v>
+        <v>1.7337</v>
       </c>
       <c r="N25" t="n">
-        <v>184</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8825</v>
+        <v>1.7234</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1097</v>
+        <v>0.2142</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.09229999999999999</v>
+        <v>0.14</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8825</v>
+        <v>1.7234</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4887</v>
+        <v>1.7234</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3938</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4887</v>
+        <v>1.7234</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3961</v>
+        <v>1.7234</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3938</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="L26" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7899</v>
+        <v>1.7234</v>
       </c>
       <c r="N26" t="n">
-        <v>311</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>RUBINO</t>
+          <t>SHOOWTiME</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8388</v>
+        <v>1.5599</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1043</v>
+        <v>0.1939</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.1097</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8388</v>
+        <v>1.5599</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8388</v>
+        <v>3.4775</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-1.9176</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8388</v>
+        <v>6.7664</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8388</v>
+        <v>3.5182</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-1.9176</v>
       </c>
       <c r="K27" t="n">
-        <v>175</v>
+        <v>136</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="M27" t="n">
-        <v>0.8388</v>
+        <v>1.6006</v>
       </c>
       <c r="N27" t="n">
-        <v>175</v>
+        <v>366</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6113</v>
+        <v>1.226</v>
       </c>
       <c r="C28" t="n">
-        <v>0.076</v>
+        <v>0.1524</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2004</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6113</v>
+        <v>1.226</v>
       </c>
       <c r="F28" t="n">
-        <v>1.0419</v>
+        <v>1.226</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.4306</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.0419</v>
+        <v>1.226</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8445</v>
+        <v>1.226</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.4306</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>124</v>
+        <v>184</v>
       </c>
       <c r="L28" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.4139</v>
+        <v>1.226</v>
       </c>
       <c r="N28" t="n">
-        <v>199</v>
+        <v>184</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.3901</v>
+        <v>1.0197</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0485</v>
+        <v>0.1267</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.2885</v>
+        <v>-0.1777</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3901</v>
+        <v>1.0197</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3901</v>
+        <v>0.9699</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.0498</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3901</v>
+        <v>0.9699</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3901</v>
+        <v>0.5043</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.0498</v>
       </c>
       <c r="K29" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M29" t="n">
-        <v>0.3901</v>
+        <v>0.5540999999999999</v>
       </c>
       <c r="N29" t="n">
-        <v>184</v>
+        <v>311</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>DAVEY</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2557</v>
+        <v>0.9758</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0318</v>
+        <v>0.1213</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5458</v>
+        <v>-0.1975</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2557</v>
+        <v>0.9758</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2028</v>
+        <v>0.9758</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.0529</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2028</v>
+        <v>0.9758</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1644</v>
+        <v>0.9758</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.0529</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="L30" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2173</v>
+        <v>0.9758</v>
       </c>
       <c r="N30" t="n">
-        <v>311</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>daps</t>
+          <t>arya</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2934</v>
+        <v>0.0411</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0365</v>
+        <v>0.0051</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5608</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2934</v>
+        <v>0.0411</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.2934</v>
+        <v>0.0411</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2934</v>
+        <v>0.0411</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2934</v>
+        <v>0.0411</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>184</v>
+        <v>155</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2934</v>
+        <v>0.0411</v>
       </c>
       <c r="N31" t="n">
-        <v>184</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>arya</t>
+          <t>daps</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3637</v>
+        <v>-0.0851</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0452</v>
+        <v>-0.0106</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5888</v>
+        <v>-0.6764</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3637</v>
+        <v>-0.0851</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.3637</v>
+        <v>-0.0851</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3637</v>
+        <v>-0.0851</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3637</v>
+        <v>-0.0851</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3637</v>
+        <v>-0.0851</v>
       </c>
       <c r="N32" t="n">
-        <v>155</v>
+        <v>184</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Professor_Chaos</t>
+          <t>MAiNLiNE</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.8303</v>
+        <v>-0.318</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1032</v>
+        <v>-0.0395</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7747000000000001</v>
+        <v>-0.7816</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.8303</v>
+        <v>-0.318</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.8303</v>
+        <v>-0.318</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.8303</v>
+        <v>-0.318</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8303</v>
+        <v>-0.318</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>155</v>
+        <v>79</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.8303</v>
+        <v>-0.318</v>
       </c>
       <c r="N33" t="n">
-        <v>155</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MAiNLiNE</t>
+          <t>Professor_Chaos</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.8671</v>
+        <v>-0.4128</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1078</v>
+        <v>-0.0513</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7894</v>
+        <v>-0.8244</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.8671</v>
+        <v>-0.4128</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.8671</v>
+        <v>-0.4128</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8671</v>
+        <v>-0.4128</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.8671</v>
+        <v>-0.4128</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>79</v>
+        <v>155</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.8671</v>
+        <v>-0.4128</v>
       </c>
       <c r="N34" t="n">
-        <v>79</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.164</v>
+        <v>-0.526</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1447</v>
+        <v>-0.0654</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9076</v>
+        <v>-0.8754999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.164</v>
+        <v>-0.526</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.164</v>
+        <v>-0.526</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.164</v>
+        <v>-0.526</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.164</v>
+        <v>-0.526</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.164</v>
+        <v>-0.526</v>
       </c>
       <c r="N35" t="n">
         <v>155</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.2245</v>
+        <v>-0.5797</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1522</v>
+        <v>-0.0721</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9318</v>
+        <v>-0.8997000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.2245</v>
+        <v>-0.5797</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.2245</v>
+        <v>-0.5797</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.2245</v>
+        <v>-0.5797</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.2245</v>
+        <v>-0.5797</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.2245</v>
+        <v>-0.5797</v>
       </c>
       <c r="N36" t="n">
         <v>175</v>
@@ -2102,78 +2102,78 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Relyks</t>
+          <t>jasonR</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2451</v>
+        <v>-0.9328</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1548</v>
+        <v>-0.1159</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.0591</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2451</v>
+        <v>-0.9328</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.2451</v>
+        <v>-0.9328</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.2451</v>
+        <v>-0.9328</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.2451</v>
+        <v>-0.9328</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>79</v>
+        <v>155</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.2451</v>
+        <v>-0.9328</v>
       </c>
       <c r="N37" t="n">
-        <v>79</v>
+        <v>155</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Relyks</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.4912</v>
+        <v>-1.0948</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1853</v>
+        <v>-0.1361</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.038</v>
+        <v>-1.1323</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.4912</v>
+        <v>-1.0948</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.4912</v>
+        <v>-1.0948</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.4912</v>
+        <v>-1.0948</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.4912</v>
+        <v>-1.0948</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.4912</v>
+        <v>-1.0948</v>
       </c>
       <c r="N38" t="n">
         <v>79</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.5037</v>
+        <v>-1.1257</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1869</v>
+        <v>-0.1399</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.043</v>
+        <v>-1.1462</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.5037</v>
+        <v>-1.1257</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.5037</v>
+        <v>-1.1257</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.5037</v>
+        <v>-1.1257</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.5037</v>
+        <v>-1.1257</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.5037</v>
+        <v>-1.1257</v>
       </c>
       <c r="N39" t="n">
         <v>79</v>
@@ -2240,47 +2240,47 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>jasonR</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.509</v>
+        <v>-1.2569</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1876</v>
+        <v>-0.1562</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0451</v>
+        <v>-1.2054</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.509</v>
+        <v>-1.2569</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.509</v>
+        <v>-1.2569</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.509</v>
+        <v>-1.2569</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.509</v>
+        <v>-1.2569</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>155</v>
+        <v>79</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.509</v>
+        <v>-1.2569</v>
       </c>
       <c r="N40" t="n">
-        <v>155</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41">
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.6641</v>
+        <v>-1.4721</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.2068</v>
+        <v>-0.183</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1069</v>
+        <v>-1.3026</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.6641</v>
+        <v>-1.4721</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.6641</v>
+        <v>-1.4721</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.6641</v>
+        <v>-1.4721</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.6641</v>
+        <v>-1.4721</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.6641</v>
+        <v>-1.4721</v>
       </c>
       <c r="N41" t="n">
         <v>79</v>
@@ -2429,10 +2429,10 @@
         <v>0.85</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1373</v>
+        <v>-0.1341</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.8833</v>
+        <v>-2.8161</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.8</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2175</v>
+        <v>-0.1898</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.5675</v>
+        <v>-3.9858</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.78</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.249</v>
+        <v>-0.2112</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.229</v>
+        <v>-4.4352</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.47</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7395</v>
+        <v>-0.5039</v>
       </c>
       <c r="J5" t="n">
-        <v>-15.5295</v>
+        <v>-10.5819</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.39</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8415</v>
+        <v>-0.5793</v>
       </c>
       <c r="J6" t="n">
-        <v>-17.6715</v>
+        <v>-12.1653</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.69</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4781</v>
+        <v>1.3235</v>
       </c>
       <c r="J7" t="n">
-        <v>31.0401</v>
+        <v>27.7935</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.67</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4409</v>
+        <v>1.3002</v>
       </c>
       <c r="J8" t="n">
-        <v>30.2589</v>
+        <v>27.3042</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.41</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8828</v>
+        <v>0.9794</v>
       </c>
       <c r="J9" t="n">
-        <v>18.5388</v>
+        <v>20.5674</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.36</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7685999999999999</v>
+        <v>0.8813</v>
       </c>
       <c r="J10" t="n">
-        <v>16.1406</v>
+        <v>18.5073</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.06</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0399</v>
+        <v>0.1298</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8379</v>
+        <v>2.7258</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.32</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5335</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>19.206</v>
+        <v>22.9536</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.27</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4679</v>
+        <v>0.5515</v>
       </c>
       <c r="J13" t="n">
-        <v>16.8444</v>
+        <v>19.854</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.08</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1765</v>
+        <v>0.1971</v>
       </c>
       <c r="J14" t="n">
-        <v>6.354</v>
+        <v>7.0956</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.79</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4061</v>
+        <v>-0.2533</v>
       </c>
       <c r="J15" t="n">
-        <v>-14.6196</v>
+        <v>-9.1188</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.73</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4877</v>
+        <v>-0.3118</v>
       </c>
       <c r="J16" t="n">
-        <v>-17.5572</v>
+        <v>-11.2248</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.47</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2389</v>
+        <v>1.1454</v>
       </c>
       <c r="J17" t="n">
-        <v>44.6004</v>
+        <v>41.2344</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.18</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5847</v>
+        <v>0.5481</v>
       </c>
       <c r="J18" t="n">
-        <v>21.0492</v>
+        <v>19.7316</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.15</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.4694</v>
       </c>
       <c r="J19" t="n">
-        <v>18.162</v>
+        <v>16.8984</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.96</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2326</v>
+        <v>-0.1779</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.3736</v>
+        <v>-6.4044</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.5</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.3385</v>
+        <v>-1.3615</v>
       </c>
       <c r="J21" t="n">
-        <v>-48.186</v>
+        <v>-49.014</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.38</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5343</v>
+        <v>0.4785</v>
       </c>
       <c r="J22" t="n">
-        <v>13.3575</v>
+        <v>11.9625</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.36</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5083</v>
+        <v>0.4565</v>
       </c>
       <c r="J23" t="n">
-        <v>12.7075</v>
+        <v>11.4125</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.32</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4541</v>
+        <v>0.4122</v>
       </c>
       <c r="J24" t="n">
-        <v>11.3525</v>
+        <v>10.305</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.31</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4398</v>
+        <v>0.4011</v>
       </c>
       <c r="J25" t="n">
-        <v>10.995</v>
+        <v>10.0275</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.03</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0078</v>
+        <v>0.0327</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.195</v>
+        <v>0.8175</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>0.95</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0549</v>
+        <v>-0.0612</v>
       </c>
       <c r="J27" t="n">
-        <v>-1.3725</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0747</v>
+        <v>-0.0738</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.8675</v>
+        <v>-1.845</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.92</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.113</v>
+        <v>-0.0978</v>
       </c>
       <c r="J29" t="n">
-        <v>-2.825</v>
+        <v>-2.445</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.83</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2906</v>
+        <v>-0.1921</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.265</v>
+        <v>-4.8025</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.66</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5433</v>
+        <v>-0.3568</v>
       </c>
       <c r="J31" t="n">
-        <v>-13.5825</v>
+        <v>-8.92</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.47</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7507</v>
+        <v>0.9351</v>
       </c>
       <c r="J32" t="n">
-        <v>18.0168</v>
+        <v>22.4424</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.99</v>
       </c>
       <c r="I33" t="n">
-        <v>0.001</v>
+        <v>-0.0152</v>
       </c>
       <c r="J33" t="n">
-        <v>0.024</v>
+        <v>-0.3648</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.8</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3676</v>
+        <v>-0.2316</v>
       </c>
       <c r="J34" t="n">
-        <v>-8.8224</v>
+        <v>-5.5584</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.73</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4674</v>
+        <v>-0.3002</v>
       </c>
       <c r="J35" t="n">
-        <v>-11.2176</v>
+        <v>-7.2048</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.7</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.508</v>
+        <v>-0.329</v>
       </c>
       <c r="J36" t="n">
-        <v>-12.192</v>
+        <v>-7.896</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.57</v>
       </c>
       <c r="I37" t="n">
-        <v>1.3657</v>
+        <v>1.2336</v>
       </c>
       <c r="J37" t="n">
-        <v>32.7768</v>
+        <v>29.6064</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.43</v>
       </c>
       <c r="I38" t="n">
-        <v>1.0851</v>
+        <v>1.0532</v>
       </c>
       <c r="J38" t="n">
-        <v>26.0424</v>
+        <v>25.2768</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.22</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5997</v>
+        <v>0.6093</v>
       </c>
       <c r="J39" t="n">
-        <v>14.3928</v>
+        <v>14.6232</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.95</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3245</v>
+        <v>-0.2474</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.788</v>
+        <v>-5.9376</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.77</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.797</v>
+        <v>-0.7488</v>
       </c>
       <c r="J41" t="n">
-        <v>-19.128</v>
+        <v>-17.9712</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.55</v>
       </c>
       <c r="I42" t="n">
-        <v>1.3151</v>
+        <v>0.9283</v>
       </c>
       <c r="J42" t="n">
-        <v>32.8775</v>
+        <v>23.2075</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.29</v>
       </c>
       <c r="I43" t="n">
-        <v>0.761</v>
+        <v>0.5893</v>
       </c>
       <c r="J43" t="n">
-        <v>19.025</v>
+        <v>14.7325</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.16</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3982</v>
+        <v>0.4084</v>
       </c>
       <c r="J44" t="n">
-        <v>9.955</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.14</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3431</v>
+        <v>0.3779</v>
       </c>
       <c r="J45" t="n">
-        <v>8.577500000000001</v>
+        <v>9.4475</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.92</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4233</v>
+        <v>-0.3474</v>
       </c>
       <c r="J46" t="n">
-        <v>-10.5825</v>
+        <v>-8.685</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.08</v>
       </c>
       <c r="I47" t="n">
-        <v>0.249</v>
+        <v>0.2512</v>
       </c>
       <c r="J47" t="n">
-        <v>6.225</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.92</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1111</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="J48" t="n">
-        <v>-2.7775</v>
+        <v>-2.43</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.82</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3058</v>
+        <v>-0.2016</v>
       </c>
       <c r="J49" t="n">
-        <v>-7.645</v>
+        <v>-5.04</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.76</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4011</v>
+        <v>-0.2606</v>
       </c>
       <c r="J50" t="n">
-        <v>-10.0275</v>
+        <v>-6.515</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.7</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4877</v>
+        <v>-0.3183</v>
       </c>
       <c r="J51" t="n">
-        <v>-12.1925</v>
+        <v>-7.9575</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.53</v>
       </c>
       <c r="I52" t="n">
-        <v>1.2547</v>
+        <v>0.8927</v>
       </c>
       <c r="J52" t="n">
-        <v>28.8581</v>
+        <v>20.5321</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.34</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8525</v>
+        <v>0.6494</v>
       </c>
       <c r="J53" t="n">
-        <v>19.6075</v>
+        <v>14.9362</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.23</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5584</v>
+        <v>0.5039</v>
       </c>
       <c r="J54" t="n">
-        <v>12.8432</v>
+        <v>11.5897</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.14</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3211</v>
+        <v>0.3721</v>
       </c>
       <c r="J55" t="n">
-        <v>7.3853</v>
+        <v>8.558299999999999</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.04</v>
       </c>
       <c r="I56" t="n">
-        <v>0.0289</v>
+        <v>0.1055</v>
       </c>
       <c r="J56" t="n">
-        <v>0.6647</v>
+        <v>2.4265</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.31</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5894</v>
+        <v>0.5561</v>
       </c>
       <c r="J57" t="n">
-        <v>13.5562</v>
+        <v>12.7903</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.88</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1799</v>
+        <v>-0.1405</v>
       </c>
       <c r="J58" t="n">
-        <v>-4.1377</v>
+        <v>-3.2315</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.8</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3345</v>
+        <v>-0.2202</v>
       </c>
       <c r="J59" t="n">
-        <v>-7.6935</v>
+        <v>-5.0646</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.68</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5125</v>
+        <v>-0.336</v>
       </c>
       <c r="J60" t="n">
-        <v>-11.7875</v>
+        <v>-7.728</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6692</v>
+        <v>-0.4482</v>
       </c>
       <c r="J61" t="n">
-        <v>-15.3916</v>
+        <v>-10.3086</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>0.72</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.2718</v>
+        <v>-0.2357</v>
       </c>
       <c r="J62" t="n">
-        <v>-5.436</v>
+        <v>-4.714</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.58</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.4896</v>
+        <v>-0.3808</v>
       </c>
       <c r="J63" t="n">
-        <v>-9.792</v>
+        <v>-7.616</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.5238</v>
+        <v>-0.3995</v>
       </c>
       <c r="J64" t="n">
-        <v>-10.476</v>
+        <v>-7.99</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.46</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.7072000000000001</v>
+        <v>-0.4897</v>
       </c>
       <c r="J65" t="n">
-        <v>-14.144</v>
+        <v>-9.794</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.36</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.8484</v>
+        <v>-0.5863</v>
       </c>
       <c r="J66" t="n">
-        <v>-16.968</v>
+        <v>-11.726</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.67</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7965</v>
+        <v>0.5755</v>
       </c>
       <c r="J67" t="n">
-        <v>15.93</v>
+        <v>11.51</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.62</v>
       </c>
       <c r="I68" t="n">
-        <v>0.7395</v>
+        <v>0.547</v>
       </c>
       <c r="J68" t="n">
-        <v>14.79</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.61</v>
       </c>
       <c r="I69" t="n">
-        <v>0.7277</v>
+        <v>0.5413</v>
       </c>
       <c r="J69" t="n">
-        <v>14.554</v>
+        <v>10.826</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.53</v>
       </c>
       <c r="I70" t="n">
-        <v>0.6194</v>
+        <v>0.496</v>
       </c>
       <c r="J70" t="n">
-        <v>12.388</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.38</v>
       </c>
       <c r="I71" t="n">
-        <v>0.4384</v>
+        <v>0.4043</v>
       </c>
       <c r="J71" t="n">
-        <v>8.768000000000001</v>
+        <v>8.086</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.09</v>
       </c>
       <c r="I72" t="n">
-        <v>0.2568</v>
+        <v>0.2016</v>
       </c>
       <c r="J72" t="n">
-        <v>7.4472</v>
+        <v>5.8464</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.01</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0961</v>
+        <v>0.0507</v>
       </c>
       <c r="J73" t="n">
-        <v>2.7869</v>
+        <v>1.4703</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.97</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0217</v>
+        <v>-0.0376</v>
       </c>
       <c r="J74" t="n">
-        <v>-0.6293</v>
+        <v>-1.0904</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.77</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3944</v>
+        <v>-0.254</v>
       </c>
       <c r="J75" t="n">
-        <v>-11.4376</v>
+        <v>-7.366</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6755</v>
+        <v>-0.4524</v>
       </c>
       <c r="J76" t="n">
-        <v>-19.5895</v>
+        <v>-13.1196</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.44</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6217</v>
+        <v>0.4619</v>
       </c>
       <c r="J77" t="n">
-        <v>18.0293</v>
+        <v>13.3951</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.37</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5353</v>
+        <v>0.4162</v>
       </c>
       <c r="J78" t="n">
-        <v>15.5237</v>
+        <v>12.0698</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.31</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4564</v>
+        <v>0.3764</v>
       </c>
       <c r="J79" t="n">
-        <v>13.2356</v>
+        <v>10.9156</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.04</v>
       </c>
       <c r="I80" t="n">
-        <v>0.0207</v>
+        <v>0.0555</v>
       </c>
       <c r="J80" t="n">
-        <v>0.6002999999999999</v>
+        <v>1.6095</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.02</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.0207</v>
+        <v>0.0193</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.6002999999999999</v>
+        <v>0.5597</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.62</v>
       </c>
       <c r="I82" t="n">
-        <v>1.4201</v>
+        <v>1.0001</v>
       </c>
       <c r="J82" t="n">
-        <v>38.3427</v>
+        <v>27.0027</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.56</v>
       </c>
       <c r="I83" t="n">
-        <v>1.305</v>
+        <v>0.9261</v>
       </c>
       <c r="J83" t="n">
-        <v>35.235</v>
+        <v>25.0047</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.18</v>
       </c>
       <c r="I84" t="n">
-        <v>0.4177</v>
+        <v>0.4304</v>
       </c>
       <c r="J84" t="n">
-        <v>11.2779</v>
+        <v>11.6208</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.09</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1759</v>
+        <v>0.2564</v>
       </c>
       <c r="J85" t="n">
-        <v>4.7493</v>
+        <v>6.9228</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.92</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4407</v>
+        <v>-0.3623</v>
       </c>
       <c r="J86" t="n">
-        <v>-11.8989</v>
+        <v>-9.7821</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.11</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3099</v>
+        <v>0.3261</v>
       </c>
       <c r="J87" t="n">
-        <v>8.3673</v>
+        <v>8.8047</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.03</v>
       </c>
       <c r="I88" t="n">
-        <v>0.164</v>
+        <v>0.142</v>
       </c>
       <c r="J88" t="n">
-        <v>4.428</v>
+        <v>3.834</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.86</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2073</v>
+        <v>-0.1596</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.5971</v>
+        <v>-4.3092</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.66</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5354</v>
+        <v>-0.3527</v>
       </c>
       <c r="J90" t="n">
-        <v>-14.4558</v>
+        <v>-9.5229</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.49</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.7521</v>
+        <v>-0.5104</v>
       </c>
       <c r="J91" t="n">
-        <v>-20.3067</v>
+        <v>-13.7808</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>0.92</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.0707</v>
+        <v>-0.081</v>
       </c>
       <c r="J92" t="n">
-        <v>-1.8382</v>
+        <v>-2.106</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.85</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1919</v>
+        <v>-0.1608</v>
       </c>
       <c r="J93" t="n">
-        <v>-4.9894</v>
+        <v>-4.1808</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.78</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.3126</v>
+        <v>-0.2315</v>
       </c>
       <c r="J94" t="n">
-        <v>-8.127599999999999</v>
+        <v>-6.019</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.76</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3574</v>
+        <v>-0.2497</v>
       </c>
       <c r="J95" t="n">
-        <v>-9.292400000000001</v>
+        <v>-6.4922</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.53</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6904</v>
+        <v>-0.4652</v>
       </c>
       <c r="J96" t="n">
-        <v>-17.9504</v>
+        <v>-12.0952</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.8</v>
       </c>
       <c r="I97" t="n">
-        <v>1.7084</v>
+        <v>1.1995</v>
       </c>
       <c r="J97" t="n">
-        <v>44.4184</v>
+        <v>31.187</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.3</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6812</v>
+        <v>0.5891999999999999</v>
       </c>
       <c r="J98" t="n">
-        <v>17.7112</v>
+        <v>15.3192</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.26</v>
       </c>
       <c r="I99" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.5357</v>
       </c>
       <c r="J99" t="n">
-        <v>15.1892</v>
+        <v>13.9282</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.24</v>
       </c>
       <c r="I100" t="n">
-        <v>0.536</v>
+        <v>0.5081</v>
       </c>
       <c r="J100" t="n">
-        <v>13.936</v>
+        <v>13.2106</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.1</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1812</v>
+        <v>0.2699</v>
       </c>
       <c r="J101" t="n">
-        <v>4.7112</v>
+        <v>7.0174</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.3</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5024</v>
+        <v>0.4896</v>
       </c>
       <c r="J102" t="n">
-        <v>15.072</v>
+        <v>14.688</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.12</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2404</v>
+        <v>0.2739</v>
       </c>
       <c r="J103" t="n">
-        <v>7.212</v>
+        <v>8.217000000000001</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.09</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1877</v>
+        <v>0.2147</v>
       </c>
       <c r="J104" t="n">
-        <v>5.631</v>
+        <v>6.441</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.92</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2092</v>
+        <v>-0.1175</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.276</v>
+        <v>-3.525</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.84</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3373</v>
+        <v>-0.2045</v>
       </c>
       <c r="J106" t="n">
-        <v>-10.119</v>
+        <v>-6.135</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.25</v>
       </c>
       <c r="I107" t="n">
-        <v>0.7391</v>
+        <v>0.5566</v>
       </c>
       <c r="J107" t="n">
-        <v>22.173</v>
+        <v>16.698</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.17</v>
       </c>
       <c r="I108" t="n">
-        <v>0.5366</v>
+        <v>0.4384</v>
       </c>
       <c r="J108" t="n">
-        <v>16.098</v>
+        <v>13.152</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.1</v>
       </c>
       <c r="I109" t="n">
-        <v>0.3307</v>
+        <v>0.3233</v>
       </c>
       <c r="J109" t="n">
-        <v>9.920999999999999</v>
+        <v>9.699</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.07</v>
       </c>
       <c r="I110" t="n">
-        <v>0.2157</v>
+        <v>0.241</v>
       </c>
       <c r="J110" t="n">
-        <v>6.471</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.84</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5985</v>
+        <v>-0.5404</v>
       </c>
       <c r="J111" t="n">
-        <v>-17.955</v>
+        <v>-16.212</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.03</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3128</v>
+        <v>0.3563</v>
       </c>
       <c r="J112" t="n">
-        <v>5.9432</v>
+        <v>6.7697</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.52</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.6113</v>
+        <v>-0.4345</v>
       </c>
       <c r="J113" t="n">
-        <v>-11.6147</v>
+        <v>-8.2555</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.51</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.629</v>
+        <v>-0.4435</v>
       </c>
       <c r="J114" t="n">
-        <v>-11.951</v>
+        <v>-8.426500000000001</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.35</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.8623</v>
+        <v>-0.5965</v>
       </c>
       <c r="J115" t="n">
-        <v>-16.3837</v>
+        <v>-11.3335</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.28</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.9532</v>
+        <v>-0.6655</v>
       </c>
       <c r="J116" t="n">
-        <v>-18.1108</v>
+        <v>-12.6445</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.8</v>
       </c>
       <c r="I117" t="n">
-        <v>1.6373</v>
+        <v>1.1594</v>
       </c>
       <c r="J117" t="n">
-        <v>31.1087</v>
+        <v>22.0286</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.6</v>
       </c>
       <c r="I118" t="n">
-        <v>1.2608</v>
+        <v>0.9321</v>
       </c>
       <c r="J118" t="n">
-        <v>23.9552</v>
+        <v>17.7099</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.54</v>
       </c>
       <c r="I119" t="n">
-        <v>1.1291</v>
+        <v>0.8637</v>
       </c>
       <c r="J119" t="n">
-        <v>21.4529</v>
+        <v>16.4103</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.37</v>
       </c>
       <c r="I120" t="n">
-        <v>0.7513</v>
+        <v>0.6586</v>
       </c>
       <c r="J120" t="n">
-        <v>14.2747</v>
+        <v>12.5134</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.36</v>
       </c>
       <c r="I121" t="n">
-        <v>0.7301</v>
+        <v>0.6458</v>
       </c>
       <c r="J121" t="n">
-        <v>13.8719</v>
+        <v>12.2702</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.24</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4962</v>
+        <v>0.5802</v>
       </c>
       <c r="J122" t="n">
-        <v>10.9164</v>
+        <v>12.7644</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.0683</v>
+        <v>-0.0716</v>
       </c>
       <c r="J123" t="n">
-        <v>-1.5026</v>
+        <v>-1.5752</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0683</v>
+        <v>-0.0716</v>
       </c>
       <c r="J124" t="n">
-        <v>-1.5026</v>
+        <v>-1.5752</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.58</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.644</v>
+        <v>-0.4297</v>
       </c>
       <c r="J125" t="n">
-        <v>-14.168</v>
+        <v>-9.4534</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.53</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.7063</v>
+        <v>-0.4758</v>
       </c>
       <c r="J126" t="n">
-        <v>-15.5386</v>
+        <v>-10.4676</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.93</v>
       </c>
       <c r="I127" t="n">
-        <v>1.915</v>
+        <v>1.6146</v>
       </c>
       <c r="J127" t="n">
-        <v>42.13</v>
+        <v>35.5212</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.38</v>
       </c>
       <c r="I128" t="n">
-        <v>0.8648</v>
+        <v>0.9315</v>
       </c>
       <c r="J128" t="n">
-        <v>19.0256</v>
+        <v>20.493</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.26</v>
       </c>
       <c r="I129" t="n">
-        <v>0.5676</v>
+        <v>0.6691</v>
       </c>
       <c r="J129" t="n">
-        <v>12.4872</v>
+        <v>14.7202</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.24</v>
       </c>
       <c r="I130" t="n">
-        <v>0.5205</v>
+        <v>0.622</v>
       </c>
       <c r="J130" t="n">
-        <v>11.451</v>
+        <v>13.684</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>1.07</v>
       </c>
       <c r="I131" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.1738</v>
       </c>
       <c r="J131" t="n">
-        <v>1.881</v>
+        <v>3.8236</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.67</v>
       </c>
       <c r="I132" t="n">
-        <v>1.021</v>
+        <v>1.2129</v>
       </c>
       <c r="J132" t="n">
-        <v>24.504</v>
+        <v>29.1096</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0585</v>
+        <v>-0.0677</v>
       </c>
       <c r="J133" t="n">
-        <v>-1.404</v>
+        <v>-1.6248</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.63</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.5742</v>
+        <v>-0.3801</v>
       </c>
       <c r="J134" t="n">
-        <v>-13.7808</v>
+        <v>-9.122400000000001</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.46</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.787</v>
+        <v>-0.5371</v>
       </c>
       <c r="J135" t="n">
-        <v>-18.888</v>
+        <v>-12.8904</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.42</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.8341</v>
+        <v>-0.5734</v>
       </c>
       <c r="J136" t="n">
-        <v>-20.0184</v>
+        <v>-13.7616</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.51</v>
       </c>
       <c r="I137" t="n">
-        <v>1.1908</v>
+        <v>1.1313</v>
       </c>
       <c r="J137" t="n">
-        <v>28.5792</v>
+        <v>27.1512</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.49</v>
       </c>
       <c r="I138" t="n">
-        <v>1.1503</v>
+        <v>1.1065</v>
       </c>
       <c r="J138" t="n">
-        <v>27.6072</v>
+        <v>26.556</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.37</v>
       </c>
       <c r="I139" t="n">
-        <v>0.892</v>
+        <v>0.9227</v>
       </c>
       <c r="J139" t="n">
-        <v>21.408</v>
+        <v>22.1448</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.26</v>
       </c>
       <c r="I140" t="n">
-        <v>0.6028</v>
+        <v>0.6829</v>
       </c>
       <c r="J140" t="n">
-        <v>14.4672</v>
+        <v>16.3896</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.9</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5042</v>
+        <v>-0.4285</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.1008</v>
+        <v>-10.284</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.99</v>
       </c>
       <c r="I142" t="n">
-        <v>1.9442</v>
+        <v>1.6464</v>
       </c>
       <c r="J142" t="n">
-        <v>36.9398</v>
+        <v>31.2816</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.78</v>
       </c>
       <c r="I143" t="n">
-        <v>1.6054</v>
+        <v>1.4119</v>
       </c>
       <c r="J143" t="n">
-        <v>30.5026</v>
+        <v>26.8261</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.51</v>
       </c>
       <c r="I144" t="n">
-        <v>1.0563</v>
+        <v>1.104</v>
       </c>
       <c r="J144" t="n">
-        <v>20.0697</v>
+        <v>20.976</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.24</v>
       </c>
       <c r="I145" t="n">
-        <v>0.471</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="J145" t="n">
-        <v>8.949</v>
+        <v>11.2328</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.11</v>
       </c>
       <c r="I146" t="n">
-        <v>0.1588</v>
+        <v>0.2589</v>
       </c>
       <c r="J146" t="n">
-        <v>3.0172</v>
+        <v>4.9191</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>0.74</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.2816</v>
+        <v>-0.2383</v>
       </c>
       <c r="J147" t="n">
-        <v>-5.3504</v>
+        <v>-4.5277</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.3592</v>
+        <v>-0.2899</v>
       </c>
       <c r="J148" t="n">
-        <v>-6.8248</v>
+        <v>-5.5081</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.68</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.3749</v>
+        <v>-0.2999</v>
       </c>
       <c r="J149" t="n">
-        <v>-7.1231</v>
+        <v>-5.6981</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.5904</v>
+        <v>-0.4099</v>
       </c>
       <c r="J150" t="n">
-        <v>-11.2176</v>
+        <v>-7.7881</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.35</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.8794999999999999</v>
+        <v>-0.6086</v>
       </c>
       <c r="J151" t="n">
-        <v>-16.7105</v>
+        <v>-11.5634</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.29</v>
       </c>
       <c r="I152" t="n">
-        <v>0.8005</v>
+        <v>0.7873</v>
       </c>
       <c r="J152" t="n">
-        <v>21.6135</v>
+        <v>21.2571</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.27</v>
       </c>
       <c r="I153" t="n">
-        <v>0.7534</v>
+        <v>0.74</v>
       </c>
       <c r="J153" t="n">
-        <v>20.3418</v>
+        <v>19.98</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.15</v>
       </c>
       <c r="I154" t="n">
-        <v>0.4336</v>
+        <v>0.4464</v>
       </c>
       <c r="J154" t="n">
-        <v>11.7072</v>
+        <v>12.0528</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.14</v>
       </c>
       <c r="I155" t="n">
-        <v>0.3941</v>
+        <v>0.4216</v>
       </c>
       <c r="J155" t="n">
-        <v>10.6407</v>
+        <v>11.3832</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.87</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-0.4741</v>
       </c>
       <c r="J156" t="n">
-        <v>-14.5746</v>
+        <v>-12.8007</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.56</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8263</v>
+        <v>1.0214</v>
       </c>
       <c r="J157" t="n">
-        <v>22.3101</v>
+        <v>27.5778</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.3</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5149</v>
+        <v>0.6112</v>
       </c>
       <c r="J158" t="n">
-        <v>13.9023</v>
+        <v>16.5024</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.83</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.3434</v>
+        <v>-0.2105</v>
       </c>
       <c r="J159" t="n">
-        <v>-9.271800000000001</v>
+        <v>-5.6835</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.77</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4295</v>
+        <v>-0.2706</v>
       </c>
       <c r="J160" t="n">
-        <v>-11.5965</v>
+        <v>-7.3062</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.62</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.6238</v>
+        <v>-0.4126</v>
       </c>
       <c r="J161" t="n">
-        <v>-16.8426</v>
+        <v>-11.1402</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.28</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4893</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="J162" t="n">
-        <v>14.679</v>
+        <v>17.313</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.17</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3345</v>
+        <v>0.3788</v>
       </c>
       <c r="J163" t="n">
-        <v>10.035</v>
+        <v>11.364</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.95</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1408</v>
+        <v>-0.07729999999999999</v>
       </c>
       <c r="J164" t="n">
-        <v>-4.224</v>
+        <v>-2.319</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.93</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1792</v>
+        <v>-0.1015</v>
       </c>
       <c r="J165" t="n">
-        <v>-5.376</v>
+        <v>-3.045</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.74</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.47</v>
+        <v>-0.2996</v>
       </c>
       <c r="J166" t="n">
-        <v>-14.1</v>
+        <v>-8.988</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.34</v>
       </c>
       <c r="I167" t="n">
-        <v>0.947</v>
+        <v>0.9275</v>
       </c>
       <c r="J167" t="n">
-        <v>28.41</v>
+        <v>27.825</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.14</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4549</v>
+        <v>0.4334</v>
       </c>
       <c r="J168" t="n">
-        <v>13.647</v>
+        <v>13.002</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.06</v>
       </c>
       <c r="I169" t="n">
-        <v>0.1822</v>
+        <v>0.2114</v>
       </c>
       <c r="J169" t="n">
-        <v>5.466</v>
+        <v>6.342</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.04</v>
       </c>
       <c r="I170" t="n">
-        <v>0.1104</v>
+        <v>0.1476</v>
       </c>
       <c r="J170" t="n">
-        <v>3.312</v>
+        <v>4.428</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.84</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5978</v>
+        <v>-0.5397999999999999</v>
       </c>
       <c r="J171" t="n">
-        <v>-17.934</v>
+        <v>-16.194</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.02</v>
       </c>
       <c r="I172" t="n">
-        <v>0.1195</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="J172" t="n">
-        <v>3.2265</v>
+        <v>2.5569</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.01</v>
       </c>
       <c r="I173" t="n">
-        <v>0.0944</v>
+        <v>0.0649</v>
       </c>
       <c r="J173" t="n">
-        <v>2.5488</v>
+        <v>1.7523</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.99</v>
       </c>
       <c r="I174" t="n">
-        <v>0.0249</v>
+        <v>-0.0075</v>
       </c>
       <c r="J174" t="n">
-        <v>0.6723</v>
+        <v>-0.2025</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.7</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4952</v>
+        <v>-0.3221</v>
       </c>
       <c r="J175" t="n">
-        <v>-13.3704</v>
+        <v>-8.6967</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.7</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4952</v>
+        <v>-0.3221</v>
       </c>
       <c r="J176" t="n">
-        <v>-13.3704</v>
+        <v>-8.6967</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.61</v>
       </c>
       <c r="I177" t="n">
-        <v>1.4199</v>
+        <v>1.2715</v>
       </c>
       <c r="J177" t="n">
-        <v>38.3373</v>
+        <v>34.3305</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.37</v>
       </c>
       <c r="I178" t="n">
-        <v>0.9325</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J178" t="n">
-        <v>25.1775</v>
+        <v>25.38</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.18</v>
       </c>
       <c r="I179" t="n">
-        <v>0.4392</v>
+        <v>0.506</v>
       </c>
       <c r="J179" t="n">
-        <v>11.8584</v>
+        <v>13.662</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.02</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.0353</v>
+        <v>0.0389</v>
       </c>
       <c r="J180" t="n">
-        <v>-0.9530999999999999</v>
+        <v>1.0503</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.99</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1935</v>
+        <v>-0.112</v>
       </c>
       <c r="J181" t="n">
-        <v>-5.2245</v>
+        <v>-3.024</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.25</v>
       </c>
       <c r="I182" t="n">
-        <v>0.649</v>
+        <v>0.6718</v>
       </c>
       <c r="J182" t="n">
-        <v>18.172</v>
+        <v>18.8104</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.25</v>
       </c>
       <c r="I183" t="n">
-        <v>0.649</v>
+        <v>0.6718</v>
       </c>
       <c r="J183" t="n">
-        <v>18.172</v>
+        <v>18.8104</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.23</v>
       </c>
       <c r="I184" t="n">
-        <v>0.5903</v>
+        <v>0.6261</v>
       </c>
       <c r="J184" t="n">
-        <v>16.5284</v>
+        <v>17.5308</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.21</v>
       </c>
       <c r="I185" t="n">
-        <v>0.5253</v>
+        <v>0.5799</v>
       </c>
       <c r="J185" t="n">
-        <v>14.7084</v>
+        <v>16.2372</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.2</v>
       </c>
       <c r="I186" t="n">
-        <v>0.4974</v>
+        <v>0.5561</v>
       </c>
       <c r="J186" t="n">
-        <v>13.9272</v>
+        <v>15.5708</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.13</v>
       </c>
       <c r="I187" t="n">
-        <v>0.3292</v>
+        <v>0.3555</v>
       </c>
       <c r="J187" t="n">
-        <v>9.217599999999999</v>
+        <v>9.954000000000001</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.05</v>
       </c>
       <c r="I188" t="n">
-        <v>0.1916</v>
+        <v>0.1795</v>
       </c>
       <c r="J188" t="n">
-        <v>5.3648</v>
+        <v>5.026</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.82</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.3088</v>
+        <v>-0.2023</v>
       </c>
       <c r="J189" t="n">
-        <v>-8.6464</v>
+        <v>-5.6644</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.76</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.4032</v>
+        <v>-0.2614</v>
       </c>
       <c r="J190" t="n">
-        <v>-11.2896</v>
+        <v>-7.3192</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.55</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.6846</v>
+        <v>-0.4594</v>
       </c>
       <c r="J191" t="n">
-        <v>-19.1688</v>
+        <v>-12.8632</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.37</v>
       </c>
       <c r="I192" t="n">
-        <v>0.6097</v>
+        <v>0.5648</v>
       </c>
       <c r="J192" t="n">
-        <v>17.0716</v>
+        <v>15.8144</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.17</v>
       </c>
       <c r="I193" t="n">
-        <v>0.3402</v>
+        <v>0.2935</v>
       </c>
       <c r="J193" t="n">
-        <v>9.525600000000001</v>
+        <v>8.218</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.84</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.3239</v>
+        <v>-0.1981</v>
       </c>
       <c r="J194" t="n">
-        <v>-9.0692</v>
+        <v>-5.5468</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.83</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.339</v>
+        <v>-0.2084</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.492000000000001</v>
+        <v>-5.8352</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.78</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4116</v>
+        <v>-0.2587</v>
       </c>
       <c r="J196" t="n">
-        <v>-11.5248</v>
+        <v>-7.2436</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.26</v>
       </c>
       <c r="I197" t="n">
-        <v>0.4385</v>
+        <v>0.3702</v>
       </c>
       <c r="J197" t="n">
-        <v>12.278</v>
+        <v>10.3656</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.17</v>
       </c>
       <c r="I198" t="n">
-        <v>0.3084</v>
+        <v>0.257</v>
       </c>
       <c r="J198" t="n">
-        <v>8.635199999999999</v>
+        <v>7.196</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.07</v>
       </c>
       <c r="I199" t="n">
-        <v>0.124</v>
+        <v>0.1212</v>
       </c>
       <c r="J199" t="n">
-        <v>3.472</v>
+        <v>3.3936</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.03</v>
       </c>
       <c r="I200" t="n">
-        <v>0.0411</v>
+        <v>0.0568</v>
       </c>
       <c r="J200" t="n">
-        <v>1.1508</v>
+        <v>1.5904</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.9</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.2511</v>
+        <v>-0.1437</v>
       </c>
       <c r="J201" t="n">
-        <v>-7.0308</v>
+        <v>-4.0236</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.59</v>
       </c>
       <c r="I202" t="n">
-        <v>1.407</v>
+        <v>1.2607</v>
       </c>
       <c r="J202" t="n">
-        <v>42.21</v>
+        <v>37.821</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.4</v>
       </c>
       <c r="I203" t="n">
-        <v>1.0249</v>
+        <v>1.0101</v>
       </c>
       <c r="J203" t="n">
-        <v>30.747</v>
+        <v>30.303</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.3</v>
       </c>
       <c r="I204" t="n">
-        <v>0.8023</v>
+        <v>0.7987</v>
       </c>
       <c r="J204" t="n">
-        <v>24.069</v>
+        <v>23.961</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.86</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.5774</v>
+        <v>-0.5115</v>
       </c>
       <c r="J205" t="n">
-        <v>-17.322</v>
+        <v>-15.345</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.76</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.8185</v>
+        <v>-0.7726</v>
       </c>
       <c r="J206" t="n">
-        <v>-24.555</v>
+        <v>-23.178</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.22</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4218</v>
+        <v>0.485</v>
       </c>
       <c r="J207" t="n">
-        <v>12.654</v>
+        <v>14.55</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.04</v>
       </c>
       <c r="I208" t="n">
-        <v>0.1271</v>
+        <v>0.1219</v>
       </c>
       <c r="J208" t="n">
-        <v>3.813</v>
+        <v>3.657</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.01</v>
       </c>
       <c r="I209" t="n">
-        <v>0.056</v>
+        <v>0.0423</v>
       </c>
       <c r="J209" t="n">
-        <v>1.68</v>
+        <v>1.269</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1</v>
       </c>
       <c r="I210" t="n">
-        <v>0.02</v>
+        <v>0.0039</v>
       </c>
       <c r="J210" t="n">
-        <v>0.6</v>
+        <v>0.117</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.59</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6539</v>
+        <v>-0.4354</v>
       </c>
       <c r="J211" t="n">
-        <v>-19.617</v>
+        <v>-13.062</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>0.87</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.0391</v>
+        <v>-0.0604</v>
       </c>
       <c r="J212" t="n">
-        <v>-0.7429</v>
+        <v>-1.1476</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.5291</v>
+        <v>-0.4006</v>
       </c>
       <c r="J213" t="n">
-        <v>-10.0529</v>
+        <v>-7.6114</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.5</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.6484</v>
+        <v>-0.4535</v>
       </c>
       <c r="J214" t="n">
-        <v>-12.3196</v>
+        <v>-8.6165</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.45</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.725</v>
+        <v>-0.5004</v>
       </c>
       <c r="J215" t="n">
-        <v>-13.775</v>
+        <v>-9.5076</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.33</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.8898</v>
+        <v>-0.6169</v>
       </c>
       <c r="J216" t="n">
-        <v>-16.9062</v>
+        <v>-11.7211</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.86</v>
       </c>
       <c r="I217" t="n">
-        <v>1.7338</v>
+        <v>1.4963</v>
       </c>
       <c r="J217" t="n">
-        <v>32.9422</v>
+        <v>28.4297</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.81</v>
       </c>
       <c r="I218" t="n">
-        <v>1.646</v>
+        <v>1.4405</v>
       </c>
       <c r="J218" t="n">
-        <v>31.274</v>
+        <v>27.3695</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.44</v>
       </c>
       <c r="I219" t="n">
-        <v>0.8893</v>
+        <v>1.0122</v>
       </c>
       <c r="J219" t="n">
-        <v>16.8967</v>
+        <v>19.2318</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.44</v>
       </c>
       <c r="I220" t="n">
-        <v>0.8893</v>
+        <v>1.0122</v>
       </c>
       <c r="J220" t="n">
-        <v>16.8967</v>
+        <v>19.2318</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.24</v>
       </c>
       <c r="I221" t="n">
-        <v>0.4625</v>
+        <v>0.5849</v>
       </c>
       <c r="J221" t="n">
-        <v>8.7875</v>
+        <v>11.1131</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.3</v>
       </c>
       <c r="I222" t="n">
-        <v>0.4483</v>
+        <v>0.3964</v>
       </c>
       <c r="J222" t="n">
-        <v>12.5524</v>
+        <v>11.0992</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.3</v>
       </c>
       <c r="I223" t="n">
-        <v>0.4483</v>
+        <v>0.3964</v>
       </c>
       <c r="J223" t="n">
-        <v>12.5524</v>
+        <v>11.0992</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.22</v>
       </c>
       <c r="I224" t="n">
-        <v>0.3256</v>
+        <v>0.3039</v>
       </c>
       <c r="J224" t="n">
-        <v>9.1168</v>
+        <v>8.5092</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.19</v>
       </c>
       <c r="I225" t="n">
-        <v>0.2733</v>
+        <v>0.2682</v>
       </c>
       <c r="J225" t="n">
-        <v>7.6524</v>
+        <v>7.5096</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.09</v>
       </c>
       <c r="I226" t="n">
-        <v>0.1137</v>
+        <v>0.1354</v>
       </c>
       <c r="J226" t="n">
-        <v>3.1836</v>
+        <v>3.7912</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.24</v>
       </c>
       <c r="I227" t="n">
-        <v>0.4524</v>
+        <v>0.4013</v>
       </c>
       <c r="J227" t="n">
-        <v>12.6672</v>
+        <v>11.2364</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.07</v>
       </c>
       <c r="I228" t="n">
-        <v>0.1889</v>
+        <v>0.1472</v>
       </c>
       <c r="J228" t="n">
-        <v>5.2892</v>
+        <v>4.1216</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.97</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.065</v>
+        <v>-0.0475</v>
       </c>
       <c r="J229" t="n">
-        <v>-1.82</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.82</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.345</v>
+        <v>-0.2146</v>
       </c>
       <c r="J230" t="n">
-        <v>-9.66</v>
+        <v>-6.0088</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.72</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4868</v>
+        <v>-0.313</v>
       </c>
       <c r="J231" t="n">
-        <v>-13.6304</v>
+        <v>-8.763999999999999</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>0.93</v>
       </c>
       <c r="I232" t="n">
-        <v>-0.0396</v>
+        <v>-0.0617</v>
       </c>
       <c r="J232" t="n">
-        <v>-0.9504</v>
+        <v>-1.4808</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.88</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.1277</v>
+        <v>-0.1218</v>
       </c>
       <c r="J233" t="n">
-        <v>-3.0648</v>
+        <v>-2.9232</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.72</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.4102</v>
+        <v>-0.2835</v>
       </c>
       <c r="J234" t="n">
-        <v>-9.844799999999999</v>
+        <v>-6.804</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.67</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.4902</v>
+        <v>-0.3301</v>
       </c>
       <c r="J235" t="n">
-        <v>-11.7648</v>
+        <v>-7.9224</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.5</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.722</v>
+        <v>-0.489</v>
       </c>
       <c r="J236" t="n">
-        <v>-17.328</v>
+        <v>-11.736</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.72</v>
       </c>
       <c r="I237" t="n">
-        <v>1.5728</v>
+        <v>1.3775</v>
       </c>
       <c r="J237" t="n">
-        <v>37.7472</v>
+        <v>33.06</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.33</v>
       </c>
       <c r="I238" t="n">
-        <v>0.7524</v>
+        <v>0.8319</v>
       </c>
       <c r="J238" t="n">
-        <v>18.0576</v>
+        <v>19.9656</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.27</v>
       </c>
       <c r="I239" t="n">
-        <v>0.6052</v>
+        <v>0.6982</v>
       </c>
       <c r="J239" t="n">
-        <v>14.5248</v>
+        <v>16.7568</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.23</v>
       </c>
       <c r="I240" t="n">
-        <v>0.5092</v>
+        <v>0.6045</v>
       </c>
       <c r="J240" t="n">
-        <v>12.2208</v>
+        <v>14.508</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>1.18</v>
       </c>
       <c r="I241" t="n">
-        <v>0.387</v>
+        <v>0.4818</v>
       </c>
       <c r="J241" t="n">
-        <v>9.288</v>
+        <v>11.5632</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>2.08</v>
       </c>
       <c r="I242" t="n">
-        <v>1.9977</v>
+        <v>1.7132</v>
       </c>
       <c r="J242" t="n">
-        <v>37.9563</v>
+        <v>32.5508</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.88</v>
       </c>
       <c r="I243" t="n">
-        <v>1.7181</v>
+        <v>1.4989</v>
       </c>
       <c r="J243" t="n">
-        <v>32.6439</v>
+        <v>28.4791</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.63</v>
       </c>
       <c r="I244" t="n">
-        <v>1.2205</v>
+        <v>1.2276</v>
       </c>
       <c r="J244" t="n">
-        <v>23.1895</v>
+        <v>23.3244</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.45</v>
       </c>
       <c r="I245" t="n">
-        <v>0.8663999999999999</v>
+        <v>1.0105</v>
       </c>
       <c r="J245" t="n">
-        <v>16.4616</v>
+        <v>19.1995</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>1.4</v>
       </c>
       <c r="I246" t="n">
-        <v>0.7668</v>
+        <v>0.9205</v>
       </c>
       <c r="J246" t="n">
-        <v>14.5692</v>
+        <v>17.4895</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.07</v>
       </c>
       <c r="I247" t="n">
-        <v>0.4429</v>
+        <v>0.6017</v>
       </c>
       <c r="J247" t="n">
-        <v>8.415100000000001</v>
+        <v>11.4323</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.53</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.5211</v>
+        <v>-0.4114</v>
       </c>
       <c r="J248" t="n">
-        <v>-9.9009</v>
+        <v>-7.8166</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.32</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.8806</v>
+        <v>-0.6115</v>
       </c>
       <c r="J249" t="n">
-        <v>-16.7314</v>
+        <v>-11.6185</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.3</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.9083</v>
+        <v>-0.6318</v>
       </c>
       <c r="J250" t="n">
-        <v>-17.2577</v>
+        <v>-12.0042</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.13</v>
       </c>
       <c r="I251" t="n">
-        <v>-1.1293</v>
+        <v>-0.8084</v>
       </c>
       <c r="J251" t="n">
-        <v>-21.4567</v>
+        <v>-15.3596</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.88</v>
       </c>
       <c r="I252" t="n">
-        <v>1.763</v>
+        <v>1.5161</v>
       </c>
       <c r="J252" t="n">
-        <v>29.971</v>
+        <v>25.7737</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.86</v>
       </c>
       <c r="I253" t="n">
-        <v>1.7283</v>
+        <v>1.4939</v>
       </c>
       <c r="J253" t="n">
-        <v>29.3811</v>
+        <v>25.3963</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.71</v>
       </c>
       <c r="I254" t="n">
-        <v>1.4577</v>
+        <v>1.3263</v>
       </c>
       <c r="J254" t="n">
-        <v>24.7809</v>
+        <v>22.5471</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.35</v>
       </c>
       <c r="I255" t="n">
-        <v>0.6967</v>
+        <v>0.834</v>
       </c>
       <c r="J255" t="n">
-        <v>11.8439</v>
+        <v>14.178</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>1.06</v>
       </c>
       <c r="I256" t="n">
-        <v>0.0113</v>
+        <v>0.1037</v>
       </c>
       <c r="J256" t="n">
-        <v>0.1921</v>
+        <v>1.7629</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>0.89</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.0307</v>
+        <v>-0.0566</v>
       </c>
       <c r="J257" t="n">
-        <v>-0.5219</v>
+        <v>-0.9622000000000001</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.85</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.0973</v>
+        <v>-0.1064</v>
       </c>
       <c r="J258" t="n">
-        <v>-1.6541</v>
+        <v>-1.8088</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.53</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.626</v>
+        <v>-0.4338</v>
       </c>
       <c r="J259" t="n">
-        <v>-10.642</v>
+        <v>-7.3746</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.48</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.7003</v>
+        <v>-0.4807</v>
       </c>
       <c r="J260" t="n">
-        <v>-11.9051</v>
+        <v>-8.171900000000001</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.17</v>
       </c>
       <c r="I261" t="n">
-        <v>-1.0938</v>
+        <v>-0.7802</v>
       </c>
       <c r="J261" t="n">
-        <v>-18.5946</v>
+        <v>-13.2634</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.19</v>
       </c>
       <c r="I262" t="n">
-        <v>0.3804</v>
+        <v>0.3297</v>
       </c>
       <c r="J262" t="n">
-        <v>9.1296</v>
+        <v>7.9128</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.06</v>
       </c>
       <c r="I263" t="n">
-        <v>0.1686</v>
+        <v>0.1295</v>
       </c>
       <c r="J263" t="n">
-        <v>4.0464</v>
+        <v>3.108</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.9</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2169</v>
+        <v>-0.1307</v>
       </c>
       <c r="J264" t="n">
-        <v>-5.2056</v>
+        <v>-3.1368</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.89</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.2343</v>
+        <v>-0.1417</v>
       </c>
       <c r="J265" t="n">
-        <v>-5.6232</v>
+        <v>-3.4008</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.8</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3758</v>
+        <v>-0.2352</v>
       </c>
       <c r="J266" t="n">
-        <v>-9.0192</v>
+        <v>-5.6448</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.45</v>
       </c>
       <c r="I267" t="n">
-        <v>0.6411</v>
+        <v>0.5667</v>
       </c>
       <c r="J267" t="n">
-        <v>15.3864</v>
+        <v>13.6008</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.44</v>
       </c>
       <c r="I268" t="n">
-        <v>0.6292</v>
+        <v>0.5557</v>
       </c>
       <c r="J268" t="n">
-        <v>15.1008</v>
+        <v>13.3368</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.21</v>
       </c>
       <c r="I269" t="n">
-        <v>0.3142</v>
+        <v>0.2928</v>
       </c>
       <c r="J269" t="n">
-        <v>7.5408</v>
+        <v>7.0272</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.02</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.0153</v>
+        <v>0.0226</v>
       </c>
       <c r="J270" t="n">
-        <v>-0.3672</v>
+        <v>0.5424</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.93</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.2261</v>
+        <v>-0.1218</v>
       </c>
       <c r="J271" t="n">
-        <v>-5.4264</v>
+        <v>-2.9232</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.5</v>
       </c>
       <c r="I272" t="n">
-        <v>1.1571</v>
+        <v>1.114</v>
       </c>
       <c r="J272" t="n">
-        <v>27.7704</v>
+        <v>26.736</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.43</v>
       </c>
       <c r="I273" t="n">
-        <v>1.01</v>
+        <v>1.0239</v>
       </c>
       <c r="J273" t="n">
-        <v>24.24</v>
+        <v>24.5736</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.35</v>
       </c>
       <c r="I274" t="n">
-        <v>0.8247</v>
+        <v>0.8754999999999999</v>
       </c>
       <c r="J274" t="n">
-        <v>19.7928</v>
+        <v>21.012</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.2</v>
       </c>
       <c r="I275" t="n">
-        <v>0.4412</v>
+        <v>0.5343</v>
       </c>
       <c r="J275" t="n">
-        <v>10.5888</v>
+        <v>12.8232</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>1.19</v>
       </c>
       <c r="I276" t="n">
-        <v>0.4165</v>
+        <v>0.5095</v>
       </c>
       <c r="J276" t="n">
-        <v>9.996</v>
+        <v>12.228</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.26</v>
       </c>
       <c r="I277" t="n">
-        <v>0.5581</v>
+        <v>0.673</v>
       </c>
       <c r="J277" t="n">
-        <v>13.3944</v>
+        <v>16.152</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.83</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.2234</v>
+        <v>-0.1812</v>
       </c>
       <c r="J278" t="n">
-        <v>-5.3616</v>
+        <v>-4.3488</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.76</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.3537</v>
+        <v>-0.2494</v>
       </c>
       <c r="J279" t="n">
-        <v>-8.488799999999999</v>
+        <v>-5.9856</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.62</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.5706</v>
+        <v>-0.3806</v>
       </c>
       <c r="J280" t="n">
-        <v>-13.6944</v>
+        <v>-9.134399999999999</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.35</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.9071</v>
+        <v>-0.6304</v>
       </c>
       <c r="J281" t="n">
-        <v>-21.7704</v>
+        <v>-15.1296</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.76</v>
       </c>
       <c r="I282" t="n">
-        <v>1.5636</v>
+        <v>1.3871</v>
       </c>
       <c r="J282" t="n">
-        <v>29.7084</v>
+        <v>26.3549</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.6</v>
       </c>
       <c r="I283" t="n">
-        <v>1.2576</v>
+        <v>1.2052</v>
       </c>
       <c r="J283" t="n">
-        <v>23.8944</v>
+        <v>22.8988</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.56</v>
       </c>
       <c r="I284" t="n">
-        <v>1.1719</v>
+        <v>1.1596</v>
       </c>
       <c r="J284" t="n">
-        <v>22.2661</v>
+        <v>22.0324</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.42</v>
       </c>
       <c r="I285" t="n">
-        <v>0.8546</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="J285" t="n">
-        <v>16.2374</v>
+        <v>18.6656</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>1.36</v>
       </c>
       <c r="I286" t="n">
-        <v>0.728</v>
+        <v>0.8621</v>
       </c>
       <c r="J286" t="n">
-        <v>13.832</v>
+        <v>16.3799</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>0.85</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.1342</v>
+        <v>-0.1321</v>
       </c>
       <c r="J287" t="n">
-        <v>-2.5498</v>
+        <v>-2.5099</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.65</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.4673</v>
+        <v>-0.3363</v>
       </c>
       <c r="J288" t="n">
-        <v>-8.8787</v>
+        <v>-6.3897</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.64</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.4879</v>
+        <v>-0.345</v>
       </c>
       <c r="J289" t="n">
-        <v>-9.270099999999999</v>
+        <v>-6.555</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.64</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.4879</v>
+        <v>-0.345</v>
       </c>
       <c r="J290" t="n">
-        <v>-9.270099999999999</v>
+        <v>-6.555</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.48</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.7246</v>
+        <v>-0.4934</v>
       </c>
       <c r="J291" t="n">
-        <v>-13.7674</v>
+        <v>-9.374599999999999</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.81</v>
       </c>
       <c r="I292" t="n">
-        <v>1.7359</v>
+        <v>1.485</v>
       </c>
       <c r="J292" t="n">
-        <v>38.1898</v>
+        <v>32.67</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.42</v>
       </c>
       <c r="I293" t="n">
-        <v>0.9849</v>
+        <v>1.0077</v>
       </c>
       <c r="J293" t="n">
-        <v>21.6678</v>
+        <v>22.1694</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.22</v>
       </c>
       <c r="I294" t="n">
-        <v>0.4876</v>
+        <v>0.5817</v>
       </c>
       <c r="J294" t="n">
-        <v>10.7272</v>
+        <v>12.7974</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.21</v>
       </c>
       <c r="I295" t="n">
-        <v>0.4632</v>
+        <v>0.5575</v>
       </c>
       <c r="J295" t="n">
-        <v>10.1904</v>
+        <v>12.265</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.04</v>
       </c>
       <c r="I296" t="n">
-        <v>0.0026</v>
+        <v>0.0859</v>
       </c>
       <c r="J296" t="n">
-        <v>0.0572</v>
+        <v>1.8898</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>0.99</v>
       </c>
       <c r="I297" t="n">
-        <v>0.0367</v>
+        <v>-0.0027</v>
       </c>
       <c r="J297" t="n">
-        <v>0.8074</v>
+        <v>-0.0594</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.98</v>
       </c>
       <c r="I298" t="n">
-        <v>0.0114</v>
+        <v>-0.0189</v>
       </c>
       <c r="J298" t="n">
-        <v>0.2508</v>
+        <v>-0.4158</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.0732</v>
       </c>
       <c r="J299" t="n">
-        <v>-1.6038</v>
+        <v>-1.6104</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.86</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.2255</v>
+        <v>-0.1622</v>
       </c>
       <c r="J300" t="n">
-        <v>-4.961</v>
+        <v>-3.5684</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.51</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.7323</v>
+        <v>-0.4953</v>
       </c>
       <c r="J301" t="n">
-        <v>-16.1106</v>
+        <v>-10.8966</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.68</v>
       </c>
       <c r="I302" t="n">
-        <v>1.4648</v>
+        <v>1.3141</v>
       </c>
       <c r="J302" t="n">
-        <v>30.7608</v>
+        <v>27.5961</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.63</v>
       </c>
       <c r="I303" t="n">
-        <v>1.3706</v>
+        <v>1.2554</v>
       </c>
       <c r="J303" t="n">
-        <v>28.7826</v>
+        <v>26.3634</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.34</v>
       </c>
       <c r="I304" t="n">
-        <v>0.7292</v>
+        <v>0.84</v>
       </c>
       <c r="J304" t="n">
-        <v>15.3132</v>
+        <v>17.64</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.32</v>
       </c>
       <c r="I305" t="n">
-        <v>0.6841</v>
+        <v>0.7958</v>
       </c>
       <c r="J305" t="n">
-        <v>14.3661</v>
+        <v>16.7118</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>1.16</v>
       </c>
       <c r="I306" t="n">
-        <v>0.311</v>
+        <v>0.4133</v>
       </c>
       <c r="J306" t="n">
-        <v>6.531</v>
+        <v>8.6793</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.04</v>
       </c>
       <c r="I307" t="n">
-        <v>0.2411</v>
+        <v>0.2384</v>
       </c>
       <c r="J307" t="n">
-        <v>5.0631</v>
+        <v>5.0064</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.79</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.2565</v>
+        <v>-0.2109</v>
       </c>
       <c r="J308" t="n">
-        <v>-5.3865</v>
+        <v>-4.4289</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.59</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.5911999999999999</v>
+        <v>-0.3989</v>
       </c>
       <c r="J309" t="n">
-        <v>-12.4152</v>
+        <v>-8.376899999999999</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.55</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.6464</v>
+        <v>-0.4363</v>
       </c>
       <c r="J310" t="n">
-        <v>-13.5744</v>
+        <v>-9.1623</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.54</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.6598000000000001</v>
+        <v>-0.4457</v>
       </c>
       <c r="J311" t="n">
-        <v>-13.8558</v>
+        <v>-9.3597</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.26</v>
       </c>
       <c r="I312" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.7288</v>
       </c>
       <c r="J312" t="n">
-        <v>22.545</v>
+        <v>21.864</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.16</v>
       </c>
       <c r="I313" t="n">
-        <v>0.4957</v>
+        <v>0.4798</v>
       </c>
       <c r="J313" t="n">
-        <v>14.871</v>
+        <v>14.394</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.12</v>
       </c>
       <c r="I314" t="n">
-        <v>0.3767</v>
+        <v>0.3754</v>
       </c>
       <c r="J314" t="n">
-        <v>11.301</v>
+        <v>11.262</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.03</v>
       </c>
       <c r="I315" t="n">
-        <v>0.0594</v>
+        <v>0.108</v>
       </c>
       <c r="J315" t="n">
-        <v>1.782</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.96</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.2593</v>
+        <v>-0.1925</v>
       </c>
       <c r="J316" t="n">
-        <v>-7.779</v>
+        <v>-5.775</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.16</v>
       </c>
       <c r="I317" t="n">
-        <v>0.3337</v>
+        <v>0.3721</v>
       </c>
       <c r="J317" t="n">
-        <v>10.011</v>
+        <v>11.163</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.06</v>
       </c>
       <c r="I318" t="n">
-        <v>0.1662</v>
+        <v>0.1677</v>
       </c>
       <c r="J318" t="n">
-        <v>4.986</v>
+        <v>5.031</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.97</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.0766</v>
+        <v>-0.048</v>
       </c>
       <c r="J319" t="n">
-        <v>-2.298</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.87</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2697</v>
+        <v>-0.1639</v>
       </c>
       <c r="J320" t="n">
-        <v>-8.090999999999999</v>
+        <v>-4.917</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.3626</v>
+        <v>-0.2259</v>
       </c>
       <c r="J321" t="n">
-        <v>-10.878</v>
+        <v>-6.777</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.15</v>
       </c>
       <c r="I322" t="n">
-        <v>0.3221</v>
+        <v>0.2724</v>
       </c>
       <c r="J322" t="n">
-        <v>8.6967</v>
+        <v>7.3548</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.09</v>
       </c>
       <c r="I323" t="n">
-        <v>0.2246</v>
+        <v>0.18</v>
       </c>
       <c r="J323" t="n">
-        <v>6.0642</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.06</v>
       </c>
       <c r="I324" t="n">
-        <v>0.1702</v>
+        <v>0.1302</v>
       </c>
       <c r="J324" t="n">
-        <v>4.5954</v>
+        <v>3.5154</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.82</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.345</v>
+        <v>-0.2146</v>
       </c>
       <c r="J325" t="n">
-        <v>-9.315</v>
+        <v>-5.7942</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.7</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.5134</v>
+        <v>-0.3321</v>
       </c>
       <c r="J326" t="n">
-        <v>-13.8618</v>
+        <v>-8.966699999999999</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.38</v>
       </c>
       <c r="I327" t="n">
-        <v>0.5856</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="J327" t="n">
-        <v>15.8112</v>
+        <v>13.7052</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.2</v>
       </c>
       <c r="I328" t="n">
-        <v>0.3443</v>
+        <v>0.2914</v>
       </c>
       <c r="J328" t="n">
-        <v>9.296099999999999</v>
+        <v>7.8678</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>1.06</v>
       </c>
       <c r="I329" t="n">
-        <v>0.0929</v>
+        <v>0.1033</v>
       </c>
       <c r="J329" t="n">
-        <v>2.5083</v>
+        <v>2.7891</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.97</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.1301</v>
+        <v>-0.0612</v>
       </c>
       <c r="J330" t="n">
-        <v>-3.5127</v>
+        <v>-1.6524</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.95</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.1699</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="J331" t="n">
-        <v>-4.5873</v>
+        <v>-2.3625</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.42</v>
       </c>
       <c r="I332" t="n">
-        <v>1.058</v>
+        <v>1.0364</v>
       </c>
       <c r="J332" t="n">
-        <v>28.566</v>
+        <v>27.9828</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.39</v>
       </c>
       <c r="I333" t="n">
-        <v>0.9941</v>
+        <v>0.9879</v>
       </c>
       <c r="J333" t="n">
-        <v>26.8407</v>
+        <v>26.6733</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.23</v>
       </c>
       <c r="I334" t="n">
-        <v>0.6173999999999999</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="J334" t="n">
-        <v>16.6698</v>
+        <v>17.0235</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.14</v>
       </c>
       <c r="I335" t="n">
-        <v>0.3499</v>
+        <v>0.4111</v>
       </c>
       <c r="J335" t="n">
-        <v>9.4473</v>
+        <v>11.0997</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.82</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.6231</v>
       </c>
       <c r="J336" t="n">
-        <v>-18.414</v>
+        <v>-16.8237</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.21</v>
       </c>
       <c r="I337" t="n">
-        <v>0.4169</v>
+        <v>0.4764</v>
       </c>
       <c r="J337" t="n">
-        <v>11.2563</v>
+        <v>12.8628</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.12</v>
       </c>
       <c r="I338" t="n">
-        <v>0.2815</v>
+        <v>0.3025</v>
       </c>
       <c r="J338" t="n">
-        <v>7.6005</v>
+        <v>8.1675</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.97</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.0533</v>
+        <v>-0.046</v>
       </c>
       <c r="J339" t="n">
-        <v>-1.4391</v>
+        <v>-1.242</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.83</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.3245</v>
+        <v>-0.2022</v>
       </c>
       <c r="J340" t="n">
-        <v>-8.7615</v>
+        <v>-5.4594</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.6</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.6375</v>
+        <v>-0.4234</v>
       </c>
       <c r="J341" t="n">
-        <v>-17.2125</v>
+        <v>-11.4318</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.27</v>
       </c>
       <c r="I342" t="n">
-        <v>0.7649</v>
+        <v>0.7466</v>
       </c>
       <c r="J342" t="n">
-        <v>21.4172</v>
+        <v>20.9048</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.24</v>
       </c>
       <c r="I343" t="n">
-        <v>0.6925</v>
+        <v>0.6743</v>
       </c>
       <c r="J343" t="n">
-        <v>19.39</v>
+        <v>18.8804</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.09</v>
       </c>
       <c r="I344" t="n">
-        <v>0.251</v>
+        <v>0.2913</v>
       </c>
       <c r="J344" t="n">
-        <v>7.028</v>
+        <v>8.1564</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>1.07</v>
       </c>
       <c r="I345" t="n">
-        <v>0.1868</v>
+        <v>0.233</v>
       </c>
       <c r="J345" t="n">
-        <v>5.2304</v>
+        <v>6.524</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.95</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.3007</v>
+        <v>-0.2307</v>
       </c>
       <c r="J346" t="n">
-        <v>-8.419600000000001</v>
+        <v>-6.4596</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.2</v>
       </c>
       <c r="I347" t="n">
-        <v>0.4005</v>
+        <v>0.4554</v>
       </c>
       <c r="J347" t="n">
-        <v>11.214</v>
+        <v>12.7512</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>1.06</v>
       </c>
       <c r="I348" t="n">
-        <v>0.175</v>
+        <v>0.1734</v>
       </c>
       <c r="J348" t="n">
-        <v>4.9</v>
+        <v>4.8552</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.1323</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="J349" t="n">
-        <v>-3.7044</v>
+        <v>-2.3408</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.82</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.3416</v>
+        <v>-0.2131</v>
       </c>
       <c r="J350" t="n">
-        <v>-9.5648</v>
+        <v>-5.9668</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.74</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.4569</v>
+        <v>-0.2923</v>
       </c>
       <c r="J351" t="n">
-        <v>-12.7932</v>
+        <v>-8.1844</v>
       </c>
     </row>
     <row r="352">
@@ -16429,10 +16429,10 @@
         <v>1.79</v>
       </c>
       <c r="I352" t="n">
-        <v>1.6835</v>
+        <v>1.4519</v>
       </c>
       <c r="J352" t="n">
-        <v>37.037</v>
+        <v>31.9418</v>
       </c>
     </row>
     <row r="353">
@@ -16469,10 +16469,10 @@
         <v>1.57</v>
       </c>
       <c r="I353" t="n">
-        <v>1.2753</v>
+        <v>1.1916</v>
       </c>
       <c r="J353" t="n">
-        <v>28.0566</v>
+        <v>26.2152</v>
       </c>
     </row>
     <row r="354">
@@ -16509,10 +16509,10 @@
         <v>1.26</v>
       </c>
       <c r="I354" t="n">
-        <v>0.5659</v>
+        <v>0.6683</v>
       </c>
       <c r="J354" t="n">
-        <v>12.4498</v>
+        <v>14.7026</v>
       </c>
     </row>
     <row r="355">
@@ -16549,10 +16549,10 @@
         <v>1.25</v>
       </c>
       <c r="I355" t="n">
-        <v>0.5424</v>
+        <v>0.6448</v>
       </c>
       <c r="J355" t="n">
-        <v>11.9328</v>
+        <v>14.1856</v>
       </c>
     </row>
     <row r="356">
@@ -16589,10 +16589,10 @@
         <v>1.03</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.0422</v>
+        <v>0.0423</v>
       </c>
       <c r="J356" t="n">
-        <v>-0.9284</v>
+        <v>0.9306</v>
       </c>
     </row>
     <row r="357">
@@ -16629,10 +16629,10 @@
         <v>1</v>
       </c>
       <c r="I357" t="n">
-        <v>0.1176</v>
+        <v>0.0822</v>
       </c>
       <c r="J357" t="n">
-        <v>2.5872</v>
+        <v>1.8084</v>
       </c>
     </row>
     <row r="358">
@@ -16669,10 +16669,10 @@
         <v>0.86</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.1653</v>
+        <v>-0.146</v>
       </c>
       <c r="J358" t="n">
-        <v>-3.6366</v>
+        <v>-3.212</v>
       </c>
     </row>
     <row r="359">
@@ -16709,10 +16709,10 @@
         <v>0.76</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.3346</v>
+        <v>-0.2481</v>
       </c>
       <c r="J359" t="n">
-        <v>-7.3612</v>
+        <v>-5.4582</v>
       </c>
     </row>
     <row r="360">
@@ -16749,10 +16749,10 @@
         <v>0.66</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.5084</v>
+        <v>-0.3407</v>
       </c>
       <c r="J360" t="n">
-        <v>-11.1848</v>
+        <v>-7.4954</v>
       </c>
     </row>
     <row r="361">
@@ -16789,10 +16789,10 @@
         <v>0.46</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.7736</v>
+        <v>-0.5272</v>
       </c>
       <c r="J361" t="n">
-        <v>-17.0192</v>
+        <v>-11.5984</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2150/event_2150_evp_summary.xlsx
+++ b/database/event/2150/event_2150_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.9963</v>
+        <v>8.051</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9939</v>
+        <v>1.0006</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9719</v>
+        <v>3.0408</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9963</v>
+        <v>8.051</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0313</v>
+        <v>2.924</v>
       </c>
       <c r="G2" t="n">
-        <v>4.965</v>
+        <v>5.127</v>
       </c>
       <c r="H2" t="n">
-        <v>5.1941</v>
+        <v>4.7532</v>
       </c>
       <c r="I2" t="n">
-        <v>2.7007</v>
+        <v>2.5667</v>
       </c>
       <c r="J2" t="n">
-        <v>4.965</v>
+        <v>5.127</v>
       </c>
       <c r="K2" t="n">
         <v>136</v>
@@ -529,7 +529,7 @@
         <v>230</v>
       </c>
       <c r="M2" t="n">
-        <v>7.665699999999999</v>
+        <v>7.6937</v>
       </c>
       <c r="N2" t="n">
         <v>366</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.153</v>
+        <v>7.3493</v>
       </c>
       <c r="C3" t="n">
-        <v>0.889</v>
+        <v>0.9134</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5912</v>
+        <v>2.7213</v>
       </c>
       <c r="E3" t="n">
-        <v>7.153</v>
+        <v>7.3493</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1124</v>
+        <v>3.0454</v>
       </c>
       <c r="G3" t="n">
-        <v>4.0406</v>
+        <v>4.3039</v>
       </c>
       <c r="H3" t="n">
-        <v>5.4799</v>
+        <v>5.1536</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8493</v>
+        <v>2.7829</v>
       </c>
       <c r="J3" t="n">
-        <v>4.0406</v>
+        <v>4.3039</v>
       </c>
       <c r="K3" t="n">
         <v>136</v>
@@ -575,7 +575,7 @@
         <v>230</v>
       </c>
       <c r="M3" t="n">
-        <v>6.889900000000001</v>
+        <v>7.0868</v>
       </c>
       <c r="N3" t="n">
         <v>366</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.5064</v>
+        <v>6.6531</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8087</v>
+        <v>0.8269</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2993</v>
+        <v>2.4044</v>
       </c>
       <c r="E4" t="n">
-        <v>6.5064</v>
+        <v>6.6531</v>
       </c>
       <c r="F4" t="n">
-        <v>3.9393</v>
+        <v>3.9091</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5671</v>
+        <v>2.744</v>
       </c>
       <c r="H4" t="n">
-        <v>8.3934</v>
+        <v>8.003500000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>4.3642</v>
+        <v>4.3218</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5671</v>
+        <v>2.744</v>
       </c>
       <c r="K4" t="n">
         <v>132</v>
@@ -621,7 +621,7 @@
         <v>181</v>
       </c>
       <c r="M4" t="n">
-        <v>6.9313</v>
+        <v>7.065799999999999</v>
       </c>
       <c r="N4" t="n">
         <v>313</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.1528</v>
+        <v>6.2381</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7647</v>
+        <v>0.7753</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1397</v>
+        <v>2.2155</v>
       </c>
       <c r="E5" t="n">
-        <v>6.1528</v>
+        <v>6.2381</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6702</v>
+        <v>2.6449</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4826</v>
+        <v>3.5932</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9219</v>
+        <v>3.8323</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0392</v>
+        <v>2.0694</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4826</v>
+        <v>3.5932</v>
       </c>
       <c r="K5" t="n">
         <v>132</v>
@@ -667,7 +667,7 @@
         <v>181</v>
       </c>
       <c r="M5" t="n">
-        <v>5.521800000000001</v>
+        <v>5.662599999999999</v>
       </c>
       <c r="N5" t="n">
         <v>313</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.7143</v>
+        <v>5.8044</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.7214</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9417</v>
+        <v>2.0181</v>
       </c>
       <c r="E6" t="n">
-        <v>5.7143</v>
+        <v>5.8044</v>
       </c>
       <c r="F6" t="n">
-        <v>4.2123</v>
+        <v>4.1747</v>
       </c>
       <c r="G6" t="n">
-        <v>1.502</v>
+        <v>1.6297</v>
       </c>
       <c r="H6" t="n">
-        <v>9.3553</v>
+        <v>8.879799999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>4.8643</v>
+        <v>4.795</v>
       </c>
       <c r="J6" t="n">
-        <v>1.502</v>
+        <v>1.6297</v>
       </c>
       <c r="K6" t="n">
         <v>132</v>
@@ -713,7 +713,7 @@
         <v>181</v>
       </c>
       <c r="M6" t="n">
-        <v>6.3663</v>
+        <v>6.4247</v>
       </c>
       <c r="N6" t="n">
         <v>313</v>
@@ -722,185 +722,185 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>AcilioN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.3357</v>
+        <v>4.4158</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5389</v>
+        <v>0.5488</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3193</v>
+        <v>1.386</v>
       </c>
       <c r="E7" t="n">
-        <v>4.3357</v>
+        <v>4.4158</v>
       </c>
       <c r="F7" t="n">
-        <v>3.9962</v>
+        <v>3.1914</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3395</v>
+        <v>1.2244</v>
       </c>
       <c r="H7" t="n">
-        <v>8.5936</v>
+        <v>5.6353</v>
       </c>
       <c r="I7" t="n">
-        <v>4.4683</v>
+        <v>3.043</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3395</v>
+        <v>1.2244</v>
       </c>
       <c r="K7" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="L7" t="n">
-        <v>75</v>
+        <v>181</v>
       </c>
       <c r="M7" t="n">
-        <v>4.8078</v>
+        <v>4.2674</v>
       </c>
       <c r="N7" t="n">
-        <v>199</v>
+        <v>313</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AcilioN</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.315</v>
+        <v>4.2984</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5363</v>
+        <v>0.5342</v>
       </c>
       <c r="D8" t="n">
-        <v>1.31</v>
+        <v>1.3325</v>
       </c>
       <c r="E8" t="n">
-        <v>4.315</v>
+        <v>4.2984</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2445</v>
+        <v>1.0176</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0705</v>
+        <v>3.2808</v>
       </c>
       <c r="H8" t="n">
-        <v>5.9453</v>
+        <v>1.0176</v>
       </c>
       <c r="I8" t="n">
-        <v>3.0913</v>
+        <v>0.5495</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0705</v>
+        <v>3.2808</v>
       </c>
       <c r="K8" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="L8" t="n">
-        <v>181</v>
+        <v>230</v>
       </c>
       <c r="M8" t="n">
-        <v>4.161799999999999</v>
+        <v>3.8303</v>
       </c>
       <c r="N8" t="n">
-        <v>313</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.1257</v>
+        <v>4.1819</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5128</v>
+        <v>0.5198</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2245</v>
+        <v>1.2795</v>
       </c>
       <c r="E9" t="n">
-        <v>4.1257</v>
+        <v>4.1819</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2411</v>
+        <v>3.9011</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8846000000000001</v>
+        <v>0.2808</v>
       </c>
       <c r="H9" t="n">
-        <v>5.9334</v>
+        <v>7.9772</v>
       </c>
       <c r="I9" t="n">
-        <v>3.0851</v>
+        <v>4.3076</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8846000000000001</v>
+        <v>0.2808</v>
       </c>
       <c r="K9" t="n">
-        <v>187</v>
+        <v>124</v>
       </c>
       <c r="L9" t="n">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="M9" t="n">
-        <v>3.9697</v>
+        <v>4.5884</v>
       </c>
       <c r="N9" t="n">
-        <v>311</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.0301</v>
+        <v>4.1404</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5009</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1814</v>
+        <v>1.2606</v>
       </c>
       <c r="E10" t="n">
-        <v>4.0301</v>
+        <v>4.1404</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9001</v>
+        <v>3.1477</v>
       </c>
       <c r="G10" t="n">
-        <v>3.13</v>
+        <v>0.9927</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9001</v>
+        <v>5.4912</v>
       </c>
       <c r="I10" t="n">
-        <v>0.468</v>
+        <v>2.9652</v>
       </c>
       <c r="J10" t="n">
-        <v>3.13</v>
+        <v>0.9927</v>
       </c>
       <c r="K10" t="n">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="L10" t="n">
-        <v>230</v>
+        <v>124</v>
       </c>
       <c r="M10" t="n">
-        <v>3.598</v>
+        <v>3.9579</v>
       </c>
       <c r="N10" t="n">
-        <v>366</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.0118</v>
+        <v>4.091</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4986</v>
+        <v>0.5085</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1731</v>
+        <v>1.2381</v>
       </c>
       <c r="E11" t="n">
-        <v>4.0118</v>
+        <v>4.091</v>
       </c>
       <c r="F11" t="n">
-        <v>3.2371</v>
+        <v>3.1221</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7747000000000001</v>
+        <v>0.9689</v>
       </c>
       <c r="H11" t="n">
-        <v>5.9192</v>
+        <v>5.4069</v>
       </c>
       <c r="I11" t="n">
-        <v>3.0777</v>
+        <v>2.9197</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7747000000000001</v>
+        <v>0.9689</v>
       </c>
       <c r="K11" t="n">
         <v>132</v>
@@ -943,7 +943,7 @@
         <v>181</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8524</v>
+        <v>3.8886</v>
       </c>
       <c r="N11" t="n">
         <v>313</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.9272</v>
+        <v>3.8611</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4881</v>
+        <v>0.4799</v>
       </c>
       <c r="D12" t="n">
-        <v>1.1349</v>
+        <v>1.1334</v>
       </c>
       <c r="E12" t="n">
-        <v>3.9272</v>
+        <v>3.8611</v>
       </c>
       <c r="F12" t="n">
-        <v>3.8424</v>
+        <v>3.7429</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0848</v>
+        <v>0.1182</v>
       </c>
       <c r="H12" t="n">
-        <v>8.0519</v>
+        <v>7.4549</v>
       </c>
       <c r="I12" t="n">
-        <v>4.1866</v>
+        <v>4.0256</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0848</v>
+        <v>0.1182</v>
       </c>
       <c r="K12" t="n">
         <v>187</v>
@@ -989,7 +989,7 @@
         <v>124</v>
       </c>
       <c r="M12" t="n">
-        <v>4.271400000000001</v>
+        <v>4.1438</v>
       </c>
       <c r="N12" t="n">
         <v>311</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.7354</v>
+        <v>3.8169</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4643</v>
+        <v>0.4744</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0483</v>
+        <v>1.1133</v>
       </c>
       <c r="E13" t="n">
-        <v>3.7354</v>
+        <v>3.8169</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0846</v>
+        <v>3.0057</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6508</v>
+        <v>0.8112</v>
       </c>
       <c r="H13" t="n">
-        <v>5.3818</v>
+        <v>5.0227</v>
       </c>
       <c r="I13" t="n">
-        <v>2.7983</v>
+        <v>2.7122</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6508</v>
+        <v>0.8112</v>
       </c>
       <c r="K13" t="n">
         <v>187</v>
@@ -1035,7 +1035,7 @@
         <v>124</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4491</v>
+        <v>3.5234</v>
       </c>
       <c r="N13" t="n">
         <v>311</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.609</v>
+        <v>3.5324</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4486</v>
+        <v>0.439</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9913</v>
+        <v>0.9838</v>
       </c>
       <c r="E14" t="n">
-        <v>3.609</v>
+        <v>3.5324</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2457</v>
+        <v>2.1611</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3633</v>
+        <v>1.3713</v>
       </c>
       <c r="H14" t="n">
-        <v>2.426</v>
+        <v>2.2361</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2614</v>
+        <v>1.2075</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3633</v>
+        <v>1.3713</v>
       </c>
       <c r="K14" t="n">
         <v>136</v>
@@ -1081,7 +1081,7 @@
         <v>230</v>
       </c>
       <c r="M14" t="n">
-        <v>2.6247</v>
+        <v>2.5788</v>
       </c>
       <c r="N14" t="n">
         <v>366</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.8697</v>
+        <v>2.5664</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3567</v>
+        <v>0.319</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6575</v>
+        <v>0.5441</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8697</v>
+        <v>2.5664</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8697</v>
+        <v>2.5664</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.9417</v>
+        <v>2.8921</v>
       </c>
       <c r="I15" t="n">
-        <v>2.9417</v>
+        <v>2.8921</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9417</v>
+        <v>2.8921</v>
       </c>
       <c r="N15" t="n">
         <v>175</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.5389</v>
+        <v>2.3593</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3156</v>
+        <v>0.2932</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5082</v>
+        <v>0.4498</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5389</v>
+        <v>2.3593</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5389</v>
+        <v>2.3593</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5389</v>
+        <v>2.4389</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5389</v>
+        <v>2.4389</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.5389</v>
+        <v>2.4389</v>
       </c>
       <c r="N16" t="n">
         <v>184</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.3855</v>
+        <v>2.2908</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2965</v>
+        <v>0.2847</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4389</v>
+        <v>0.4186</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3855</v>
+        <v>2.2908</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7958</v>
+        <v>2.7316</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4103</v>
+        <v>-0.4408</v>
       </c>
       <c r="H17" t="n">
-        <v>4.3642</v>
+        <v>4.1182</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2692</v>
+        <v>2.2238</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4103</v>
+        <v>-0.4408</v>
       </c>
       <c r="K17" t="n">
         <v>124</v>
@@ -1219,7 +1219,7 @@
         <v>75</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8589</v>
+        <v>1.783</v>
       </c>
       <c r="N17" t="n">
         <v>199</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.2429</v>
+        <v>2.1068</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2788</v>
+        <v>0.2619</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3745</v>
+        <v>0.3349</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2429</v>
+        <v>2.1068</v>
       </c>
       <c r="F18" t="n">
-        <v>2.9647</v>
+        <v>2.8775</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7218</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>4.9593</v>
+        <v>4.5997</v>
       </c>
       <c r="I18" t="n">
-        <v>2.5786</v>
+        <v>2.4838</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7218</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="K18" t="n">
         <v>124</v>
@@ -1265,7 +1265,7 @@
         <v>75</v>
       </c>
       <c r="M18" t="n">
-        <v>1.8568</v>
+        <v>1.7131</v>
       </c>
       <c r="N18" t="n">
         <v>199</v>
@@ -1274,47 +1274,47 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.1164</v>
+        <v>2.0603</v>
       </c>
       <c r="C19" t="n">
-        <v>0.263</v>
+        <v>0.2561</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3174</v>
+        <v>0.3137</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1164</v>
+        <v>2.0603</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1164</v>
+        <v>1.4863</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.574</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1164</v>
+        <v>1.4863</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1164</v>
+        <v>0.8026</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.574</v>
       </c>
       <c r="K19" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M19" t="n">
-        <v>2.1164</v>
+        <v>1.3766</v>
       </c>
       <c r="N19" t="n">
-        <v>184</v>
+        <v>311</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.1058</v>
+        <v>2.0464</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2617</v>
+        <v>0.2543</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3126</v>
+        <v>0.3074</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1058</v>
+        <v>2.0464</v>
       </c>
       <c r="F20" t="n">
-        <v>3.1058</v>
+        <v>3.0464</v>
       </c>
       <c r="G20" t="n">
         <v>-1</v>
       </c>
       <c r="H20" t="n">
-        <v>5.4564</v>
+        <v>5.1571</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8371</v>
+        <v>2.7848</v>
       </c>
       <c r="J20" t="n">
         <v>-1</v>
@@ -1357,7 +1357,7 @@
         <v>75</v>
       </c>
       <c r="M20" t="n">
-        <v>1.8371</v>
+        <v>1.7848</v>
       </c>
       <c r="N20" t="n">
         <v>199</v>
@@ -1366,216 +1366,216 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.066</v>
+        <v>2.0275</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2568</v>
+        <v>0.252</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2947</v>
+        <v>0.2988</v>
       </c>
       <c r="E21" t="n">
-        <v>2.066</v>
+        <v>2.0275</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2539</v>
+        <v>2.0275</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1879</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.455</v>
+        <v>2.0275</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2765</v>
+        <v>2.0275</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1879</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>124</v>
+        <v>184</v>
       </c>
       <c r="L21" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.0886</v>
+        <v>2.0275</v>
       </c>
       <c r="N21" t="n">
-        <v>199</v>
+        <v>184</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>Zero</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.0213</v>
+        <v>2.0243</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2512</v>
+        <v>0.2516</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2745</v>
+        <v>0.2973</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0213</v>
+        <v>2.0243</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5678</v>
+        <v>2.1821</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4535</v>
+        <v>-0.1578</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5678</v>
+        <v>2.3052</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8152</v>
+        <v>1.2448</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4535</v>
+        <v>-0.1578</v>
       </c>
       <c r="K22" t="n">
-        <v>187</v>
+        <v>124</v>
       </c>
       <c r="L22" t="n">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="M22" t="n">
-        <v>1.2687</v>
+        <v>1.087</v>
       </c>
       <c r="N22" t="n">
-        <v>311</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>TENZKI</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.913</v>
+        <v>1.8034</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2378</v>
+        <v>0.2241</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2256</v>
+        <v>0.1967</v>
       </c>
       <c r="E23" t="n">
-        <v>1.913</v>
+        <v>1.8034</v>
       </c>
       <c r="F23" t="n">
-        <v>1.913</v>
+        <v>1.8034</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.913</v>
+        <v>1.8034</v>
       </c>
       <c r="I23" t="n">
-        <v>1.913</v>
+        <v>1.8034</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.913</v>
+        <v>1.8034</v>
       </c>
       <c r="N23" t="n">
-        <v>184</v>
+        <v>175</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TENZKI</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.9007</v>
+        <v>1.7329</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2362</v>
+        <v>0.2154</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2201</v>
+        <v>0.1646</v>
       </c>
       <c r="E24" t="n">
-        <v>1.9007</v>
+        <v>1.7329</v>
       </c>
       <c r="F24" t="n">
-        <v>1.9007</v>
+        <v>1.7329</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.9007</v>
+        <v>1.7329</v>
       </c>
       <c r="I24" t="n">
-        <v>1.9007</v>
+        <v>1.7329</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.9007</v>
+        <v>1.7329</v>
       </c>
       <c r="N24" t="n">
-        <v>175</v>
+        <v>184</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RUBINO</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.7337</v>
+        <v>1.6434</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2155</v>
+        <v>0.2043</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1447</v>
+        <v>0.1239</v>
       </c>
       <c r="E25" t="n">
-        <v>1.7337</v>
+        <v>1.6434</v>
       </c>
       <c r="F25" t="n">
-        <v>1.7337</v>
+        <v>1.6434</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.7337</v>
+        <v>1.6434</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7337</v>
+        <v>1.6434</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.7337</v>
+        <v>1.6434</v>
       </c>
       <c r="N25" t="n">
         <v>175</v>
@@ -1596,32 +1596,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>RUBINO</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.7234</v>
+        <v>1.632</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2142</v>
+        <v>0.2028</v>
       </c>
       <c r="D26" t="n">
-        <v>0.14</v>
+        <v>0.1187</v>
       </c>
       <c r="E26" t="n">
-        <v>1.7234</v>
+        <v>1.632</v>
       </c>
       <c r="F26" t="n">
-        <v>1.7234</v>
+        <v>1.632</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.7234</v>
+        <v>1.632</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7234</v>
+        <v>1.632</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.7234</v>
+        <v>1.632</v>
       </c>
       <c r="N26" t="n">
         <v>175</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.5599</v>
+        <v>1.5439</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1939</v>
+        <v>0.1919</v>
       </c>
       <c r="D27" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0786</v>
       </c>
       <c r="E27" t="n">
-        <v>1.5599</v>
+        <v>1.5439</v>
       </c>
       <c r="F27" t="n">
-        <v>3.4775</v>
+        <v>3.4015</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.9176</v>
+        <v>-1.8576</v>
       </c>
       <c r="H27" t="n">
-        <v>6.7664</v>
+        <v>6.3286</v>
       </c>
       <c r="I27" t="n">
-        <v>3.5182</v>
+        <v>3.4174</v>
       </c>
       <c r="J27" t="n">
-        <v>-1.9176</v>
+        <v>-1.8576</v>
       </c>
       <c r="K27" t="n">
         <v>136</v>
@@ -1679,7 +1679,7 @@
         <v>230</v>
       </c>
       <c r="M27" t="n">
-        <v>1.6006</v>
+        <v>1.5598</v>
       </c>
       <c r="N27" t="n">
         <v>366</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.226</v>
+        <v>1.1037</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1524</v>
+        <v>0.1372</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.1218</v>
       </c>
       <c r="E28" t="n">
-        <v>1.226</v>
+        <v>1.1037</v>
       </c>
       <c r="F28" t="n">
-        <v>1.226</v>
+        <v>1.1037</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.226</v>
+        <v>1.1037</v>
       </c>
       <c r="I28" t="n">
-        <v>1.226</v>
+        <v>1.1037</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.226</v>
+        <v>1.1037</v>
       </c>
       <c r="N28" t="n">
         <v>184</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.0197</v>
+        <v>1.0065</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1267</v>
+        <v>0.1251</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1777</v>
+        <v>-0.166</v>
       </c>
       <c r="E29" t="n">
-        <v>1.0197</v>
+        <v>1.0065</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9699</v>
+        <v>0.9154</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0498</v>
+        <v>0.0911</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9699</v>
+        <v>0.9154</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5043</v>
+        <v>0.4943</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0498</v>
+        <v>0.0911</v>
       </c>
       <c r="K29" t="n">
         <v>187</v>
@@ -1771,7 +1771,7 @@
         <v>124</v>
       </c>
       <c r="M29" t="n">
-        <v>0.5540999999999999</v>
+        <v>0.5854</v>
       </c>
       <c r="N29" t="n">
         <v>311</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9758</v>
+        <v>0.9548</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1213</v>
+        <v>0.1187</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1975</v>
+        <v>-0.1896</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9758</v>
+        <v>0.9548</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9758</v>
+        <v>0.9548</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9758</v>
+        <v>0.9548</v>
       </c>
       <c r="I30" t="n">
-        <v>0.9758</v>
+        <v>0.9548</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.9758</v>
+        <v>0.9548</v>
       </c>
       <c r="N30" t="n">
         <v>155</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0411</v>
+        <v>0.0221</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0051</v>
+        <v>0.0027</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-0.6141</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0411</v>
+        <v>0.0221</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0411</v>
+        <v>0.0221</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0411</v>
+        <v>0.0221</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0411</v>
+        <v>0.0221</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0411</v>
+        <v>0.0221</v>
       </c>
       <c r="N31" t="n">
         <v>155</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.0851</v>
+        <v>-0.1125</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0106</v>
+        <v>-0.014</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6764</v>
+        <v>-0.6754</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.0851</v>
+        <v>-0.1125</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.0851</v>
+        <v>-0.1125</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.0851</v>
+        <v>-0.1125</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.0851</v>
+        <v>-0.1125</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.0851</v>
+        <v>-0.1125</v>
       </c>
       <c r="N32" t="n">
         <v>184</v>
@@ -1918,93 +1918,93 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MAiNLiNE</t>
+          <t>Professor_Chaos</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.318</v>
+        <v>-0.4461</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0395</v>
+        <v>-0.0554</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7816</v>
+        <v>-0.8273</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.318</v>
+        <v>-0.4461</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.318</v>
+        <v>-0.4461</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.318</v>
+        <v>-0.4461</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.318</v>
+        <v>-0.4461</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>79</v>
+        <v>155</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.318</v>
+        <v>-0.4461</v>
       </c>
       <c r="N33" t="n">
-        <v>79</v>
+        <v>155</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Professor_Chaos</t>
+          <t>MAiNLiNE</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4128</v>
+        <v>-0.4544</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0513</v>
+        <v>-0.0565</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8244</v>
+        <v>-0.8310999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4128</v>
+        <v>-0.4544</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4128</v>
+        <v>-0.4544</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4128</v>
+        <v>-0.4544</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4128</v>
+        <v>-0.4544</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>155</v>
+        <v>79</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4128</v>
+        <v>-0.4544</v>
       </c>
       <c r="N34" t="n">
-        <v>155</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.526</v>
+        <v>-0.5659</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0654</v>
+        <v>-0.0703</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8754999999999999</v>
+        <v>-0.8818</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.526</v>
+        <v>-0.5659</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.526</v>
+        <v>-0.5659</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.526</v>
+        <v>-0.5659</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.526</v>
+        <v>-0.5659</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.526</v>
+        <v>-0.5659</v>
       </c>
       <c r="N35" t="n">
         <v>155</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.5797</v>
+        <v>-0.6172</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0721</v>
+        <v>-0.0767</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8997000000000001</v>
+        <v>-0.9052</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.5797</v>
+        <v>-0.6172</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.5797</v>
+        <v>-0.6172</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.5797</v>
+        <v>-0.6172</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5797</v>
+        <v>-0.6172</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.5797</v>
+        <v>-0.6172</v>
       </c>
       <c r="N36" t="n">
         <v>175</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9328</v>
+        <v>-0.9746</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1159</v>
+        <v>-0.1211</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0591</v>
+        <v>-1.0679</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9328</v>
+        <v>-0.9746</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9328</v>
+        <v>-0.9746</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9328</v>
+        <v>-0.9746</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9328</v>
+        <v>-0.9746</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9328</v>
+        <v>-0.9746</v>
       </c>
       <c r="N37" t="n">
         <v>155</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0948</v>
+        <v>-1.1478</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1361</v>
+        <v>-0.1427</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1323</v>
+        <v>-1.1467</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0948</v>
+        <v>-1.1478</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.0948</v>
+        <v>-1.1478</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.0948</v>
+        <v>-1.1478</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.0948</v>
+        <v>-1.1478</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0948</v>
+        <v>-1.1478</v>
       </c>
       <c r="N38" t="n">
         <v>79</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.1257</v>
+        <v>-1.2104</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1399</v>
+        <v>-0.1504</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1462</v>
+        <v>-1.1752</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.1257</v>
+        <v>-1.2104</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.1257</v>
+        <v>-1.2104</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.1257</v>
+        <v>-1.2104</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.1257</v>
+        <v>-1.2104</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.1257</v>
+        <v>-1.2104</v>
       </c>
       <c r="N39" t="n">
         <v>79</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.2569</v>
+        <v>-1.2882</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1562</v>
+        <v>-0.1601</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2054</v>
+        <v>-1.2106</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.2569</v>
+        <v>-1.2882</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.2569</v>
+        <v>-1.2882</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.2569</v>
+        <v>-1.2882</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.2569</v>
+        <v>-1.2882</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.2569</v>
+        <v>-1.2882</v>
       </c>
       <c r="N40" t="n">
         <v>79</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.4721</v>
+        <v>-1.5025</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.183</v>
+        <v>-0.1867</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3026</v>
+        <v>-1.3082</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.4721</v>
+        <v>-1.5025</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.4721</v>
+        <v>-1.5025</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.4721</v>
+        <v>-1.5025</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.4721</v>
+        <v>-1.5025</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.4721</v>
+        <v>-1.5025</v>
       </c>
       <c r="N41" t="n">
         <v>79</v>
@@ -2429,10 +2429,10 @@
         <v>0.85</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1341</v>
+        <v>-0.1597</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.8161</v>
+        <v>-3.3537</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.8</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1898</v>
+        <v>-0.2143</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.9858</v>
+        <v>-4.5003</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.78</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2112</v>
+        <v>-0.2352</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.4352</v>
+        <v>-4.9392</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.47</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5039</v>
+        <v>-0.5148</v>
       </c>
       <c r="J5" t="n">
-        <v>-10.5819</v>
+        <v>-10.8108</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.39</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5793</v>
+        <v>-0.5848</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.1653</v>
+        <v>-12.2808</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.69</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3235</v>
+        <v>1.4147</v>
       </c>
       <c r="J7" t="n">
-        <v>27.7935</v>
+        <v>29.7087</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.67</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3002</v>
+        <v>1.3816</v>
       </c>
       <c r="J8" t="n">
-        <v>27.3042</v>
+        <v>29.0136</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.41</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9794</v>
+        <v>0.9316</v>
       </c>
       <c r="J9" t="n">
-        <v>20.5674</v>
+        <v>19.5636</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.36</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8813</v>
+        <v>0.8389</v>
       </c>
       <c r="J10" t="n">
-        <v>18.5073</v>
+        <v>17.6169</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.06</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1298</v>
+        <v>0.1617</v>
       </c>
       <c r="J11" t="n">
-        <v>2.7258</v>
+        <v>3.3957</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.32</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>22.9536</v>
+        <v>22.2624</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.27</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5515</v>
+        <v>0.5399</v>
       </c>
       <c r="J13" t="n">
-        <v>19.854</v>
+        <v>19.4364</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.08</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1971</v>
+        <v>0.2067</v>
       </c>
       <c r="J14" t="n">
-        <v>7.0956</v>
+        <v>7.4412</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.79</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2533</v>
+        <v>-0.2657</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.1188</v>
+        <v>-9.565200000000001</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.73</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3118</v>
+        <v>-0.3232</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.2248</v>
+        <v>-11.6352</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.47</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1454</v>
+        <v>1.1344</v>
       </c>
       <c r="J17" t="n">
-        <v>41.2344</v>
+        <v>40.8384</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.18</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5481</v>
+        <v>0.5264</v>
       </c>
       <c r="J18" t="n">
-        <v>19.7316</v>
+        <v>18.9504</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.15</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4694</v>
+        <v>0.4556</v>
       </c>
       <c r="J19" t="n">
-        <v>16.8984</v>
+        <v>16.4016</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.96</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1779</v>
+        <v>-0.1781</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.4044</v>
+        <v>-6.4116</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.5</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.3615</v>
+        <v>-1.2253</v>
       </c>
       <c r="J21" t="n">
-        <v>-49.014</v>
+        <v>-44.1108</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.38</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4785</v>
+        <v>0.4911</v>
       </c>
       <c r="J22" t="n">
-        <v>11.9625</v>
+        <v>12.2775</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.36</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4565</v>
+        <v>0.4701</v>
       </c>
       <c r="J23" t="n">
-        <v>11.4125</v>
+        <v>11.7525</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.32</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4122</v>
+        <v>0.4277</v>
       </c>
       <c r="J24" t="n">
-        <v>10.305</v>
+        <v>10.6925</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.31</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4011</v>
+        <v>0.417</v>
       </c>
       <c r="J25" t="n">
-        <v>10.0275</v>
+        <v>10.425</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.03</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0327</v>
+        <v>0.0497</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8175</v>
+        <v>1.2425</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>0.95</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0612</v>
+        <v>-0.07480000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>-1.53</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0738</v>
+        <v>-0.0881</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.845</v>
+        <v>-2.2025</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.92</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0978</v>
+        <v>-0.1131</v>
       </c>
       <c r="J29" t="n">
-        <v>-2.445</v>
+        <v>-2.8275</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.83</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1921</v>
+        <v>-0.2094</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.8025</v>
+        <v>-5.235</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.66</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3568</v>
+        <v>-0.3707</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.92</v>
+        <v>-9.2675</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.47</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9351</v>
+        <v>0.8791</v>
       </c>
       <c r="J32" t="n">
-        <v>22.4424</v>
+        <v>21.0984</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.99</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0152</v>
+        <v>-0.0212</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.3648</v>
+        <v>-0.5088</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.8</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2316</v>
+        <v>-0.2466</v>
       </c>
       <c r="J34" t="n">
-        <v>-5.5584</v>
+        <v>-5.9184</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.73</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3002</v>
+        <v>-0.314</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.2048</v>
+        <v>-7.536</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.7</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.329</v>
+        <v>-0.342</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.896</v>
+        <v>-8.208</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.57</v>
       </c>
       <c r="I37" t="n">
-        <v>1.2336</v>
+        <v>1.2721</v>
       </c>
       <c r="J37" t="n">
-        <v>29.6064</v>
+        <v>30.5304</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.43</v>
       </c>
       <c r="I38" t="n">
-        <v>1.0532</v>
+        <v>1.011</v>
       </c>
       <c r="J38" t="n">
-        <v>25.2768</v>
+        <v>24.264</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.22</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6093</v>
+        <v>0.589</v>
       </c>
       <c r="J39" t="n">
-        <v>14.6232</v>
+        <v>14.136</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.95</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2474</v>
+        <v>-0.2352</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.9376</v>
+        <v>-5.6448</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.77</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7488</v>
+        <v>-0.6912</v>
       </c>
       <c r="J41" t="n">
-        <v>-17.9712</v>
+        <v>-16.5888</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.55</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9283</v>
+        <v>1.0224</v>
       </c>
       <c r="J42" t="n">
-        <v>23.2075</v>
+        <v>25.56</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.29</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5893</v>
+        <v>0.6545</v>
       </c>
       <c r="J43" t="n">
-        <v>14.7325</v>
+        <v>16.3625</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.16</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4084</v>
+        <v>0.4497</v>
       </c>
       <c r="J44" t="n">
-        <v>10.21</v>
+        <v>11.2425</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.14</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3779</v>
+        <v>0.4078</v>
       </c>
       <c r="J45" t="n">
-        <v>9.4475</v>
+        <v>10.195</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.92</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3474</v>
+        <v>-0.3276</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.685</v>
+        <v>-8.19</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.08</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2512</v>
+        <v>0.2462</v>
       </c>
       <c r="J47" t="n">
-        <v>6.28</v>
+        <v>6.155</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.92</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.09719999999999999</v>
+        <v>-0.1126</v>
       </c>
       <c r="J48" t="n">
-        <v>-2.43</v>
+        <v>-2.815</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.82</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2016</v>
+        <v>-0.2191</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.04</v>
+        <v>-5.4775</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.76</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2606</v>
+        <v>-0.2774</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.515</v>
+        <v>-6.935</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.7</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3183</v>
+        <v>-0.3336</v>
       </c>
       <c r="J51" t="n">
-        <v>-7.9575</v>
+        <v>-8.34</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.53</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8927</v>
+        <v>0.9862</v>
       </c>
       <c r="J52" t="n">
-        <v>20.5321</v>
+        <v>22.6826</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.34</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6494</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>14.9362</v>
+        <v>16.6129</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.23</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5039</v>
+        <v>0.5602</v>
       </c>
       <c r="J54" t="n">
-        <v>11.5897</v>
+        <v>12.8846</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.14</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3721</v>
+        <v>0.4012</v>
       </c>
       <c r="J55" t="n">
-        <v>8.558299999999999</v>
+        <v>9.227600000000001</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.04</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1055</v>
+        <v>0.1283</v>
       </c>
       <c r="J56" t="n">
-        <v>2.4265</v>
+        <v>2.9509</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.31</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5561</v>
+        <v>0.6095</v>
       </c>
       <c r="J57" t="n">
-        <v>12.7903</v>
+        <v>14.0185</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.88</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1405</v>
+        <v>-0.1573</v>
       </c>
       <c r="J58" t="n">
-        <v>-3.2315</v>
+        <v>-3.6179</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.8</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2202</v>
+        <v>-0.2378</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.0646</v>
+        <v>-5.4694</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.68</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.336</v>
+        <v>-0.351</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.728</v>
+        <v>-8.073</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4482</v>
+        <v>-0.4581</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.3086</v>
+        <v>-10.5363</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>0.72</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.2357</v>
+        <v>-0.2658</v>
       </c>
       <c r="J62" t="n">
-        <v>-4.714</v>
+        <v>-5.316</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.58</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.3808</v>
+        <v>-0.4027</v>
       </c>
       <c r="J63" t="n">
-        <v>-7.616</v>
+        <v>-8.054</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.3995</v>
+        <v>-0.4203</v>
       </c>
       <c r="J64" t="n">
-        <v>-7.99</v>
+        <v>-8.406000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.46</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.4897</v>
+        <v>-0.5051</v>
       </c>
       <c r="J65" t="n">
-        <v>-9.794</v>
+        <v>-10.102</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.36</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5863</v>
+        <v>-0.5941</v>
       </c>
       <c r="J66" t="n">
-        <v>-11.726</v>
+        <v>-11.882</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.67</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5755</v>
+        <v>0.6662</v>
       </c>
       <c r="J67" t="n">
-        <v>11.51</v>
+        <v>13.324</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.62</v>
       </c>
       <c r="I68" t="n">
-        <v>0.547</v>
+        <v>0.6329</v>
       </c>
       <c r="J68" t="n">
-        <v>10.94</v>
+        <v>12.658</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.61</v>
       </c>
       <c r="I69" t="n">
-        <v>0.5413</v>
+        <v>0.6262</v>
       </c>
       <c r="J69" t="n">
-        <v>10.826</v>
+        <v>12.524</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.53</v>
       </c>
       <c r="I70" t="n">
-        <v>0.496</v>
+        <v>0.5725</v>
       </c>
       <c r="J70" t="n">
-        <v>9.92</v>
+        <v>11.45</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.38</v>
       </c>
       <c r="I71" t="n">
-        <v>0.4043</v>
+        <v>0.4632</v>
       </c>
       <c r="J71" t="n">
-        <v>8.086</v>
+        <v>9.263999999999999</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.09</v>
       </c>
       <c r="I72" t="n">
-        <v>0.2016</v>
+        <v>0.2038</v>
       </c>
       <c r="J72" t="n">
-        <v>5.8464</v>
+        <v>5.9102</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.01</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0507</v>
+        <v>0.0501</v>
       </c>
       <c r="J73" t="n">
-        <v>1.4703</v>
+        <v>1.4529</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.97</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0376</v>
+        <v>-0.0487</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.0904</v>
+        <v>-1.4123</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.77</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.254</v>
+        <v>-0.2702</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.366</v>
+        <v>-7.8358</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4524</v>
+        <v>-0.4615</v>
       </c>
       <c r="J76" t="n">
-        <v>-13.1196</v>
+        <v>-13.3835</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.44</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4619</v>
+        <v>0.5271</v>
       </c>
       <c r="J77" t="n">
-        <v>13.3951</v>
+        <v>15.2859</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.37</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4162</v>
+        <v>0.4729</v>
       </c>
       <c r="J78" t="n">
-        <v>12.0698</v>
+        <v>13.7141</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.31</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3764</v>
+        <v>0.4196</v>
       </c>
       <c r="J79" t="n">
-        <v>10.9156</v>
+        <v>12.1684</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.04</v>
       </c>
       <c r="I80" t="n">
-        <v>0.0555</v>
+        <v>0.0722</v>
       </c>
       <c r="J80" t="n">
-        <v>1.6095</v>
+        <v>2.0938</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.02</v>
       </c>
       <c r="I81" t="n">
-        <v>0.0193</v>
+        <v>0.0337</v>
       </c>
       <c r="J81" t="n">
-        <v>0.5597</v>
+        <v>0.9772999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.62</v>
       </c>
       <c r="I82" t="n">
-        <v>1.0001</v>
+        <v>1.1017</v>
       </c>
       <c r="J82" t="n">
-        <v>27.0027</v>
+        <v>29.7459</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.56</v>
       </c>
       <c r="I83" t="n">
-        <v>0.9261</v>
+        <v>1.0228</v>
       </c>
       <c r="J83" t="n">
-        <v>25.0047</v>
+        <v>27.6156</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.18</v>
       </c>
       <c r="I84" t="n">
-        <v>0.4304</v>
+        <v>0.4779</v>
       </c>
       <c r="J84" t="n">
-        <v>11.6208</v>
+        <v>12.9033</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.09</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2564</v>
+        <v>0.2716</v>
       </c>
       <c r="J85" t="n">
-        <v>6.9228</v>
+        <v>7.3332</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.92</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3623</v>
+        <v>-0.3381</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.7821</v>
+        <v>-9.1287</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.11</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3261</v>
+        <v>0.3172</v>
       </c>
       <c r="J87" t="n">
-        <v>8.8047</v>
+        <v>8.564399999999999</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.03</v>
       </c>
       <c r="I88" t="n">
-        <v>0.142</v>
+        <v>0.1365</v>
       </c>
       <c r="J88" t="n">
-        <v>3.834</v>
+        <v>3.6855</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.86</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1596</v>
+        <v>-0.1772</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.3092</v>
+        <v>-4.7844</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.66</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3527</v>
+        <v>-0.3674</v>
       </c>
       <c r="J90" t="n">
-        <v>-9.5229</v>
+        <v>-9.9198</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.49</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5104</v>
+        <v>-0.5172</v>
       </c>
       <c r="J91" t="n">
-        <v>-13.7808</v>
+        <v>-13.9644</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>0.92</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.081</v>
+        <v>-0.1</v>
       </c>
       <c r="J92" t="n">
-        <v>-2.106</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.85</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1608</v>
+        <v>-0.1806</v>
       </c>
       <c r="J93" t="n">
-        <v>-4.1808</v>
+        <v>-4.6956</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.78</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2315</v>
+        <v>-0.2509</v>
       </c>
       <c r="J94" t="n">
-        <v>-6.019</v>
+        <v>-6.5234</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.76</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2497</v>
+        <v>-0.269</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.4922</v>
+        <v>-6.994</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.53</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4652</v>
+        <v>-0.476</v>
       </c>
       <c r="J96" t="n">
-        <v>-12.0952</v>
+        <v>-12.376</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.8</v>
       </c>
       <c r="I97" t="n">
-        <v>1.1995</v>
+        <v>1.3156</v>
       </c>
       <c r="J97" t="n">
-        <v>31.187</v>
+        <v>34.2056</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.3</v>
       </c>
       <c r="I98" t="n">
-        <v>0.5891999999999999</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="J98" t="n">
-        <v>15.3192</v>
+        <v>17.1028</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.26</v>
       </c>
       <c r="I99" t="n">
-        <v>0.5357</v>
+        <v>0.5982</v>
       </c>
       <c r="J99" t="n">
-        <v>13.9282</v>
+        <v>15.5532</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.24</v>
       </c>
       <c r="I100" t="n">
-        <v>0.5081</v>
+        <v>0.5674</v>
       </c>
       <c r="J100" t="n">
-        <v>13.2106</v>
+        <v>14.7524</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.1</v>
       </c>
       <c r="I101" t="n">
-        <v>0.2699</v>
+        <v>0.2876</v>
       </c>
       <c r="J101" t="n">
-        <v>7.0174</v>
+        <v>7.4776</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.3</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4896</v>
+        <v>0.5456</v>
       </c>
       <c r="J102" t="n">
-        <v>14.688</v>
+        <v>16.368</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.12</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2739</v>
+        <v>0.2817</v>
       </c>
       <c r="J103" t="n">
-        <v>8.217000000000001</v>
+        <v>8.451000000000001</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.09</v>
       </c>
       <c r="I104" t="n">
-        <v>0.2147</v>
+        <v>0.2246</v>
       </c>
       <c r="J104" t="n">
-        <v>6.441</v>
+        <v>6.738</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.92</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1175</v>
+        <v>-0.1281</v>
       </c>
       <c r="J105" t="n">
-        <v>-3.525</v>
+        <v>-3.843</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.84</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2045</v>
+        <v>-0.2167</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.135</v>
+        <v>-6.501</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.25</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5566</v>
+        <v>0.6128</v>
       </c>
       <c r="J107" t="n">
-        <v>16.698</v>
+        <v>18.384</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.17</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4384</v>
+        <v>0.4806</v>
       </c>
       <c r="J108" t="n">
-        <v>13.152</v>
+        <v>14.418</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.1</v>
       </c>
       <c r="I109" t="n">
-        <v>0.3233</v>
+        <v>0.3256</v>
       </c>
       <c r="J109" t="n">
-        <v>9.699</v>
+        <v>9.768000000000001</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.07</v>
       </c>
       <c r="I110" t="n">
-        <v>0.241</v>
+        <v>0.2466</v>
       </c>
       <c r="J110" t="n">
-        <v>7.23</v>
+        <v>7.398</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.84</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5404</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="J111" t="n">
-        <v>-16.212</v>
+        <v>-15.318</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.03</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3563</v>
+        <v>0.3071</v>
       </c>
       <c r="J112" t="n">
-        <v>6.7697</v>
+        <v>5.8349</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.52</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.4345</v>
+        <v>-0.4535</v>
       </c>
       <c r="J113" t="n">
-        <v>-8.2555</v>
+        <v>-8.6165</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.51</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.4435</v>
+        <v>-0.462</v>
       </c>
       <c r="J114" t="n">
-        <v>-8.426500000000001</v>
+        <v>-8.778</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.35</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5965</v>
+        <v>-0.6034</v>
       </c>
       <c r="J115" t="n">
-        <v>-11.3335</v>
+        <v>-11.4646</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.28</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6655</v>
+        <v>-0.6664</v>
       </c>
       <c r="J116" t="n">
-        <v>-12.6445</v>
+        <v>-12.6616</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.8</v>
       </c>
       <c r="I117" t="n">
-        <v>1.1594</v>
+        <v>1.2802</v>
       </c>
       <c r="J117" t="n">
-        <v>22.0286</v>
+        <v>24.3238</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.6</v>
       </c>
       <c r="I118" t="n">
-        <v>0.9321</v>
+        <v>1.0375</v>
       </c>
       <c r="J118" t="n">
-        <v>17.7099</v>
+        <v>19.7125</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.54</v>
       </c>
       <c r="I119" t="n">
-        <v>0.8637</v>
+        <v>0.9635</v>
       </c>
       <c r="J119" t="n">
-        <v>16.4103</v>
+        <v>18.3065</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.37</v>
       </c>
       <c r="I120" t="n">
-        <v>0.6586</v>
+        <v>0.7395</v>
       </c>
       <c r="J120" t="n">
-        <v>12.5134</v>
+        <v>14.0505</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.36</v>
       </c>
       <c r="I121" t="n">
-        <v>0.6458</v>
+        <v>0.7254</v>
       </c>
       <c r="J121" t="n">
-        <v>12.2702</v>
+        <v>13.7826</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.24</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5802</v>
+        <v>0.5516</v>
       </c>
       <c r="J122" t="n">
-        <v>12.7644</v>
+        <v>12.1352</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.0716</v>
+        <v>-0.0863</v>
       </c>
       <c r="J123" t="n">
-        <v>-1.5752</v>
+        <v>-1.8986</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0716</v>
+        <v>-0.0863</v>
       </c>
       <c r="J124" t="n">
-        <v>-1.5752</v>
+        <v>-1.8986</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.58</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.4297</v>
+        <v>-0.4406</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.4534</v>
+        <v>-9.693199999999999</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.53</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4758</v>
+        <v>-0.4843</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.4676</v>
+        <v>-10.6546</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.93</v>
       </c>
       <c r="I127" t="n">
-        <v>1.6146</v>
+        <v>1.6128</v>
       </c>
       <c r="J127" t="n">
-        <v>35.5212</v>
+        <v>35.4816</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.38</v>
       </c>
       <c r="I128" t="n">
-        <v>0.9315</v>
+        <v>0.8824</v>
       </c>
       <c r="J128" t="n">
-        <v>20.493</v>
+        <v>19.4128</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.26</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6691</v>
+        <v>0.6495</v>
       </c>
       <c r="J129" t="n">
-        <v>14.7202</v>
+        <v>14.289</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.24</v>
       </c>
       <c r="I130" t="n">
-        <v>0.622</v>
+        <v>0.6077</v>
       </c>
       <c r="J130" t="n">
-        <v>13.684</v>
+        <v>13.3694</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>1.07</v>
       </c>
       <c r="I131" t="n">
-        <v>0.1738</v>
+        <v>0.2</v>
       </c>
       <c r="J131" t="n">
-        <v>3.8236</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.67</v>
       </c>
       <c r="I132" t="n">
-        <v>1.2129</v>
+        <v>1.178</v>
       </c>
       <c r="J132" t="n">
-        <v>29.1096</v>
+        <v>28.272</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0677</v>
+        <v>-0.0833</v>
       </c>
       <c r="J133" t="n">
-        <v>-1.6248</v>
+        <v>-1.9992</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.63</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.3801</v>
+        <v>-0.3938</v>
       </c>
       <c r="J134" t="n">
-        <v>-9.122400000000001</v>
+        <v>-9.4512</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.46</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.5371</v>
+        <v>-0.5423</v>
       </c>
       <c r="J135" t="n">
-        <v>-12.8904</v>
+        <v>-13.0152</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.42</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5734</v>
+        <v>-0.5763</v>
       </c>
       <c r="J136" t="n">
-        <v>-13.7616</v>
+        <v>-13.8312</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.51</v>
       </c>
       <c r="I137" t="n">
-        <v>1.1313</v>
+        <v>1.0978</v>
       </c>
       <c r="J137" t="n">
-        <v>27.1512</v>
+        <v>26.3472</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.49</v>
       </c>
       <c r="I138" t="n">
-        <v>1.1065</v>
+        <v>1.0708</v>
       </c>
       <c r="J138" t="n">
-        <v>26.556</v>
+        <v>25.6992</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.37</v>
       </c>
       <c r="I139" t="n">
-        <v>0.9227</v>
+        <v>0.8719</v>
       </c>
       <c r="J139" t="n">
-        <v>22.1448</v>
+        <v>20.9256</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.26</v>
       </c>
       <c r="I140" t="n">
-        <v>0.6829</v>
+        <v>0.659</v>
       </c>
       <c r="J140" t="n">
-        <v>16.3896</v>
+        <v>15.816</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.9</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4285</v>
+        <v>-0.3977</v>
       </c>
       <c r="J141" t="n">
-        <v>-10.284</v>
+        <v>-9.5448</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.99</v>
       </c>
       <c r="I142" t="n">
-        <v>1.6464</v>
+        <v>1.6517</v>
       </c>
       <c r="J142" t="n">
-        <v>31.2816</v>
+        <v>31.3823</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.78</v>
       </c>
       <c r="I143" t="n">
-        <v>1.4119</v>
+        <v>1.4048</v>
       </c>
       <c r="J143" t="n">
-        <v>26.8261</v>
+        <v>26.6912</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.51</v>
       </c>
       <c r="I144" t="n">
-        <v>1.104</v>
+        <v>1.074</v>
       </c>
       <c r="J144" t="n">
-        <v>20.976</v>
+        <v>20.406</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.24</v>
       </c>
       <c r="I145" t="n">
-        <v>0.5911999999999999</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="J145" t="n">
-        <v>11.2328</v>
+        <v>11.1378</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.11</v>
       </c>
       <c r="I146" t="n">
-        <v>0.2589</v>
+        <v>0.2861</v>
       </c>
       <c r="J146" t="n">
-        <v>4.9191</v>
+        <v>5.4359</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>0.74</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.2383</v>
+        <v>-0.2642</v>
       </c>
       <c r="J147" t="n">
-        <v>-4.5277</v>
+        <v>-5.0198</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.2899</v>
+        <v>-0.3136</v>
       </c>
       <c r="J148" t="n">
-        <v>-5.5081</v>
+        <v>-5.9584</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.68</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2999</v>
+        <v>-0.3231</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.6981</v>
+        <v>-6.1389</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4099</v>
+        <v>-0.4282</v>
       </c>
       <c r="J150" t="n">
-        <v>-7.7881</v>
+        <v>-8.1358</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.35</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6086</v>
+        <v>-0.613</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.5634</v>
+        <v>-11.647</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.29</v>
       </c>
       <c r="I152" t="n">
-        <v>0.7873</v>
+        <v>0.7444</v>
       </c>
       <c r="J152" t="n">
-        <v>21.2571</v>
+        <v>20.0988</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.27</v>
       </c>
       <c r="I153" t="n">
-        <v>0.74</v>
+        <v>0.7027</v>
       </c>
       <c r="J153" t="n">
-        <v>19.98</v>
+        <v>18.9729</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.15</v>
       </c>
       <c r="I154" t="n">
-        <v>0.4464</v>
+        <v>0.4399</v>
       </c>
       <c r="J154" t="n">
-        <v>12.0528</v>
+        <v>11.8773</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.14</v>
       </c>
       <c r="I155" t="n">
-        <v>0.4216</v>
+        <v>0.4171</v>
       </c>
       <c r="J155" t="n">
-        <v>11.3832</v>
+        <v>11.2617</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.87</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4741</v>
+        <v>-0.4477</v>
       </c>
       <c r="J156" t="n">
-        <v>-12.8007</v>
+        <v>-12.0879</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.56</v>
       </c>
       <c r="I157" t="n">
-        <v>1.0214</v>
+        <v>0.9748</v>
       </c>
       <c r="J157" t="n">
-        <v>27.5778</v>
+        <v>26.3196</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.3</v>
       </c>
       <c r="I158" t="n">
-        <v>0.6112</v>
+        <v>0.593</v>
       </c>
       <c r="J158" t="n">
-        <v>16.5024</v>
+        <v>16.011</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.83</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.2105</v>
+        <v>-0.2236</v>
       </c>
       <c r="J159" t="n">
-        <v>-5.6835</v>
+        <v>-6.0372</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.77</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2706</v>
+        <v>-0.2832</v>
       </c>
       <c r="J160" t="n">
-        <v>-7.3062</v>
+        <v>-7.6464</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.62</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4126</v>
+        <v>-0.421</v>
       </c>
       <c r="J161" t="n">
-        <v>-11.1402</v>
+        <v>-11.367</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.28</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.5619</v>
       </c>
       <c r="J162" t="n">
-        <v>17.313</v>
+        <v>16.857</v>
       </c>
     </row>
     <row r="163">
@@ -8909,10 +8909,10 @@
         <v>0.95</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.0871</v>
       </c>
       <c r="J164" t="n">
-        <v>-2.319</v>
+        <v>-2.613</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.93</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1015</v>
+        <v>-0.1127</v>
       </c>
       <c r="J165" t="n">
-        <v>-3.045</v>
+        <v>-3.381</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.74</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2996</v>
+        <v>-0.3117</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.988</v>
+        <v>-9.351000000000001</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.34</v>
       </c>
       <c r="I167" t="n">
-        <v>0.9275</v>
+        <v>0.8636</v>
       </c>
       <c r="J167" t="n">
-        <v>27.825</v>
+        <v>25.908</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.14</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4334</v>
+        <v>0.425</v>
       </c>
       <c r="J168" t="n">
-        <v>13.002</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.06</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2114</v>
+        <v>0.2185</v>
       </c>
       <c r="J169" t="n">
-        <v>6.342</v>
+        <v>6.555</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.04</v>
       </c>
       <c r="I170" t="n">
-        <v>0.1476</v>
+        <v>0.1575</v>
       </c>
       <c r="J170" t="n">
-        <v>4.428</v>
+        <v>4.725</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.84</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-0.5102</v>
       </c>
       <c r="J171" t="n">
-        <v>-16.194</v>
+        <v>-15.306</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.02</v>
       </c>
       <c r="I172" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.0941</v>
       </c>
       <c r="J172" t="n">
-        <v>2.5569</v>
+        <v>2.5407</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.01</v>
       </c>
       <c r="I173" t="n">
-        <v>0.0649</v>
+        <v>0.063</v>
       </c>
       <c r="J173" t="n">
-        <v>1.7523</v>
+        <v>1.701</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.99</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.0075</v>
+        <v>-0.0153</v>
       </c>
       <c r="J174" t="n">
-        <v>-0.2025</v>
+        <v>-0.4131</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.7</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3221</v>
+        <v>-0.3366</v>
       </c>
       <c r="J175" t="n">
-        <v>-8.6967</v>
+        <v>-9.088200000000001</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.7</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3221</v>
+        <v>-0.3366</v>
       </c>
       <c r="J176" t="n">
-        <v>-8.6967</v>
+        <v>-9.088200000000001</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.61</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2715</v>
+        <v>1.2447</v>
       </c>
       <c r="J177" t="n">
-        <v>34.3305</v>
+        <v>33.6069</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.37</v>
       </c>
       <c r="I178" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8847</v>
       </c>
       <c r="J178" t="n">
-        <v>25.38</v>
+        <v>23.8869</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.18</v>
       </c>
       <c r="I179" t="n">
-        <v>0.506</v>
+        <v>0.4976</v>
       </c>
       <c r="J179" t="n">
-        <v>13.662</v>
+        <v>13.4352</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.02</v>
       </c>
       <c r="I180" t="n">
-        <v>0.0389</v>
+        <v>0.0618</v>
       </c>
       <c r="J180" t="n">
-        <v>1.0503</v>
+        <v>1.6686</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.99</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.112</v>
+        <v>-0.0993</v>
       </c>
       <c r="J181" t="n">
-        <v>-3.024</v>
+        <v>-2.6811</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.25</v>
       </c>
       <c r="I182" t="n">
-        <v>0.6718</v>
+        <v>0.6466</v>
       </c>
       <c r="J182" t="n">
-        <v>18.8104</v>
+        <v>18.1048</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.25</v>
       </c>
       <c r="I183" t="n">
-        <v>0.6718</v>
+        <v>0.6466</v>
       </c>
       <c r="J183" t="n">
-        <v>18.8104</v>
+        <v>18.1048</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.23</v>
       </c>
       <c r="I184" t="n">
-        <v>0.6261</v>
+        <v>0.6056</v>
       </c>
       <c r="J184" t="n">
-        <v>17.5308</v>
+        <v>16.9568</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.21</v>
       </c>
       <c r="I185" t="n">
-        <v>0.5799</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="J185" t="n">
-        <v>16.2372</v>
+        <v>15.792</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.2</v>
       </c>
       <c r="I186" t="n">
-        <v>0.5561</v>
+        <v>0.5425</v>
       </c>
       <c r="J186" t="n">
-        <v>15.5708</v>
+        <v>15.19</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.13</v>
       </c>
       <c r="I187" t="n">
-        <v>0.3555</v>
+        <v>0.3457</v>
       </c>
       <c r="J187" t="n">
-        <v>9.954000000000001</v>
+        <v>9.679600000000001</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.05</v>
       </c>
       <c r="I188" t="n">
-        <v>0.1795</v>
+        <v>0.1771</v>
       </c>
       <c r="J188" t="n">
-        <v>5.026</v>
+        <v>4.9588</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.82</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2023</v>
+        <v>-0.2196</v>
       </c>
       <c r="J189" t="n">
-        <v>-5.6644</v>
+        <v>-6.1488</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.76</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2614</v>
+        <v>-0.278</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.3192</v>
+        <v>-7.784</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.55</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4594</v>
+        <v>-0.4685</v>
       </c>
       <c r="J191" t="n">
-        <v>-12.8632</v>
+        <v>-13.118</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.37</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5648</v>
+        <v>0.5534</v>
       </c>
       <c r="J192" t="n">
-        <v>15.8144</v>
+        <v>15.4952</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.17</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2935</v>
+        <v>0.2994</v>
       </c>
       <c r="J193" t="n">
-        <v>8.218</v>
+        <v>8.3832</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.84</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1981</v>
+        <v>-0.2117</v>
       </c>
       <c r="J194" t="n">
-        <v>-5.5468</v>
+        <v>-5.9276</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.83</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2084</v>
+        <v>-0.222</v>
       </c>
       <c r="J195" t="n">
-        <v>-5.8352</v>
+        <v>-6.216</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.78</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.2587</v>
+        <v>-0.2719</v>
       </c>
       <c r="J196" t="n">
-        <v>-7.2436</v>
+        <v>-7.6132</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.26</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3702</v>
+        <v>0.3817</v>
       </c>
       <c r="J197" t="n">
-        <v>10.3656</v>
+        <v>10.6876</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.17</v>
       </c>
       <c r="I198" t="n">
-        <v>0.257</v>
+        <v>0.2718</v>
       </c>
       <c r="J198" t="n">
-        <v>7.196</v>
+        <v>7.6104</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.07</v>
       </c>
       <c r="I199" t="n">
-        <v>0.1212</v>
+        <v>0.1353</v>
       </c>
       <c r="J199" t="n">
-        <v>3.3936</v>
+        <v>3.7884</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.03</v>
       </c>
       <c r="I200" t="n">
-        <v>0.0568</v>
+        <v>0.0679</v>
       </c>
       <c r="J200" t="n">
-        <v>1.5904</v>
+        <v>1.9012</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.9</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.1437</v>
+        <v>-0.1543</v>
       </c>
       <c r="J201" t="n">
-        <v>-4.0236</v>
+        <v>-4.3204</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.59</v>
       </c>
       <c r="I202" t="n">
-        <v>1.2607</v>
+        <v>1.2307</v>
       </c>
       <c r="J202" t="n">
-        <v>37.821</v>
+        <v>36.921</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.4</v>
       </c>
       <c r="I203" t="n">
-        <v>1.0101</v>
+        <v>0.9530999999999999</v>
       </c>
       <c r="J203" t="n">
-        <v>30.303</v>
+        <v>28.593</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.3</v>
       </c>
       <c r="I204" t="n">
-        <v>0.7987</v>
+        <v>0.7565</v>
       </c>
       <c r="J204" t="n">
-        <v>23.961</v>
+        <v>22.695</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.86</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.5115</v>
+        <v>-0.4795</v>
       </c>
       <c r="J205" t="n">
-        <v>-15.345</v>
+        <v>-14.385</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.76</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.7726</v>
+        <v>-0.7124</v>
       </c>
       <c r="J206" t="n">
-        <v>-23.178</v>
+        <v>-21.372</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.22</v>
       </c>
       <c r="I207" t="n">
-        <v>0.485</v>
+        <v>0.4747</v>
       </c>
       <c r="J207" t="n">
-        <v>14.55</v>
+        <v>14.241</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.04</v>
       </c>
       <c r="I208" t="n">
-        <v>0.1219</v>
+        <v>0.1288</v>
       </c>
       <c r="J208" t="n">
-        <v>3.657</v>
+        <v>3.864</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.01</v>
       </c>
       <c r="I209" t="n">
-        <v>0.0423</v>
+        <v>0.0466</v>
       </c>
       <c r="J209" t="n">
-        <v>1.269</v>
+        <v>1.398</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1</v>
       </c>
       <c r="I210" t="n">
-        <v>0.0039</v>
+        <v>0.0027</v>
       </c>
       <c r="J210" t="n">
-        <v>0.117</v>
+        <v>0.081</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.59</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4354</v>
+        <v>-0.4436</v>
       </c>
       <c r="J211" t="n">
-        <v>-13.062</v>
+        <v>-13.308</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>0.87</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.0604</v>
+        <v>-0.0968</v>
       </c>
       <c r="J212" t="n">
-        <v>-1.1476</v>
+        <v>-1.8392</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.4006</v>
+        <v>-0.4212</v>
       </c>
       <c r="J213" t="n">
-        <v>-7.6114</v>
+        <v>-8.002800000000001</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.5</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.4535</v>
+        <v>-0.4712</v>
       </c>
       <c r="J214" t="n">
-        <v>-8.6165</v>
+        <v>-8.9528</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.45</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.5004</v>
+        <v>-0.5149</v>
       </c>
       <c r="J215" t="n">
-        <v>-9.5076</v>
+        <v>-9.783099999999999</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.33</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.6169</v>
+        <v>-0.622</v>
       </c>
       <c r="J216" t="n">
-        <v>-11.7211</v>
+        <v>-11.818</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.86</v>
       </c>
       <c r="I217" t="n">
-        <v>1.4963</v>
+        <v>1.495</v>
       </c>
       <c r="J217" t="n">
-        <v>28.4297</v>
+        <v>28.405</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.81</v>
       </c>
       <c r="I218" t="n">
-        <v>1.4405</v>
+        <v>1.436</v>
       </c>
       <c r="J218" t="n">
-        <v>27.3695</v>
+        <v>27.284</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.44</v>
       </c>
       <c r="I219" t="n">
-        <v>1.0122</v>
+        <v>0.9692</v>
       </c>
       <c r="J219" t="n">
-        <v>19.2318</v>
+        <v>18.4148</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.44</v>
       </c>
       <c r="I220" t="n">
-        <v>1.0122</v>
+        <v>0.9692</v>
       </c>
       <c r="J220" t="n">
-        <v>19.2318</v>
+        <v>18.4148</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.24</v>
       </c>
       <c r="I221" t="n">
-        <v>0.5849</v>
+        <v>0.5818</v>
       </c>
       <c r="J221" t="n">
-        <v>11.1131</v>
+        <v>11.0542</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.3</v>
       </c>
       <c r="I222" t="n">
-        <v>0.3964</v>
+        <v>0.4111</v>
       </c>
       <c r="J222" t="n">
-        <v>11.0992</v>
+        <v>11.5108</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.3</v>
       </c>
       <c r="I223" t="n">
-        <v>0.3964</v>
+        <v>0.4111</v>
       </c>
       <c r="J223" t="n">
-        <v>11.0992</v>
+        <v>11.5108</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.22</v>
       </c>
       <c r="I224" t="n">
-        <v>0.3039</v>
+        <v>0.3213</v>
       </c>
       <c r="J224" t="n">
-        <v>8.5092</v>
+        <v>8.9964</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.19</v>
       </c>
       <c r="I225" t="n">
-        <v>0.2682</v>
+        <v>0.2862</v>
       </c>
       <c r="J225" t="n">
-        <v>7.5096</v>
+        <v>8.0136</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.09</v>
       </c>
       <c r="I226" t="n">
-        <v>0.1354</v>
+        <v>0.1539</v>
       </c>
       <c r="J226" t="n">
-        <v>3.7912</v>
+        <v>4.3092</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.24</v>
       </c>
       <c r="I227" t="n">
-        <v>0.4013</v>
+        <v>0.3998</v>
       </c>
       <c r="J227" t="n">
-        <v>11.2364</v>
+        <v>11.1944</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.07</v>
       </c>
       <c r="I228" t="n">
-        <v>0.1472</v>
+        <v>0.1551</v>
       </c>
       <c r="J228" t="n">
-        <v>4.1216</v>
+        <v>4.3428</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.97</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.0475</v>
+        <v>-0.0563</v>
       </c>
       <c r="J229" t="n">
-        <v>-1.33</v>
+        <v>-1.5764</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.82</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2146</v>
+        <v>-0.2291</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.0088</v>
+        <v>-6.4148</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.72</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.313</v>
+        <v>-0.3259</v>
       </c>
       <c r="J231" t="n">
-        <v>-8.763999999999999</v>
+        <v>-9.1252</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>0.93</v>
       </c>
       <c r="I232" t="n">
-        <v>-0.0617</v>
+        <v>-0.0818</v>
       </c>
       <c r="J232" t="n">
-        <v>-1.4808</v>
+        <v>-1.9632</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.88</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.1218</v>
+        <v>-0.1428</v>
       </c>
       <c r="J233" t="n">
-        <v>-2.9232</v>
+        <v>-3.4272</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.72</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.2835</v>
+        <v>-0.303</v>
       </c>
       <c r="J234" t="n">
-        <v>-6.804</v>
+        <v>-7.272</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.67</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.3301</v>
+        <v>-0.3481</v>
       </c>
       <c r="J235" t="n">
-        <v>-7.9224</v>
+        <v>-8.3544</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.5</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.489</v>
+        <v>-0.4989</v>
       </c>
       <c r="J236" t="n">
-        <v>-11.736</v>
+        <v>-11.9736</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.72</v>
       </c>
       <c r="I237" t="n">
-        <v>1.3775</v>
+        <v>1.362</v>
       </c>
       <c r="J237" t="n">
-        <v>33.06</v>
+        <v>32.688</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.33</v>
       </c>
       <c r="I238" t="n">
-        <v>0.8319</v>
+        <v>0.7924</v>
       </c>
       <c r="J238" t="n">
-        <v>19.9656</v>
+        <v>19.0176</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.27</v>
       </c>
       <c r="I239" t="n">
-        <v>0.6982</v>
+        <v>0.6742</v>
       </c>
       <c r="J239" t="n">
-        <v>16.7568</v>
+        <v>16.1808</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.23</v>
       </c>
       <c r="I240" t="n">
-        <v>0.6045</v>
+        <v>0.5908</v>
       </c>
       <c r="J240" t="n">
-        <v>14.508</v>
+        <v>14.1792</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>1.18</v>
       </c>
       <c r="I241" t="n">
-        <v>0.4818</v>
+        <v>0.4808</v>
       </c>
       <c r="J241" t="n">
-        <v>11.5632</v>
+        <v>11.5392</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>2.08</v>
       </c>
       <c r="I242" t="n">
-        <v>1.7132</v>
+        <v>1.7267</v>
       </c>
       <c r="J242" t="n">
-        <v>32.5508</v>
+        <v>32.8073</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.88</v>
       </c>
       <c r="I243" t="n">
-        <v>1.4989</v>
+        <v>1.5012</v>
       </c>
       <c r="J243" t="n">
-        <v>28.4791</v>
+        <v>28.5228</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.63</v>
       </c>
       <c r="I244" t="n">
-        <v>1.2276</v>
+        <v>1.2111</v>
       </c>
       <c r="J244" t="n">
-        <v>23.3244</v>
+        <v>23.0109</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.45</v>
       </c>
       <c r="I245" t="n">
-        <v>1.0105</v>
+        <v>0.971</v>
       </c>
       <c r="J245" t="n">
-        <v>19.1995</v>
+        <v>18.449</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>1.4</v>
       </c>
       <c r="I246" t="n">
-        <v>0.9205</v>
+        <v>0.8822</v>
       </c>
       <c r="J246" t="n">
-        <v>17.4895</v>
+        <v>16.7618</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.07</v>
       </c>
       <c r="I247" t="n">
-        <v>0.6017</v>
+        <v>0.5026</v>
       </c>
       <c r="J247" t="n">
-        <v>11.4323</v>
+        <v>9.5494</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.53</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.4114</v>
+        <v>-0.4342</v>
       </c>
       <c r="J248" t="n">
-        <v>-7.8166</v>
+        <v>-8.2498</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.32</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.6115</v>
+        <v>-0.619</v>
       </c>
       <c r="J249" t="n">
-        <v>-11.6185</v>
+        <v>-11.761</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.3</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.6318</v>
+        <v>-0.6374</v>
       </c>
       <c r="J250" t="n">
-        <v>-12.0042</v>
+        <v>-12.1106</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.13</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.8084</v>
+        <v>-0.7964</v>
       </c>
       <c r="J251" t="n">
-        <v>-15.3596</v>
+        <v>-15.1316</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.88</v>
       </c>
       <c r="I252" t="n">
-        <v>1.5161</v>
+        <v>1.5163</v>
       </c>
       <c r="J252" t="n">
-        <v>25.7737</v>
+        <v>25.7771</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.86</v>
       </c>
       <c r="I253" t="n">
-        <v>1.4939</v>
+        <v>1.4929</v>
       </c>
       <c r="J253" t="n">
-        <v>25.3963</v>
+        <v>25.3793</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.71</v>
       </c>
       <c r="I254" t="n">
-        <v>1.3263</v>
+        <v>1.315</v>
       </c>
       <c r="J254" t="n">
-        <v>22.5471</v>
+        <v>22.355</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.35</v>
       </c>
       <c r="I255" t="n">
-        <v>0.834</v>
+        <v>0.8022</v>
       </c>
       <c r="J255" t="n">
-        <v>14.178</v>
+        <v>13.6374</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>1.06</v>
       </c>
       <c r="I256" t="n">
-        <v>0.1037</v>
+        <v>0.1433</v>
       </c>
       <c r="J256" t="n">
-        <v>1.7629</v>
+        <v>2.4361</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>0.89</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.0566</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="J257" t="n">
-        <v>-0.9622000000000001</v>
+        <v>-1.5113</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.85</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.1064</v>
+        <v>-0.1379</v>
       </c>
       <c r="J258" t="n">
-        <v>-1.8088</v>
+        <v>-2.3443</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.53</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.4338</v>
+        <v>-0.4514</v>
       </c>
       <c r="J259" t="n">
-        <v>-7.3746</v>
+        <v>-7.6738</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.48</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.4807</v>
+        <v>-0.4952</v>
       </c>
       <c r="J260" t="n">
-        <v>-8.171900000000001</v>
+        <v>-8.4184</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.17</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.7802</v>
+        <v>-0.7697000000000001</v>
       </c>
       <c r="J261" t="n">
-        <v>-13.2634</v>
+        <v>-13.0849</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.19</v>
       </c>
       <c r="I262" t="n">
-        <v>0.3297</v>
+        <v>0.3324</v>
       </c>
       <c r="J262" t="n">
-        <v>7.9128</v>
+        <v>7.9776</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.06</v>
       </c>
       <c r="I263" t="n">
-        <v>0.1295</v>
+        <v>0.1375</v>
       </c>
       <c r="J263" t="n">
-        <v>3.108</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.9</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.1307</v>
+        <v>-0.1442</v>
       </c>
       <c r="J264" t="n">
-        <v>-3.1368</v>
+        <v>-3.4608</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.89</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.1417</v>
+        <v>-0.1555</v>
       </c>
       <c r="J265" t="n">
-        <v>-3.4008</v>
+        <v>-3.732</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.8</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.2352</v>
+        <v>-0.2495</v>
       </c>
       <c r="J266" t="n">
-        <v>-5.6448</v>
+        <v>-5.988</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.45</v>
       </c>
       <c r="I267" t="n">
-        <v>0.5667</v>
+        <v>0.5723</v>
       </c>
       <c r="J267" t="n">
-        <v>13.6008</v>
+        <v>13.7352</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.44</v>
       </c>
       <c r="I268" t="n">
-        <v>0.5557</v>
+        <v>0.5619</v>
       </c>
       <c r="J268" t="n">
-        <v>13.3368</v>
+        <v>13.4856</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.21</v>
       </c>
       <c r="I269" t="n">
-        <v>0.2928</v>
+        <v>0.3103</v>
       </c>
       <c r="J269" t="n">
-        <v>7.0272</v>
+        <v>7.4472</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.02</v>
       </c>
       <c r="I270" t="n">
-        <v>0.0226</v>
+        <v>0.0362</v>
       </c>
       <c r="J270" t="n">
-        <v>0.5424</v>
+        <v>0.8688</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.93</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.1218</v>
+        <v>-0.1284</v>
       </c>
       <c r="J271" t="n">
-        <v>-2.9232</v>
+        <v>-3.0816</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.5</v>
       </c>
       <c r="I272" t="n">
-        <v>1.114</v>
+        <v>1.0801</v>
       </c>
       <c r="J272" t="n">
-        <v>26.736</v>
+        <v>25.9224</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.43</v>
       </c>
       <c r="I273" t="n">
-        <v>1.0239</v>
+        <v>0.9759</v>
       </c>
       <c r="J273" t="n">
-        <v>24.5736</v>
+        <v>23.4216</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.35</v>
       </c>
       <c r="I274" t="n">
-        <v>0.8754999999999999</v>
+        <v>0.8306</v>
       </c>
       <c r="J274" t="n">
-        <v>21.012</v>
+        <v>19.9344</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.2</v>
       </c>
       <c r="I275" t="n">
-        <v>0.5343</v>
+        <v>0.5275</v>
       </c>
       <c r="J275" t="n">
-        <v>12.8232</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>1.19</v>
       </c>
       <c r="I276" t="n">
-        <v>0.5095</v>
+        <v>0.5052</v>
       </c>
       <c r="J276" t="n">
-        <v>12.228</v>
+        <v>12.1248</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.26</v>
       </c>
       <c r="I277" t="n">
-        <v>0.673</v>
+        <v>0.6267</v>
       </c>
       <c r="J277" t="n">
-        <v>16.152</v>
+        <v>15.0408</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.83</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.1812</v>
+        <v>-0.2011</v>
       </c>
       <c r="J278" t="n">
-        <v>-4.3488</v>
+        <v>-4.8264</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.76</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.2494</v>
+        <v>-0.2688</v>
       </c>
       <c r="J279" t="n">
-        <v>-5.9856</v>
+        <v>-6.4512</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.62</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3806</v>
+        <v>-0.3959</v>
       </c>
       <c r="J280" t="n">
-        <v>-9.134399999999999</v>
+        <v>-9.5016</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.35</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.6304</v>
+        <v>-0.6302</v>
       </c>
       <c r="J281" t="n">
-        <v>-15.1296</v>
+        <v>-15.1248</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.76</v>
       </c>
       <c r="I282" t="n">
-        <v>1.3871</v>
+        <v>1.3789</v>
       </c>
       <c r="J282" t="n">
-        <v>26.3549</v>
+        <v>26.1991</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.6</v>
       </c>
       <c r="I283" t="n">
-        <v>1.2052</v>
+        <v>1.1843</v>
       </c>
       <c r="J283" t="n">
-        <v>22.8988</v>
+        <v>22.5017</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.56</v>
       </c>
       <c r="I284" t="n">
-        <v>1.1596</v>
+        <v>1.135</v>
       </c>
       <c r="J284" t="n">
-        <v>22.0324</v>
+        <v>21.565</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.42</v>
       </c>
       <c r="I285" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9371</v>
       </c>
       <c r="J285" t="n">
-        <v>18.6656</v>
+        <v>17.8049</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>1.36</v>
       </c>
       <c r="I286" t="n">
-        <v>0.8621</v>
+        <v>0.8256</v>
       </c>
       <c r="J286" t="n">
-        <v>16.3799</v>
+        <v>15.6864</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>0.85</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.1321</v>
+        <v>-0.1582</v>
       </c>
       <c r="J287" t="n">
-        <v>-2.5099</v>
+        <v>-3.0058</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.65</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.3363</v>
+        <v>-0.3565</v>
       </c>
       <c r="J288" t="n">
-        <v>-6.3897</v>
+        <v>-6.7735</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.64</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.345</v>
+        <v>-0.3649</v>
       </c>
       <c r="J289" t="n">
-        <v>-6.555</v>
+        <v>-6.9331</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.64</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.345</v>
+        <v>-0.3649</v>
       </c>
       <c r="J290" t="n">
-        <v>-6.555</v>
+        <v>-6.9331</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.48</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4934</v>
+        <v>-0.5052</v>
       </c>
       <c r="J291" t="n">
-        <v>-9.374599999999999</v>
+        <v>-9.598800000000001</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.81</v>
       </c>
       <c r="I292" t="n">
-        <v>1.485</v>
+        <v>1.4753</v>
       </c>
       <c r="J292" t="n">
-        <v>32.67</v>
+        <v>32.4566</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.42</v>
       </c>
       <c r="I293" t="n">
-        <v>1.0077</v>
+        <v>0.9581</v>
       </c>
       <c r="J293" t="n">
-        <v>22.1694</v>
+        <v>21.0782</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.22</v>
       </c>
       <c r="I294" t="n">
-        <v>0.5817</v>
+        <v>0.5702</v>
       </c>
       <c r="J294" t="n">
-        <v>12.7974</v>
+        <v>12.5444</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.21</v>
       </c>
       <c r="I295" t="n">
-        <v>0.5575</v>
+        <v>0.5485</v>
       </c>
       <c r="J295" t="n">
-        <v>12.265</v>
+        <v>12.067</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.04</v>
       </c>
       <c r="I296" t="n">
-        <v>0.0859</v>
+        <v>0.1146</v>
       </c>
       <c r="J296" t="n">
-        <v>1.8898</v>
+        <v>2.5212</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>0.99</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.0027</v>
+        <v>-0.0115</v>
       </c>
       <c r="J297" t="n">
-        <v>-0.0594</v>
+        <v>-0.253</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.98</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.0189</v>
+        <v>-0.0296</v>
       </c>
       <c r="J298" t="n">
-        <v>-0.4158</v>
+        <v>-0.6512</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.0732</v>
+        <v>-0.0876</v>
       </c>
       <c r="J299" t="n">
-        <v>-1.6104</v>
+        <v>-1.9272</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.86</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.1622</v>
+        <v>-0.1792</v>
       </c>
       <c r="J300" t="n">
-        <v>-3.5684</v>
+        <v>-3.9424</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.51</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4953</v>
+        <v>-0.5024999999999999</v>
       </c>
       <c r="J301" t="n">
-        <v>-10.8966</v>
+        <v>-11.055</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.68</v>
       </c>
       <c r="I302" t="n">
-        <v>1.3141</v>
+        <v>1.2977</v>
       </c>
       <c r="J302" t="n">
-        <v>27.5961</v>
+        <v>27.2517</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.63</v>
       </c>
       <c r="I303" t="n">
-        <v>1.2554</v>
+        <v>1.235</v>
       </c>
       <c r="J303" t="n">
-        <v>26.3634</v>
+        <v>25.935</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.34</v>
       </c>
       <c r="I304" t="n">
-        <v>0.84</v>
+        <v>0.8022</v>
       </c>
       <c r="J304" t="n">
-        <v>17.64</v>
+        <v>16.8462</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.32</v>
       </c>
       <c r="I305" t="n">
-        <v>0.7958</v>
+        <v>0.7633</v>
       </c>
       <c r="J305" t="n">
-        <v>16.7118</v>
+        <v>16.0293</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>1.16</v>
       </c>
       <c r="I306" t="n">
-        <v>0.4133</v>
+        <v>0.4226</v>
       </c>
       <c r="J306" t="n">
-        <v>8.6793</v>
+        <v>8.874599999999999</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.04</v>
       </c>
       <c r="I307" t="n">
-        <v>0.2384</v>
+        <v>0.2143</v>
       </c>
       <c r="J307" t="n">
-        <v>5.0064</v>
+        <v>4.5003</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.79</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.2109</v>
+        <v>-0.2329</v>
       </c>
       <c r="J308" t="n">
-        <v>-4.4289</v>
+        <v>-4.8909</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.59</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.3989</v>
+        <v>-0.4149</v>
       </c>
       <c r="J309" t="n">
-        <v>-8.376899999999999</v>
+        <v>-8.712899999999999</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.55</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.4363</v>
+        <v>-0.4503</v>
       </c>
       <c r="J310" t="n">
-        <v>-9.1623</v>
+        <v>-9.456300000000001</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.54</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4457</v>
+        <v>-0.4591</v>
       </c>
       <c r="J311" t="n">
-        <v>-9.3597</v>
+        <v>-9.6411</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.26</v>
       </c>
       <c r="I312" t="n">
-        <v>0.7288</v>
+        <v>0.6905</v>
       </c>
       <c r="J312" t="n">
-        <v>21.864</v>
+        <v>20.715</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.16</v>
       </c>
       <c r="I313" t="n">
-        <v>0.4798</v>
+        <v>0.4684</v>
       </c>
       <c r="J313" t="n">
-        <v>14.394</v>
+        <v>14.052</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.12</v>
       </c>
       <c r="I314" t="n">
-        <v>0.3754</v>
+        <v>0.3731</v>
       </c>
       <c r="J314" t="n">
-        <v>11.262</v>
+        <v>11.193</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.03</v>
       </c>
       <c r="I315" t="n">
-        <v>0.108</v>
+        <v>0.1205</v>
       </c>
       <c r="J315" t="n">
-        <v>3.24</v>
+        <v>3.615</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.96</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.1925</v>
+        <v>-0.1882</v>
       </c>
       <c r="J316" t="n">
-        <v>-5.775</v>
+        <v>-5.646</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.16</v>
       </c>
       <c r="I317" t="n">
-        <v>0.3721</v>
+        <v>0.37</v>
       </c>
       <c r="J317" t="n">
-        <v>11.163</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.06</v>
       </c>
       <c r="I318" t="n">
-        <v>0.1677</v>
+        <v>0.1744</v>
       </c>
       <c r="J318" t="n">
-        <v>5.031</v>
+        <v>5.232</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.97</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.048</v>
+        <v>-0.0567</v>
       </c>
       <c r="J319" t="n">
-        <v>-1.44</v>
+        <v>-1.701</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.87</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.1639</v>
+        <v>-0.1779</v>
       </c>
       <c r="J320" t="n">
-        <v>-4.917</v>
+        <v>-5.337</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.2259</v>
+        <v>-0.2401</v>
       </c>
       <c r="J321" t="n">
-        <v>-6.777</v>
+        <v>-7.203</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.15</v>
       </c>
       <c r="I322" t="n">
-        <v>0.2724</v>
+        <v>0.2775</v>
       </c>
       <c r="J322" t="n">
-        <v>7.3548</v>
+        <v>7.4925</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.09</v>
       </c>
       <c r="I323" t="n">
-        <v>0.18</v>
+        <v>0.1876</v>
       </c>
       <c r="J323" t="n">
-        <v>4.86</v>
+        <v>5.0652</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.06</v>
       </c>
       <c r="I324" t="n">
-        <v>0.1302</v>
+        <v>0.138</v>
       </c>
       <c r="J324" t="n">
-        <v>3.5154</v>
+        <v>3.726</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.82</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.2146</v>
+        <v>-0.2291</v>
       </c>
       <c r="J325" t="n">
-        <v>-5.7942</v>
+        <v>-6.1857</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.7</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.3321</v>
+        <v>-0.3444</v>
       </c>
       <c r="J326" t="n">
-        <v>-8.966699999999999</v>
+        <v>-9.2988</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.38</v>
       </c>
       <c r="I327" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.5132</v>
       </c>
       <c r="J327" t="n">
-        <v>13.7052</v>
+        <v>13.8564</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.2</v>
       </c>
       <c r="I328" t="n">
-        <v>0.2914</v>
+        <v>0.3064</v>
       </c>
       <c r="J328" t="n">
-        <v>7.8678</v>
+        <v>8.2728</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>1.06</v>
       </c>
       <c r="I329" t="n">
-        <v>0.1033</v>
+        <v>0.1176</v>
       </c>
       <c r="J329" t="n">
-        <v>2.7891</v>
+        <v>3.1752</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.97</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.0612</v>
+        <v>-0.0668</v>
       </c>
       <c r="J330" t="n">
-        <v>-1.6524</v>
+        <v>-1.8036</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.95</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.0951</v>
       </c>
       <c r="J331" t="n">
-        <v>-2.3625</v>
+        <v>-2.5677</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.42</v>
       </c>
       <c r="I332" t="n">
-        <v>1.0364</v>
+        <v>0.9842</v>
       </c>
       <c r="J332" t="n">
-        <v>27.9828</v>
+        <v>26.5734</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.39</v>
       </c>
       <c r="I333" t="n">
-        <v>0.9879</v>
+        <v>0.9303</v>
       </c>
       <c r="J333" t="n">
-        <v>26.6733</v>
+        <v>25.1181</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.23</v>
       </c>
       <c r="I334" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.6086</v>
       </c>
       <c r="J334" t="n">
-        <v>17.0235</v>
+        <v>16.4322</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.14</v>
       </c>
       <c r="I335" t="n">
-        <v>0.4111</v>
+        <v>0.4099</v>
       </c>
       <c r="J335" t="n">
-        <v>11.0997</v>
+        <v>11.0673</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.82</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.6231</v>
+        <v>-0.579</v>
       </c>
       <c r="J336" t="n">
-        <v>-16.8237</v>
+        <v>-15.633</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.21</v>
       </c>
       <c r="I337" t="n">
-        <v>0.4764</v>
+        <v>0.4649</v>
       </c>
       <c r="J337" t="n">
-        <v>12.8628</v>
+        <v>12.5523</v>
       </c>
     </row>
     <row r="338">
@@ -15909,10 +15909,10 @@
         <v>0.97</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.046</v>
+        <v>-0.0552</v>
       </c>
       <c r="J339" t="n">
-        <v>-1.242</v>
+        <v>-1.4904</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.83</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.2022</v>
+        <v>-0.2172</v>
       </c>
       <c r="J340" t="n">
-        <v>-5.4594</v>
+        <v>-5.8644</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.6</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.4234</v>
+        <v>-0.4326</v>
       </c>
       <c r="J341" t="n">
-        <v>-11.4318</v>
+        <v>-11.6802</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.27</v>
       </c>
       <c r="I342" t="n">
-        <v>0.7466</v>
+        <v>0.7073</v>
       </c>
       <c r="J342" t="n">
-        <v>20.9048</v>
+        <v>19.8044</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.24</v>
       </c>
       <c r="I343" t="n">
-        <v>0.6743</v>
+        <v>0.6435</v>
       </c>
       <c r="J343" t="n">
-        <v>18.8804</v>
+        <v>18.018</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.09</v>
       </c>
       <c r="I344" t="n">
-        <v>0.2913</v>
+        <v>0.2957</v>
       </c>
       <c r="J344" t="n">
-        <v>8.1564</v>
+        <v>8.2796</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>1.07</v>
       </c>
       <c r="I345" t="n">
-        <v>0.233</v>
+        <v>0.2412</v>
       </c>
       <c r="J345" t="n">
-        <v>6.524</v>
+        <v>6.7536</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.95</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.2307</v>
+        <v>-0.2235</v>
       </c>
       <c r="J346" t="n">
-        <v>-6.4596</v>
+        <v>-6.258</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.2</v>
       </c>
       <c r="I347" t="n">
-        <v>0.4554</v>
+        <v>0.446</v>
       </c>
       <c r="J347" t="n">
-        <v>12.7512</v>
+        <v>12.488</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>1.06</v>
       </c>
       <c r="I348" t="n">
-        <v>0.1734</v>
+        <v>0.1785</v>
       </c>
       <c r="J348" t="n">
-        <v>4.8552</v>
+        <v>4.998</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.08359999999999999</v>
+        <v>-0.0956</v>
       </c>
       <c r="J349" t="n">
-        <v>-2.3408</v>
+        <v>-2.6768</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.82</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.2131</v>
+        <v>-0.2279</v>
       </c>
       <c r="J350" t="n">
-        <v>-5.9668</v>
+        <v>-6.3812</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.74</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.2923</v>
+        <v>-0.306</v>
       </c>
       <c r="J351" t="n">
-        <v>-8.1844</v>
+        <v>-8.568</v>
       </c>
     </row>
     <row r="352">
@@ -16429,10 +16429,10 @@
         <v>1.79</v>
       </c>
       <c r="I352" t="n">
-        <v>1.4519</v>
+        <v>1.442</v>
       </c>
       <c r="J352" t="n">
-        <v>31.9418</v>
+        <v>31.724</v>
       </c>
     </row>
     <row r="353">
@@ -16469,10 +16469,10 @@
         <v>1.57</v>
       </c>
       <c r="I353" t="n">
-        <v>1.1916</v>
+        <v>1.1652</v>
       </c>
       <c r="J353" t="n">
-        <v>26.2152</v>
+        <v>25.6344</v>
       </c>
     </row>
     <row r="354">
@@ -16509,10 +16509,10 @@
         <v>1.26</v>
       </c>
       <c r="I354" t="n">
-        <v>0.6683</v>
+        <v>0.6489</v>
       </c>
       <c r="J354" t="n">
-        <v>14.7026</v>
+        <v>14.2758</v>
       </c>
     </row>
     <row r="355">
@@ -16549,10 +16549,10 @@
         <v>1.25</v>
       </c>
       <c r="I355" t="n">
-        <v>0.6448</v>
+        <v>0.6281</v>
       </c>
       <c r="J355" t="n">
-        <v>14.1856</v>
+        <v>13.8182</v>
       </c>
     </row>
     <row r="356">
@@ -16589,10 +16589,10 @@
         <v>1.03</v>
       </c>
       <c r="I356" t="n">
-        <v>0.0423</v>
+        <v>0.0747</v>
       </c>
       <c r="J356" t="n">
-        <v>0.9306</v>
+        <v>1.6434</v>
       </c>
     </row>
     <row r="357">
@@ -16629,10 +16629,10 @@
         <v>1</v>
       </c>
       <c r="I357" t="n">
-        <v>0.0822</v>
+        <v>0.06</v>
       </c>
       <c r="J357" t="n">
-        <v>1.8084</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="358">
@@ -16669,10 +16669,10 @@
         <v>0.86</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.146</v>
+        <v>-0.1667</v>
       </c>
       <c r="J358" t="n">
-        <v>-3.212</v>
+        <v>-3.6674</v>
       </c>
     </row>
     <row r="359">
@@ -16709,10 +16709,10 @@
         <v>0.76</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.2481</v>
+        <v>-0.2678</v>
       </c>
       <c r="J359" t="n">
-        <v>-5.4582</v>
+        <v>-5.8916</v>
       </c>
     </row>
     <row r="360">
@@ -16749,10 +16749,10 @@
         <v>0.66</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.3407</v>
+        <v>-0.3581</v>
       </c>
       <c r="J360" t="n">
-        <v>-7.4954</v>
+        <v>-7.8782</v>
       </c>
     </row>
     <row r="361">
@@ -16789,10 +16789,10 @@
         <v>0.46</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.5272</v>
+        <v>-0.5346</v>
       </c>
       <c r="J361" t="n">
-        <v>-11.5984</v>
+        <v>-11.7612</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2150/event_2150_evp_summary.xlsx
+++ b/database/event/2150/event_2150_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.051</v>
+        <v>7.9894</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0006</v>
+        <v>0.993</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0408</v>
+        <v>3.0338</v>
       </c>
       <c r="E2" t="n">
-        <v>8.051</v>
+        <v>7.9894</v>
       </c>
       <c r="F2" t="n">
-        <v>2.924</v>
+        <v>2.8944</v>
       </c>
       <c r="G2" t="n">
-        <v>5.127</v>
+        <v>5.095</v>
       </c>
       <c r="H2" t="n">
-        <v>4.7532</v>
+        <v>4.4243</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5667</v>
+        <v>2.4841</v>
       </c>
       <c r="J2" t="n">
-        <v>5.127</v>
+        <v>5.095</v>
       </c>
       <c r="K2" t="n">
         <v>136</v>
@@ -529,7 +529,7 @@
         <v>230</v>
       </c>
       <c r="M2" t="n">
-        <v>7.6937</v>
+        <v>7.5791</v>
       </c>
       <c r="N2" t="n">
         <v>366</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.3493</v>
+        <v>7.3354</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9134</v>
+        <v>0.9117</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7213</v>
+        <v>2.7358</v>
       </c>
       <c r="E3" t="n">
-        <v>7.3493</v>
+        <v>7.3354</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0454</v>
+        <v>3.069</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3039</v>
+        <v>4.2664</v>
       </c>
       <c r="H3" t="n">
-        <v>5.1536</v>
+        <v>5.0797</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7829</v>
+        <v>2.8521</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3039</v>
+        <v>4.2664</v>
       </c>
       <c r="K3" t="n">
         <v>136</v>
@@ -575,7 +575,7 @@
         <v>230</v>
       </c>
       <c r="M3" t="n">
-        <v>7.0868</v>
+        <v>7.1185</v>
       </c>
       <c r="N3" t="n">
         <v>366</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.6531</v>
+        <v>6.4514</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8269</v>
+        <v>0.8018</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4044</v>
+        <v>2.3331</v>
       </c>
       <c r="E4" t="n">
-        <v>6.6531</v>
+        <v>6.4514</v>
       </c>
       <c r="F4" t="n">
-        <v>3.9091</v>
+        <v>3.8132</v>
       </c>
       <c r="G4" t="n">
-        <v>2.744</v>
+        <v>2.6382</v>
       </c>
       <c r="H4" t="n">
-        <v>8.003500000000001</v>
+        <v>7.8738</v>
       </c>
       <c r="I4" t="n">
-        <v>4.3218</v>
+        <v>4.4209</v>
       </c>
       <c r="J4" t="n">
-        <v>2.744</v>
+        <v>2.6382</v>
       </c>
       <c r="K4" t="n">
         <v>132</v>
@@ -621,7 +621,7 @@
         <v>181</v>
       </c>
       <c r="M4" t="n">
-        <v>7.065799999999999</v>
+        <v>7.059099999999999</v>
       </c>
       <c r="N4" t="n">
         <v>313</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.2381</v>
+        <v>6.1213</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7753</v>
+        <v>0.7608</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2155</v>
+        <v>2.1828</v>
       </c>
       <c r="E5" t="n">
-        <v>6.2381</v>
+        <v>6.1213</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6449</v>
+        <v>2.6489</v>
       </c>
       <c r="G5" t="n">
-        <v>3.5932</v>
+        <v>3.4724</v>
       </c>
       <c r="H5" t="n">
-        <v>3.8323</v>
+        <v>3.5024</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0694</v>
+        <v>1.9665</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5932</v>
+        <v>3.4724</v>
       </c>
       <c r="K5" t="n">
         <v>132</v>
@@ -667,7 +667,7 @@
         <v>181</v>
       </c>
       <c r="M5" t="n">
-        <v>5.662599999999999</v>
+        <v>5.4389</v>
       </c>
       <c r="N5" t="n">
         <v>313</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.8044</v>
+        <v>5.5423</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7214</v>
+        <v>0.6888</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0181</v>
+        <v>1.919</v>
       </c>
       <c r="E6" t="n">
-        <v>5.8044</v>
+        <v>5.5423</v>
       </c>
       <c r="F6" t="n">
-        <v>4.1747</v>
+        <v>4.0443</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6297</v>
+        <v>1.498</v>
       </c>
       <c r="H6" t="n">
-        <v>8.879799999999999</v>
+        <v>8.7415</v>
       </c>
       <c r="I6" t="n">
-        <v>4.795</v>
+        <v>4.9081</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6297</v>
+        <v>1.498</v>
       </c>
       <c r="K6" t="n">
         <v>132</v>
@@ -713,7 +713,7 @@
         <v>181</v>
       </c>
       <c r="M6" t="n">
-        <v>6.4247</v>
+        <v>6.4061</v>
       </c>
       <c r="N6" t="n">
         <v>313</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.4158</v>
+        <v>4.2945</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5488</v>
+        <v>0.5338000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>1.386</v>
+        <v>1.3506</v>
       </c>
       <c r="E7" t="n">
-        <v>4.4158</v>
+        <v>4.2945</v>
       </c>
       <c r="F7" t="n">
-        <v>3.1914</v>
+        <v>3.1537</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2244</v>
+        <v>1.1408</v>
       </c>
       <c r="H7" t="n">
-        <v>5.6353</v>
+        <v>5.3978</v>
       </c>
       <c r="I7" t="n">
-        <v>3.043</v>
+        <v>3.0307</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2244</v>
+        <v>1.1408</v>
       </c>
       <c r="K7" t="n">
         <v>132</v>
@@ -759,7 +759,7 @@
         <v>181</v>
       </c>
       <c r="M7" t="n">
-        <v>4.2674</v>
+        <v>4.1715</v>
       </c>
       <c r="N7" t="n">
         <v>313</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.2984</v>
+        <v>4.1823</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5342</v>
+        <v>0.5198</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3325</v>
+        <v>1.2994</v>
       </c>
       <c r="E8" t="n">
-        <v>4.2984</v>
+        <v>4.1823</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0176</v>
+        <v>0.857</v>
       </c>
       <c r="G8" t="n">
-        <v>3.2808</v>
+        <v>3.3253</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0176</v>
+        <v>0.857</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5495</v>
+        <v>0.4812</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2808</v>
+        <v>3.3253</v>
       </c>
       <c r="K8" t="n">
         <v>136</v>
@@ -805,7 +805,7 @@
         <v>230</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8303</v>
+        <v>3.8065</v>
       </c>
       <c r="N8" t="n">
         <v>366</v>
@@ -814,139 +814,139 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>Friis</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.1819</v>
+        <v>4.0644</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5198</v>
+        <v>0.5052</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2795</v>
+        <v>1.2457</v>
       </c>
       <c r="E9" t="n">
-        <v>4.1819</v>
+        <v>4.0644</v>
       </c>
       <c r="F9" t="n">
-        <v>3.9011</v>
+        <v>3.0997</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2808</v>
+        <v>0.9647</v>
       </c>
       <c r="H9" t="n">
-        <v>7.9772</v>
+        <v>5.1949</v>
       </c>
       <c r="I9" t="n">
-        <v>4.3076</v>
+        <v>2.9168</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2808</v>
+        <v>0.9647</v>
       </c>
       <c r="K9" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="L9" t="n">
-        <v>75</v>
+        <v>181</v>
       </c>
       <c r="M9" t="n">
-        <v>4.5884</v>
+        <v>3.8815</v>
       </c>
       <c r="N9" t="n">
-        <v>199</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.1404</v>
+        <v>4.0544</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.5039</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2606</v>
+        <v>1.2412</v>
       </c>
       <c r="E10" t="n">
-        <v>4.1404</v>
+        <v>4.0544</v>
       </c>
       <c r="F10" t="n">
-        <v>3.1477</v>
+        <v>3.7774</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9927</v>
+        <v>0.277</v>
       </c>
       <c r="H10" t="n">
-        <v>5.4912</v>
+        <v>7.7393</v>
       </c>
       <c r="I10" t="n">
-        <v>2.9652</v>
+        <v>4.3454</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9927</v>
+        <v>0.277</v>
       </c>
       <c r="K10" t="n">
-        <v>187</v>
+        <v>124</v>
       </c>
       <c r="L10" t="n">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="M10" t="n">
-        <v>3.9579</v>
+        <v>4.6224</v>
       </c>
       <c r="N10" t="n">
-        <v>311</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Friis</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.091</v>
+        <v>3.9784</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5085</v>
+        <v>0.4945</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2381</v>
+        <v>1.2066</v>
       </c>
       <c r="E11" t="n">
-        <v>4.091</v>
+        <v>3.9784</v>
       </c>
       <c r="F11" t="n">
-        <v>3.1221</v>
+        <v>3.0984</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9689</v>
+        <v>0.88</v>
       </c>
       <c r="H11" t="n">
-        <v>5.4069</v>
+        <v>5.19</v>
       </c>
       <c r="I11" t="n">
-        <v>2.9197</v>
+        <v>2.914</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9689</v>
+        <v>0.88</v>
       </c>
       <c r="K11" t="n">
-        <v>132</v>
+        <v>187</v>
       </c>
       <c r="L11" t="n">
-        <v>181</v>
+        <v>124</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8886</v>
+        <v>3.794</v>
       </c>
       <c r="N11" t="n">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.8611</v>
+        <v>3.6994</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4799</v>
+        <v>0.4598</v>
       </c>
       <c r="D12" t="n">
-        <v>1.1334</v>
+        <v>1.0795</v>
       </c>
       <c r="E12" t="n">
-        <v>3.8611</v>
+        <v>3.6994</v>
       </c>
       <c r="F12" t="n">
-        <v>3.7429</v>
+        <v>3.6366</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1182</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>7.4549</v>
+        <v>7.2109</v>
       </c>
       <c r="I12" t="n">
-        <v>4.0256</v>
+        <v>4.0487</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1182</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="K12" t="n">
         <v>187</v>
@@ -989,7 +989,7 @@
         <v>124</v>
       </c>
       <c r="M12" t="n">
-        <v>4.1438</v>
+        <v>4.1115</v>
       </c>
       <c r="N12" t="n">
         <v>311</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.8169</v>
+        <v>3.6468</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4744</v>
+        <v>0.4533</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1133</v>
+        <v>1.0555</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8169</v>
+        <v>3.6468</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0057</v>
+        <v>2.9413</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8112</v>
+        <v>0.7055</v>
       </c>
       <c r="H13" t="n">
-        <v>5.0227</v>
+        <v>4.6003</v>
       </c>
       <c r="I13" t="n">
-        <v>2.7122</v>
+        <v>2.5829</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8112</v>
+        <v>0.7055</v>
       </c>
       <c r="K13" t="n">
         <v>187</v>
@@ -1035,7 +1035,7 @@
         <v>124</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5234</v>
+        <v>3.2884</v>
       </c>
       <c r="N13" t="n">
         <v>311</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.5324</v>
+        <v>3.4772</v>
       </c>
       <c r="C14" t="n">
-        <v>0.439</v>
+        <v>0.4322</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9838</v>
+        <v>0.9782</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5324</v>
+        <v>3.4772</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1611</v>
+        <v>2.1016</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3713</v>
+        <v>1.3756</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2361</v>
+        <v>2.1016</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2075</v>
+        <v>1.18</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3713</v>
+        <v>1.3756</v>
       </c>
       <c r="K14" t="n">
         <v>136</v>
@@ -1081,7 +1081,7 @@
         <v>230</v>
       </c>
       <c r="M14" t="n">
-        <v>2.5788</v>
+        <v>2.5556</v>
       </c>
       <c r="N14" t="n">
         <v>366</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5664</v>
+        <v>2.5099</v>
       </c>
       <c r="C15" t="n">
-        <v>0.319</v>
+        <v>0.312</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5441</v>
+        <v>0.5376</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5664</v>
+        <v>2.5099</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5664</v>
+        <v>2.5099</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8921</v>
+        <v>2.8019</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8921</v>
+        <v>2.8019</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.8921</v>
+        <v>2.8019</v>
       </c>
       <c r="N15" t="n">
         <v>175</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.3593</v>
+        <v>2.3578</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2932</v>
+        <v>0.293</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4498</v>
+        <v>0.4683</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3593</v>
+        <v>2.3578</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3593</v>
+        <v>2.3578</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4389</v>
+        <v>2.4532</v>
       </c>
       <c r="I16" t="n">
-        <v>2.4389</v>
+        <v>2.4532</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.4389</v>
+        <v>2.4532</v>
       </c>
       <c r="N16" t="n">
         <v>184</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.2908</v>
+        <v>2.3009</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2847</v>
+        <v>0.286</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4186</v>
+        <v>0.4424</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2908</v>
+        <v>2.3009</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7316</v>
+        <v>2.7698</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4408</v>
+        <v>-0.4689</v>
       </c>
       <c r="H17" t="n">
-        <v>4.1182</v>
+        <v>3.9566</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2238</v>
+        <v>2.2215</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4408</v>
+        <v>-0.4689</v>
       </c>
       <c r="K17" t="n">
         <v>124</v>
@@ -1219,7 +1219,7 @@
         <v>75</v>
       </c>
       <c r="M17" t="n">
-        <v>1.783</v>
+        <v>1.7526</v>
       </c>
       <c r="N17" t="n">
         <v>199</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.1068</v>
+        <v>2.1462</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2619</v>
+        <v>0.2667</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3349</v>
+        <v>0.3719</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1068</v>
+        <v>2.1462</v>
       </c>
       <c r="F18" t="n">
-        <v>2.8775</v>
+        <v>2.8789</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.7327</v>
       </c>
       <c r="H18" t="n">
-        <v>4.5997</v>
+        <v>4.3659</v>
       </c>
       <c r="I18" t="n">
-        <v>2.4838</v>
+        <v>2.4513</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.7327</v>
       </c>
       <c r="K18" t="n">
         <v>124</v>
@@ -1265,7 +1265,7 @@
         <v>75</v>
       </c>
       <c r="M18" t="n">
-        <v>1.7131</v>
+        <v>1.7186</v>
       </c>
       <c r="N18" t="n">
         <v>199</v>
@@ -1274,47 +1274,47 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.0603</v>
+        <v>2.0152</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2561</v>
+        <v>0.2505</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3137</v>
+        <v>0.3122</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0603</v>
+        <v>2.0152</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4863</v>
+        <v>2.0152</v>
       </c>
       <c r="G19" t="n">
-        <v>0.574</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4863</v>
+        <v>2.0152</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8026</v>
+        <v>2.0152</v>
       </c>
       <c r="J19" t="n">
-        <v>0.574</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="L19" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3766</v>
+        <v>2.0152</v>
       </c>
       <c r="N19" t="n">
-        <v>311</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.0464</v>
+        <v>2.0074</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2543</v>
+        <v>0.2495</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3074</v>
+        <v>0.3087</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0464</v>
+        <v>2.0074</v>
       </c>
       <c r="F20" t="n">
-        <v>3.0464</v>
+        <v>3.0074</v>
       </c>
       <c r="G20" t="n">
         <v>-1</v>
       </c>
       <c r="H20" t="n">
-        <v>5.1571</v>
+        <v>4.8484</v>
       </c>
       <c r="I20" t="n">
-        <v>2.7848</v>
+        <v>2.7222</v>
       </c>
       <c r="J20" t="n">
         <v>-1</v>
@@ -1357,7 +1357,7 @@
         <v>75</v>
       </c>
       <c r="M20" t="n">
-        <v>1.7848</v>
+        <v>1.7222</v>
       </c>
       <c r="N20" t="n">
         <v>199</v>
@@ -1366,216 +1366,216 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>Zero</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.0275</v>
+        <v>1.9898</v>
       </c>
       <c r="C21" t="n">
-        <v>0.252</v>
+        <v>0.2473</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2988</v>
+        <v>0.3007</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0275</v>
+        <v>1.9898</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0275</v>
+        <v>2.172</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.1822</v>
       </c>
       <c r="H21" t="n">
-        <v>2.0275</v>
+        <v>2.172</v>
       </c>
       <c r="I21" t="n">
-        <v>2.0275</v>
+        <v>1.2195</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.1822</v>
       </c>
       <c r="K21" t="n">
-        <v>184</v>
+        <v>124</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M21" t="n">
-        <v>2.0275</v>
+        <v>1.0373</v>
       </c>
       <c r="N21" t="n">
-        <v>184</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.0243</v>
+        <v>1.8201</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2516</v>
+        <v>0.2262</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2973</v>
+        <v>0.2234</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0243</v>
+        <v>1.8201</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1821</v>
+        <v>1.3472</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1578</v>
+        <v>0.4729</v>
       </c>
       <c r="H22" t="n">
-        <v>2.3052</v>
+        <v>1.3472</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2448</v>
+        <v>0.7564</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1578</v>
+        <v>0.4729</v>
       </c>
       <c r="K22" t="n">
+        <v>187</v>
+      </c>
+      <c r="L22" t="n">
         <v>124</v>
       </c>
-      <c r="L22" t="n">
-        <v>75</v>
-      </c>
       <c r="M22" t="n">
-        <v>1.087</v>
+        <v>1.2293</v>
       </c>
       <c r="N22" t="n">
-        <v>199</v>
+        <v>311</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TENZKI</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.8034</v>
+        <v>1.719</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2241</v>
+        <v>0.2137</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1967</v>
+        <v>0.1773</v>
       </c>
       <c r="E23" t="n">
-        <v>1.8034</v>
+        <v>1.719</v>
       </c>
       <c r="F23" t="n">
-        <v>1.8034</v>
+        <v>1.719</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.8034</v>
+        <v>1.719</v>
       </c>
       <c r="I23" t="n">
-        <v>1.8034</v>
+        <v>1.719</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.8034</v>
+        <v>1.719</v>
       </c>
       <c r="N23" t="n">
-        <v>175</v>
+        <v>184</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>TENZKI</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.7329</v>
+        <v>1.6621</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2154</v>
+        <v>0.2066</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1646</v>
+        <v>0.1514</v>
       </c>
       <c r="E24" t="n">
-        <v>1.7329</v>
+        <v>1.6621</v>
       </c>
       <c r="F24" t="n">
-        <v>1.7329</v>
+        <v>1.6621</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.7329</v>
+        <v>1.6621</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7329</v>
+        <v>1.6621</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.7329</v>
+        <v>1.6621</v>
       </c>
       <c r="N24" t="n">
-        <v>184</v>
+        <v>175</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>RUBINO</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.6434</v>
+        <v>1.6107</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2043</v>
+        <v>0.2002</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1239</v>
+        <v>0.128</v>
       </c>
       <c r="E25" t="n">
-        <v>1.6434</v>
+        <v>1.6107</v>
       </c>
       <c r="F25" t="n">
-        <v>1.6434</v>
+        <v>1.6107</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.6434</v>
+        <v>1.6107</v>
       </c>
       <c r="I25" t="n">
-        <v>1.6434</v>
+        <v>1.6107</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.6434</v>
+        <v>1.6107</v>
       </c>
       <c r="N25" t="n">
         <v>175</v>
@@ -1596,32 +1596,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RUBINO</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.632</v>
+        <v>1.5415</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2028</v>
+        <v>0.1916</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1187</v>
+        <v>0.0964</v>
       </c>
       <c r="E26" t="n">
-        <v>1.632</v>
+        <v>1.5415</v>
       </c>
       <c r="F26" t="n">
-        <v>1.632</v>
+        <v>1.5415</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.632</v>
+        <v>1.5415</v>
       </c>
       <c r="I26" t="n">
-        <v>1.632</v>
+        <v>1.5415</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.632</v>
+        <v>1.5415</v>
       </c>
       <c r="N26" t="n">
         <v>175</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.5439</v>
+        <v>1.428</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1919</v>
+        <v>0.1775</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0786</v>
+        <v>0.0447</v>
       </c>
       <c r="E27" t="n">
-        <v>1.5439</v>
+        <v>1.428</v>
       </c>
       <c r="F27" t="n">
-        <v>3.4015</v>
+        <v>3.3092</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.8576</v>
+        <v>-1.8812</v>
       </c>
       <c r="H27" t="n">
-        <v>6.3286</v>
+        <v>5.9815</v>
       </c>
       <c r="I27" t="n">
-        <v>3.4174</v>
+        <v>3.3584</v>
       </c>
       <c r="J27" t="n">
-        <v>-1.8576</v>
+        <v>-1.8812</v>
       </c>
       <c r="K27" t="n">
         <v>136</v>
@@ -1679,7 +1679,7 @@
         <v>230</v>
       </c>
       <c r="M27" t="n">
-        <v>1.5598</v>
+        <v>1.4772</v>
       </c>
       <c r="N27" t="n">
         <v>366</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.1037</v>
+        <v>0.9907</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1372</v>
+        <v>0.1231</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1218</v>
+        <v>-0.1545</v>
       </c>
       <c r="E28" t="n">
-        <v>1.1037</v>
+        <v>0.9907</v>
       </c>
       <c r="F28" t="n">
-        <v>1.1037</v>
+        <v>0.9907</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.1037</v>
+        <v>0.9907</v>
       </c>
       <c r="I28" t="n">
-        <v>1.1037</v>
+        <v>0.9907</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1037</v>
+        <v>0.9907</v>
       </c>
       <c r="N28" t="n">
         <v>184</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.0065</v>
+        <v>0.8687</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1251</v>
+        <v>0.108</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.166</v>
+        <v>-0.2101</v>
       </c>
       <c r="E29" t="n">
-        <v>1.0065</v>
+        <v>0.8687</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9154</v>
+        <v>0.7755</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0911</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9154</v>
+        <v>0.7755</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4943</v>
+        <v>0.4354</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0911</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="K29" t="n">
         <v>187</v>
@@ -1771,7 +1771,7 @@
         <v>124</v>
       </c>
       <c r="M29" t="n">
-        <v>0.5854</v>
+        <v>0.5286</v>
       </c>
       <c r="N29" t="n">
         <v>311</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9548</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1187</v>
+        <v>0.0979</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1896</v>
+        <v>-0.2469</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9548</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9548</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9548</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>0.9548</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.9548</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="N30" t="n">
         <v>155</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0221</v>
+        <v>-0.1006</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0027</v>
+        <v>-0.0125</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6141</v>
+        <v>-0.6516</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0221</v>
+        <v>-0.1006</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0221</v>
+        <v>-0.1006</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0221</v>
+        <v>-0.1006</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0221</v>
+        <v>-0.1006</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0221</v>
+        <v>-0.1006</v>
       </c>
       <c r="N31" t="n">
         <v>155</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1125</v>
+        <v>-0.1034</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.014</v>
+        <v>-0.0129</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6754</v>
+        <v>-0.6529</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1125</v>
+        <v>-0.1034</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1125</v>
+        <v>-0.1034</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.1125</v>
+        <v>-0.1034</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.1125</v>
+        <v>-0.1034</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.1125</v>
+        <v>-0.1034</v>
       </c>
       <c r="N32" t="n">
         <v>184</v>
@@ -1918,93 +1918,93 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Professor_Chaos</t>
+          <t>MAiNLiNE</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4461</v>
+        <v>-0.3712</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0554</v>
+        <v>-0.0461</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8273</v>
+        <v>-0.7749</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4461</v>
+        <v>-0.3712</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4461</v>
+        <v>-0.3712</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4461</v>
+        <v>-0.3712</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4461</v>
+        <v>-0.3712</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>155</v>
+        <v>79</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4461</v>
+        <v>-0.3712</v>
       </c>
       <c r="N33" t="n">
-        <v>155</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MAiNLiNE</t>
+          <t>Professor_Chaos</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4544</v>
+        <v>-0.5034999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0565</v>
+        <v>-0.0626</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8310999999999999</v>
+        <v>-0.8352000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4544</v>
+        <v>-0.5034999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4544</v>
+        <v>-0.5034999999999999</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4544</v>
+        <v>-0.5034999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4544</v>
+        <v>-0.5034999999999999</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>79</v>
+        <v>155</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4544</v>
+        <v>-0.5034999999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>79</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.5659</v>
+        <v>-0.6418</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0703</v>
+        <v>-0.0798</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8818</v>
+        <v>-0.8982</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5659</v>
+        <v>-0.6418</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.5659</v>
+        <v>-0.6418</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.5659</v>
+        <v>-0.6418</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5659</v>
+        <v>-0.6418</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.5659</v>
+        <v>-0.6418</v>
       </c>
       <c r="N35" t="n">
         <v>155</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.6172</v>
+        <v>-0.668</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0767</v>
+        <v>-0.083</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9052</v>
+        <v>-0.9101</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6172</v>
+        <v>-0.668</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.6172</v>
+        <v>-0.668</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.6172</v>
+        <v>-0.668</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6172</v>
+        <v>-0.668</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.6172</v>
+        <v>-0.668</v>
       </c>
       <c r="N36" t="n">
         <v>175</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9746</v>
+        <v>-0.9728</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1211</v>
+        <v>-0.1209</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0679</v>
+        <v>-1.0489</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9746</v>
+        <v>-0.9728</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9746</v>
+        <v>-0.9728</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9746</v>
+        <v>-0.9728</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9746</v>
+        <v>-0.9728</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9746</v>
+        <v>-0.9728</v>
       </c>
       <c r="N37" t="n">
         <v>155</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.1478</v>
+        <v>-1.1519</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1427</v>
+        <v>-0.1432</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1467</v>
+        <v>-1.1305</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.1478</v>
+        <v>-1.1519</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.1478</v>
+        <v>-1.1519</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.1478</v>
+        <v>-1.1519</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.1478</v>
+        <v>-1.1519</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.1478</v>
+        <v>-1.1519</v>
       </c>
       <c r="N38" t="n">
         <v>79</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2104</v>
+        <v>-1.1633</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1504</v>
+        <v>-0.1446</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1752</v>
+        <v>-1.1357</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2104</v>
+        <v>-1.1633</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.2104</v>
+        <v>-1.1633</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.2104</v>
+        <v>-1.1633</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.2104</v>
+        <v>-1.1633</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.2104</v>
+        <v>-1.1633</v>
       </c>
       <c r="N39" t="n">
         <v>79</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.2882</v>
+        <v>-1.314</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1601</v>
+        <v>-0.1633</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2106</v>
+        <v>-1.2044</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.2882</v>
+        <v>-1.314</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.2882</v>
+        <v>-1.314</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.2882</v>
+        <v>-1.314</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.2882</v>
+        <v>-1.314</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.2882</v>
+        <v>-1.314</v>
       </c>
       <c r="N40" t="n">
         <v>79</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.5025</v>
+        <v>-1.4794</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.1867</v>
+        <v>-0.1839</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3082</v>
+        <v>-1.2797</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.5025</v>
+        <v>-1.4794</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.5025</v>
+        <v>-1.4794</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.5025</v>
+        <v>-1.4794</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.5025</v>
+        <v>-1.4794</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.5025</v>
+        <v>-1.4794</v>
       </c>
       <c r="N41" t="n">
         <v>79</v>
@@ -2429,10 +2429,10 @@
         <v>0.85</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1597</v>
+        <v>-0.1429</v>
       </c>
       <c r="J2" t="n">
-        <v>-3.3537</v>
+        <v>-3.0009</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.8</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2143</v>
+        <v>-0.1993</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.5003</v>
+        <v>-4.1853</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.78</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2352</v>
+        <v>-0.2208</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.9392</v>
+        <v>-4.6368</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.47</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5148</v>
+        <v>-0.5147</v>
       </c>
       <c r="J5" t="n">
-        <v>-10.8108</v>
+        <v>-10.8087</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.39</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5848</v>
+        <v>-0.5944</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.2808</v>
+        <v>-12.4824</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.69</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4147</v>
+        <v>1.4514</v>
       </c>
       <c r="J7" t="n">
-        <v>29.7087</v>
+        <v>30.4794</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.67</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3816</v>
+        <v>1.418</v>
       </c>
       <c r="J8" t="n">
-        <v>29.0136</v>
+        <v>29.778</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.41</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9316</v>
+        <v>0.9274</v>
       </c>
       <c r="J9" t="n">
-        <v>19.5636</v>
+        <v>19.4754</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.36</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8389</v>
+        <v>0.8282</v>
       </c>
       <c r="J10" t="n">
-        <v>17.6169</v>
+        <v>17.3922</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.06</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1617</v>
+        <v>0.1318</v>
       </c>
       <c r="J11" t="n">
-        <v>3.3957</v>
+        <v>2.7678</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.32</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>22.2624</v>
+        <v>20.124</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.27</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5399</v>
+        <v>0.4803</v>
       </c>
       <c r="J13" t="n">
-        <v>19.4364</v>
+        <v>17.2908</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.08</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2067</v>
+        <v>0.166</v>
       </c>
       <c r="J14" t="n">
-        <v>7.4412</v>
+        <v>5.976</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.79</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2657</v>
+        <v>-0.2464</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.565200000000001</v>
+        <v>-8.8704</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.73</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3232</v>
+        <v>-0.3069</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.6352</v>
+        <v>-11.0484</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.47</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1344</v>
+        <v>1.1452</v>
       </c>
       <c r="J17" t="n">
-        <v>40.8384</v>
+        <v>41.2272</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.18</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5264</v>
+        <v>0.4856</v>
       </c>
       <c r="J18" t="n">
-        <v>18.9504</v>
+        <v>17.4816</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.15</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4556</v>
+        <v>0.4139</v>
       </c>
       <c r="J19" t="n">
-        <v>16.4016</v>
+        <v>14.9004</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.96</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1781</v>
+        <v>-0.1445</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.4116</v>
+        <v>-5.202</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.5</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2253</v>
+        <v>-1.2555</v>
       </c>
       <c r="J21" t="n">
-        <v>-44.1108</v>
+        <v>-45.198</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.38</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4911</v>
+        <v>0.4249</v>
       </c>
       <c r="J22" t="n">
-        <v>12.2775</v>
+        <v>10.6225</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.36</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4701</v>
+        <v>0.4052</v>
       </c>
       <c r="J23" t="n">
-        <v>11.7525</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.32</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4277</v>
+        <v>0.3657</v>
       </c>
       <c r="J24" t="n">
-        <v>10.6925</v>
+        <v>9.1425</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.31</v>
       </c>
       <c r="I25" t="n">
-        <v>0.417</v>
+        <v>0.3558</v>
       </c>
       <c r="J25" t="n">
-        <v>10.425</v>
+        <v>8.895</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.03</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0497</v>
+        <v>0.0337</v>
       </c>
       <c r="J26" t="n">
-        <v>1.2425</v>
+        <v>0.8425</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>0.95</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.07480000000000001</v>
+        <v>-0.0626</v>
       </c>
       <c r="J27" t="n">
-        <v>-1.87</v>
+        <v>-1.565</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0881</v>
+        <v>-0.07480000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>-2.2025</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.92</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1131</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>-2.8275</v>
+        <v>-2.4525</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.83</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2094</v>
+        <v>-0.1905</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.235</v>
+        <v>-4.7625</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.66</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3707</v>
+        <v>-0.3569</v>
       </c>
       <c r="J31" t="n">
-        <v>-9.2675</v>
+        <v>-8.922499999999999</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.47</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8791</v>
+        <v>0.8379</v>
       </c>
       <c r="J32" t="n">
-        <v>21.0984</v>
+        <v>20.1096</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.99</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0212</v>
+        <v>-0.0157</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.5088</v>
+        <v>-0.3768</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.8</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2466</v>
+        <v>-0.2267</v>
       </c>
       <c r="J34" t="n">
-        <v>-5.9184</v>
+        <v>-5.4408</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.73</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.314</v>
+        <v>-0.2967</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.536</v>
+        <v>-7.1208</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.7</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.342</v>
+        <v>-0.3263</v>
       </c>
       <c r="J36" t="n">
-        <v>-8.208</v>
+        <v>-7.8312</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.57</v>
       </c>
       <c r="I37" t="n">
-        <v>1.2721</v>
+        <v>1.2972</v>
       </c>
       <c r="J37" t="n">
-        <v>30.5304</v>
+        <v>31.1328</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.43</v>
       </c>
       <c r="I38" t="n">
-        <v>1.011</v>
+        <v>1.0039</v>
       </c>
       <c r="J38" t="n">
-        <v>24.264</v>
+        <v>24.0936</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.22</v>
       </c>
       <c r="I39" t="n">
-        <v>0.589</v>
+        <v>0.555</v>
       </c>
       <c r="J39" t="n">
-        <v>14.136</v>
+        <v>13.32</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.95</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2352</v>
+        <v>-0.1984</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.6448</v>
+        <v>-4.7616</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.77</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6912</v>
+        <v>-0.6614</v>
       </c>
       <c r="J41" t="n">
-        <v>-16.5888</v>
+        <v>-15.8736</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.55</v>
       </c>
       <c r="I42" t="n">
-        <v>1.0224</v>
+        <v>1.0106</v>
       </c>
       <c r="J42" t="n">
-        <v>25.56</v>
+        <v>25.265</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.29</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6545</v>
+        <v>0.6424</v>
       </c>
       <c r="J43" t="n">
-        <v>16.3625</v>
+        <v>16.06</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.16</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4497</v>
+        <v>0.421</v>
       </c>
       <c r="J44" t="n">
-        <v>11.2425</v>
+        <v>10.525</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.14</v>
       </c>
       <c r="I45" t="n">
-        <v>0.4078</v>
+        <v>0.3741</v>
       </c>
       <c r="J45" t="n">
-        <v>10.195</v>
+        <v>9.352499999999999</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.92</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3276</v>
+        <v>-0.2876</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.19</v>
+        <v>-7.19</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.08</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2462</v>
+        <v>0.2019</v>
       </c>
       <c r="J47" t="n">
-        <v>6.155</v>
+        <v>5.0475</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.92</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1126</v>
+        <v>-0.0977</v>
       </c>
       <c r="J48" t="n">
-        <v>-2.815</v>
+        <v>-2.4425</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.82</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2191</v>
+        <v>-0.2001</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.4775</v>
+        <v>-5.0025</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.76</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2774</v>
+        <v>-0.2589</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.935</v>
+        <v>-6.4725</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.7</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3336</v>
+        <v>-0.3174</v>
       </c>
       <c r="J51" t="n">
-        <v>-8.34</v>
+        <v>-7.935</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.53</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9862</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="J52" t="n">
-        <v>22.6826</v>
+        <v>22.3859</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.34</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.7093</v>
       </c>
       <c r="J53" t="n">
-        <v>16.6129</v>
+        <v>16.3139</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.23</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5602</v>
+        <v>0.5546</v>
       </c>
       <c r="J54" t="n">
-        <v>12.8846</v>
+        <v>12.7558</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.14</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4012</v>
+        <v>0.3685</v>
       </c>
       <c r="J55" t="n">
-        <v>9.227600000000001</v>
+        <v>8.4755</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.04</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1283</v>
+        <v>0.1047</v>
       </c>
       <c r="J56" t="n">
-        <v>2.9509</v>
+        <v>2.4081</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.31</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6095</v>
+        <v>0.5884</v>
       </c>
       <c r="J57" t="n">
-        <v>14.0185</v>
+        <v>13.5332</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.88</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1573</v>
+        <v>-0.1404</v>
       </c>
       <c r="J58" t="n">
-        <v>-3.6179</v>
+        <v>-3.2292</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.8</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2378</v>
+        <v>-0.219</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.4694</v>
+        <v>-5.037</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.68</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.351</v>
+        <v>-0.3358</v>
       </c>
       <c r="J60" t="n">
-        <v>-8.073</v>
+        <v>-7.7234</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4581</v>
+        <v>-0.4526</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.5363</v>
+        <v>-10.4098</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>0.72</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.2658</v>
+        <v>-0.2512</v>
       </c>
       <c r="J62" t="n">
-        <v>-5.316</v>
+        <v>-5.024</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.58</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.4027</v>
+        <v>-0.3979</v>
       </c>
       <c r="J63" t="n">
-        <v>-8.054</v>
+        <v>-7.958</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.4203</v>
+        <v>-0.4161</v>
       </c>
       <c r="J64" t="n">
-        <v>-8.406000000000001</v>
+        <v>-8.321999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.46</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.5051</v>
+        <v>-0.5046</v>
       </c>
       <c r="J65" t="n">
-        <v>-10.102</v>
+        <v>-10.092</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.36</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5941</v>
+        <v>-0.6038</v>
       </c>
       <c r="J66" t="n">
-        <v>-11.882</v>
+        <v>-12.076</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.67</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6662</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="J67" t="n">
-        <v>13.324</v>
+        <v>12.51</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.62</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6329</v>
+        <v>0.5955</v>
       </c>
       <c r="J68" t="n">
-        <v>12.658</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.61</v>
       </c>
       <c r="I69" t="n">
-        <v>0.6262</v>
+        <v>0.5895</v>
       </c>
       <c r="J69" t="n">
-        <v>12.524</v>
+        <v>11.79</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.53</v>
       </c>
       <c r="I70" t="n">
-        <v>0.5725</v>
+        <v>0.5415</v>
       </c>
       <c r="J70" t="n">
-        <v>11.45</v>
+        <v>10.83</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.38</v>
       </c>
       <c r="I71" t="n">
-        <v>0.4632</v>
+        <v>0.4128</v>
       </c>
       <c r="J71" t="n">
-        <v>9.263999999999999</v>
+        <v>8.256</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.09</v>
       </c>
       <c r="I72" t="n">
-        <v>0.2038</v>
+        <v>0.1879</v>
       </c>
       <c r="J72" t="n">
-        <v>5.9102</v>
+        <v>5.4491</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.01</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0501</v>
+        <v>0.0396</v>
       </c>
       <c r="J73" t="n">
-        <v>1.4529</v>
+        <v>1.1484</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.97</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0487</v>
+        <v>-0.0391</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.4123</v>
+        <v>-1.1339</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.77</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2702</v>
+        <v>-0.2512</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.8358</v>
+        <v>-7.2848</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4615</v>
+        <v>-0.4567</v>
       </c>
       <c r="J76" t="n">
-        <v>-13.3835</v>
+        <v>-13.2443</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.44</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5271</v>
+        <v>0.4875</v>
       </c>
       <c r="J77" t="n">
-        <v>15.2859</v>
+        <v>14.1375</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.37</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4729</v>
+        <v>0.4184</v>
       </c>
       <c r="J78" t="n">
-        <v>13.7141</v>
+        <v>12.1336</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.31</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4196</v>
+        <v>0.358</v>
       </c>
       <c r="J79" t="n">
-        <v>12.1684</v>
+        <v>10.382</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.04</v>
       </c>
       <c r="I80" t="n">
-        <v>0.0722</v>
+        <v>0.0522</v>
       </c>
       <c r="J80" t="n">
-        <v>2.0938</v>
+        <v>1.5138</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.02</v>
       </c>
       <c r="I81" t="n">
-        <v>0.0337</v>
+        <v>0.0218</v>
       </c>
       <c r="J81" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.6322</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.62</v>
       </c>
       <c r="I82" t="n">
-        <v>1.1017</v>
+        <v>1.093</v>
       </c>
       <c r="J82" t="n">
-        <v>29.7459</v>
+        <v>29.511</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.56</v>
       </c>
       <c r="I83" t="n">
-        <v>1.0228</v>
+        <v>1.011</v>
       </c>
       <c r="J83" t="n">
-        <v>27.6156</v>
+        <v>27.297</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.18</v>
       </c>
       <c r="I84" t="n">
-        <v>0.4779</v>
+        <v>0.4601</v>
       </c>
       <c r="J84" t="n">
-        <v>12.9033</v>
+        <v>12.4227</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.09</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2716</v>
+        <v>0.2406</v>
       </c>
       <c r="J85" t="n">
-        <v>7.3332</v>
+        <v>6.4962</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.92</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3381</v>
+        <v>-0.2995</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.1287</v>
+        <v>-8.086499999999999</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.11</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3172</v>
+        <v>0.2696</v>
       </c>
       <c r="J87" t="n">
-        <v>8.564399999999999</v>
+        <v>7.2792</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.03</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1365</v>
+        <v>0.1061</v>
       </c>
       <c r="J88" t="n">
-        <v>3.6855</v>
+        <v>2.8647</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.86</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1772</v>
+        <v>-0.16</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.7844</v>
+        <v>-4.32</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.66</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3674</v>
+        <v>-0.3534</v>
       </c>
       <c r="J90" t="n">
-        <v>-9.9198</v>
+        <v>-9.5418</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.49</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5172</v>
+        <v>-0.519</v>
       </c>
       <c r="J91" t="n">
-        <v>-13.9644</v>
+        <v>-14.013</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>0.92</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.1</v>
+        <v>-0.0858</v>
       </c>
       <c r="J92" t="n">
-        <v>-2.6</v>
+        <v>-2.2308</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.85</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1806</v>
+        <v>-0.1647</v>
       </c>
       <c r="J93" t="n">
-        <v>-4.6956</v>
+        <v>-4.2822</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.78</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2509</v>
+        <v>-0.2344</v>
       </c>
       <c r="J94" t="n">
-        <v>-6.5234</v>
+        <v>-6.0944</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.76</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.269</v>
+        <v>-0.2525</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.994</v>
+        <v>-6.565</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.53</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.476</v>
+        <v>-0.4718</v>
       </c>
       <c r="J96" t="n">
-        <v>-12.376</v>
+        <v>-12.2668</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.8</v>
       </c>
       <c r="I97" t="n">
-        <v>1.3156</v>
+        <v>1.3193</v>
       </c>
       <c r="J97" t="n">
-        <v>34.2056</v>
+        <v>34.3018</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.3</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6578000000000001</v>
+        <v>0.6501</v>
       </c>
       <c r="J98" t="n">
-        <v>17.1028</v>
+        <v>16.9026</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.26</v>
       </c>
       <c r="I99" t="n">
-        <v>0.5982</v>
+        <v>0.5931</v>
       </c>
       <c r="J99" t="n">
-        <v>15.5532</v>
+        <v>15.4206</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.24</v>
       </c>
       <c r="I100" t="n">
-        <v>0.5674</v>
+        <v>0.5638</v>
       </c>
       <c r="J100" t="n">
-        <v>14.7524</v>
+        <v>14.6588</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.1</v>
       </c>
       <c r="I101" t="n">
-        <v>0.2876</v>
+        <v>0.256</v>
       </c>
       <c r="J101" t="n">
-        <v>7.4776</v>
+        <v>6.656</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.3</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5456</v>
+        <v>0.5181</v>
       </c>
       <c r="J102" t="n">
-        <v>16.368</v>
+        <v>15.543</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.12</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2817</v>
+        <v>0.2337</v>
       </c>
       <c r="J103" t="n">
-        <v>8.451000000000001</v>
+        <v>7.011</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.09</v>
       </c>
       <c r="I104" t="n">
-        <v>0.2246</v>
+        <v>0.1823</v>
       </c>
       <c r="J104" t="n">
-        <v>6.738</v>
+        <v>5.469</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.92</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1281</v>
+        <v>-0.1091</v>
       </c>
       <c r="J105" t="n">
-        <v>-3.843</v>
+        <v>-3.273</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.84</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2167</v>
+        <v>-0.1962</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.501</v>
+        <v>-5.886</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.25</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6128</v>
+        <v>0.5996</v>
       </c>
       <c r="J107" t="n">
-        <v>18.384</v>
+        <v>17.988</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.17</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4806</v>
+        <v>0.4552</v>
       </c>
       <c r="J108" t="n">
-        <v>14.418</v>
+        <v>13.656</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.1</v>
       </c>
       <c r="I109" t="n">
-        <v>0.3256</v>
+        <v>0.2878</v>
       </c>
       <c r="J109" t="n">
-        <v>9.768000000000001</v>
+        <v>8.634</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.07</v>
       </c>
       <c r="I110" t="n">
-        <v>0.2466</v>
+        <v>0.2128</v>
       </c>
       <c r="J110" t="n">
-        <v>7.398</v>
+        <v>6.384</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.84</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5106000000000001</v>
+        <v>-0.4692</v>
       </c>
       <c r="J111" t="n">
-        <v>-15.318</v>
+        <v>-14.076</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.03</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3071</v>
+        <v>0.3291</v>
       </c>
       <c r="J112" t="n">
-        <v>5.8349</v>
+        <v>6.2529</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.52</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.4535</v>
+        <v>-0.4501</v>
       </c>
       <c r="J113" t="n">
-        <v>-8.6165</v>
+        <v>-8.5519</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.51</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.462</v>
+        <v>-0.4589</v>
       </c>
       <c r="J114" t="n">
-        <v>-8.778</v>
+        <v>-8.719099999999999</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.35</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.6034</v>
+        <v>-0.6145</v>
       </c>
       <c r="J115" t="n">
-        <v>-11.4646</v>
+        <v>-11.6755</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.28</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6664</v>
+        <v>-0.6885</v>
       </c>
       <c r="J116" t="n">
-        <v>-12.6616</v>
+        <v>-13.0815</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.8</v>
       </c>
       <c r="I117" t="n">
-        <v>1.2802</v>
+        <v>1.2825</v>
       </c>
       <c r="J117" t="n">
-        <v>24.3238</v>
+        <v>24.3675</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.6</v>
       </c>
       <c r="I118" t="n">
-        <v>1.0375</v>
+        <v>1.0317</v>
       </c>
       <c r="J118" t="n">
-        <v>19.7125</v>
+        <v>19.6023</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.54</v>
       </c>
       <c r="I119" t="n">
-        <v>0.9635</v>
+        <v>0.957</v>
       </c>
       <c r="J119" t="n">
-        <v>18.3065</v>
+        <v>18.183</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.37</v>
       </c>
       <c r="I120" t="n">
-        <v>0.7395</v>
+        <v>0.7342</v>
       </c>
       <c r="J120" t="n">
-        <v>14.0505</v>
+        <v>13.9498</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.36</v>
       </c>
       <c r="I121" t="n">
-        <v>0.7254</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="J121" t="n">
-        <v>13.7826</v>
+        <v>13.6857</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.24</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5516</v>
+        <v>0.5001</v>
       </c>
       <c r="J122" t="n">
-        <v>12.1352</v>
+        <v>11.0022</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.0863</v>
+        <v>-0.0733</v>
       </c>
       <c r="J123" t="n">
-        <v>-1.8986</v>
+        <v>-1.6126</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0863</v>
+        <v>-0.0733</v>
       </c>
       <c r="J124" t="n">
-        <v>-1.8986</v>
+        <v>-1.6126</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.58</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.4406</v>
+        <v>-0.4331</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.693199999999999</v>
+        <v>-9.5282</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.53</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4843</v>
+        <v>-0.4819</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.6546</v>
+        <v>-10.6018</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.93</v>
       </c>
       <c r="I127" t="n">
-        <v>1.6128</v>
+        <v>1.6539</v>
       </c>
       <c r="J127" t="n">
-        <v>35.4816</v>
+        <v>36.3858</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.38</v>
       </c>
       <c r="I128" t="n">
-        <v>0.8824</v>
+        <v>0.8717</v>
       </c>
       <c r="J128" t="n">
-        <v>19.4128</v>
+        <v>19.1774</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.26</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6495</v>
+        <v>0.6258</v>
       </c>
       <c r="J129" t="n">
-        <v>14.289</v>
+        <v>13.7676</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.24</v>
       </c>
       <c r="I130" t="n">
-        <v>0.6077</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="J130" t="n">
-        <v>13.3694</v>
+        <v>12.8084</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>1.07</v>
       </c>
       <c r="I131" t="n">
-        <v>0.2</v>
+        <v>0.1701</v>
       </c>
       <c r="J131" t="n">
-        <v>4.4</v>
+        <v>3.7422</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.67</v>
       </c>
       <c r="I132" t="n">
-        <v>1.178</v>
+        <v>1.1957</v>
       </c>
       <c r="J132" t="n">
-        <v>28.272</v>
+        <v>28.6968</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0833</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="J133" t="n">
-        <v>-1.9992</v>
+        <v>-1.692</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.63</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.3938</v>
+        <v>-0.3818</v>
       </c>
       <c r="J134" t="n">
-        <v>-9.4512</v>
+        <v>-9.1632</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.46</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.5423</v>
+        <v>-0.5477</v>
       </c>
       <c r="J135" t="n">
-        <v>-13.0152</v>
+        <v>-13.1448</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.42</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5763</v>
+        <v>-0.587</v>
       </c>
       <c r="J136" t="n">
-        <v>-13.8312</v>
+        <v>-14.088</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.51</v>
       </c>
       <c r="I137" t="n">
-        <v>1.0978</v>
+        <v>1.1098</v>
       </c>
       <c r="J137" t="n">
-        <v>26.3472</v>
+        <v>26.6352</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.49</v>
       </c>
       <c r="I138" t="n">
-        <v>1.0708</v>
+        <v>1.0805</v>
       </c>
       <c r="J138" t="n">
-        <v>25.6992</v>
+        <v>25.932</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.37</v>
       </c>
       <c r="I139" t="n">
-        <v>0.8719</v>
+        <v>0.8568</v>
       </c>
       <c r="J139" t="n">
-        <v>20.9256</v>
+        <v>20.5632</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.26</v>
       </c>
       <c r="I140" t="n">
-        <v>0.659</v>
+        <v>0.6331</v>
       </c>
       <c r="J140" t="n">
-        <v>15.816</v>
+        <v>15.1944</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.9</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3977</v>
+        <v>-0.3595</v>
       </c>
       <c r="J141" t="n">
-        <v>-9.5448</v>
+        <v>-8.628</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.99</v>
       </c>
       <c r="I142" t="n">
-        <v>1.6517</v>
+        <v>1.695</v>
       </c>
       <c r="J142" t="n">
-        <v>31.3823</v>
+        <v>32.205</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.78</v>
       </c>
       <c r="I143" t="n">
-        <v>1.4048</v>
+        <v>1.4313</v>
       </c>
       <c r="J143" t="n">
-        <v>26.6912</v>
+        <v>27.1947</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.51</v>
       </c>
       <c r="I144" t="n">
-        <v>1.074</v>
+        <v>1.0912</v>
       </c>
       <c r="J144" t="n">
-        <v>20.406</v>
+        <v>20.7328</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.24</v>
       </c>
       <c r="I145" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.5613</v>
       </c>
       <c r="J145" t="n">
-        <v>11.1378</v>
+        <v>10.6647</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.11</v>
       </c>
       <c r="I146" t="n">
-        <v>0.2861</v>
+        <v>0.2517</v>
       </c>
       <c r="J146" t="n">
-        <v>5.4359</v>
+        <v>4.7823</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>0.74</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.2642</v>
+        <v>-0.251</v>
       </c>
       <c r="J147" t="n">
-        <v>-5.0198</v>
+        <v>-4.769</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.3136</v>
+        <v>-0.3029</v>
       </c>
       <c r="J148" t="n">
-        <v>-5.9584</v>
+        <v>-5.7551</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.68</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.3231</v>
+        <v>-0.3128</v>
       </c>
       <c r="J149" t="n">
-        <v>-6.1389</v>
+        <v>-5.9432</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4282</v>
+        <v>-0.4211</v>
       </c>
       <c r="J150" t="n">
-        <v>-8.1358</v>
+        <v>-8.0009</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.35</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.613</v>
+        <v>-0.6264999999999999</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.647</v>
+        <v>-11.9035</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.29</v>
       </c>
       <c r="I152" t="n">
-        <v>0.7444</v>
+        <v>0.7148</v>
       </c>
       <c r="J152" t="n">
-        <v>20.0988</v>
+        <v>19.2996</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.27</v>
       </c>
       <c r="I153" t="n">
-        <v>0.7027</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="J153" t="n">
-        <v>18.9729</v>
+        <v>18.1143</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.15</v>
       </c>
       <c r="I154" t="n">
-        <v>0.4399</v>
+        <v>0.4025</v>
       </c>
       <c r="J154" t="n">
-        <v>11.8773</v>
+        <v>10.8675</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.14</v>
       </c>
       <c r="I155" t="n">
-        <v>0.4171</v>
+        <v>0.3799</v>
       </c>
       <c r="J155" t="n">
-        <v>11.2617</v>
+        <v>10.2573</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.87</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4477</v>
+        <v>-0.4058</v>
       </c>
       <c r="J156" t="n">
-        <v>-12.0879</v>
+        <v>-10.9566</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.56</v>
       </c>
       <c r="I157" t="n">
-        <v>0.9748</v>
+        <v>0.9394</v>
       </c>
       <c r="J157" t="n">
-        <v>26.3196</v>
+        <v>25.3638</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.3</v>
       </c>
       <c r="I158" t="n">
-        <v>0.593</v>
+        <v>0.5337</v>
       </c>
       <c r="J158" t="n">
-        <v>16.011</v>
+        <v>14.4099</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.83</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.2236</v>
+        <v>-0.2031</v>
       </c>
       <c r="J159" t="n">
-        <v>-6.0372</v>
+        <v>-5.4837</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.77</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2832</v>
+        <v>-0.2646</v>
       </c>
       <c r="J160" t="n">
-        <v>-7.6464</v>
+        <v>-7.1442</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.62</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.421</v>
+        <v>-0.4131</v>
       </c>
       <c r="J161" t="n">
-        <v>-11.367</v>
+        <v>-11.1537</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.28</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5619</v>
+        <v>0.5024</v>
       </c>
       <c r="J162" t="n">
-        <v>16.857</v>
+        <v>15.072</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.17</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3788</v>
+        <v>0.3235</v>
       </c>
       <c r="J163" t="n">
-        <v>11.364</v>
+        <v>9.705</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.95</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0871</v>
+        <v>-0.0712</v>
       </c>
       <c r="J164" t="n">
-        <v>-2.613</v>
+        <v>-2.136</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.93</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1127</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="J165" t="n">
-        <v>-3.381</v>
+        <v>-2.841</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.74</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3117</v>
+        <v>-0.2945</v>
       </c>
       <c r="J166" t="n">
-        <v>-9.351000000000001</v>
+        <v>-8.835000000000001</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.34</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8636</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="J167" t="n">
-        <v>25.908</v>
+        <v>25.266</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.14</v>
       </c>
       <c r="I168" t="n">
-        <v>0.425</v>
+        <v>0.3846</v>
       </c>
       <c r="J168" t="n">
-        <v>12.75</v>
+        <v>11.538</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.06</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2185</v>
+        <v>0.1865</v>
       </c>
       <c r="J169" t="n">
-        <v>6.555</v>
+        <v>5.595</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.04</v>
       </c>
       <c r="I170" t="n">
-        <v>0.1575</v>
+        <v>0.1308</v>
       </c>
       <c r="J170" t="n">
-        <v>4.725</v>
+        <v>3.924</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.84</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5102</v>
+        <v>-0.4688</v>
       </c>
       <c r="J171" t="n">
-        <v>-15.306</v>
+        <v>-14.064</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.02</v>
       </c>
       <c r="I172" t="n">
-        <v>0.0941</v>
+        <v>0.0687</v>
       </c>
       <c r="J172" t="n">
-        <v>2.5407</v>
+        <v>1.8549</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.01</v>
       </c>
       <c r="I173" t="n">
-        <v>0.063</v>
+        <v>0.0442</v>
       </c>
       <c r="J173" t="n">
-        <v>1.701</v>
+        <v>1.1934</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.99</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.0153</v>
+        <v>-0.0108</v>
       </c>
       <c r="J174" t="n">
-        <v>-0.4131</v>
+        <v>-0.2916</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.7</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3366</v>
+        <v>-0.3205</v>
       </c>
       <c r="J175" t="n">
-        <v>-9.088200000000001</v>
+        <v>-8.653499999999999</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.7</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3366</v>
+        <v>-0.3205</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.088200000000001</v>
+        <v>-8.653499999999999</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.61</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2447</v>
+        <v>1.2616</v>
       </c>
       <c r="J177" t="n">
-        <v>33.6069</v>
+        <v>34.0632</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.37</v>
       </c>
       <c r="I178" t="n">
-        <v>0.8847</v>
+        <v>0.8673999999999999</v>
       </c>
       <c r="J178" t="n">
-        <v>23.8869</v>
+        <v>23.4198</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.18</v>
       </c>
       <c r="I179" t="n">
-        <v>0.4976</v>
+        <v>0.4646</v>
       </c>
       <c r="J179" t="n">
-        <v>13.4352</v>
+        <v>12.5442</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.02</v>
       </c>
       <c r="I180" t="n">
-        <v>0.0618</v>
+        <v>0.0456</v>
       </c>
       <c r="J180" t="n">
-        <v>1.6686</v>
+        <v>1.2312</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.99</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.0993</v>
+        <v>-0.0786</v>
       </c>
       <c r="J181" t="n">
-        <v>-2.6811</v>
+        <v>-2.1222</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.25</v>
       </c>
       <c r="I182" t="n">
-        <v>0.6466</v>
+        <v>0.6163</v>
       </c>
       <c r="J182" t="n">
-        <v>18.1048</v>
+        <v>17.2564</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.25</v>
       </c>
       <c r="I183" t="n">
-        <v>0.6466</v>
+        <v>0.6163</v>
       </c>
       <c r="J183" t="n">
-        <v>18.1048</v>
+        <v>17.2564</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.23</v>
       </c>
       <c r="I184" t="n">
-        <v>0.6056</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="J184" t="n">
-        <v>16.9568</v>
+        <v>16.0748</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.21</v>
       </c>
       <c r="I185" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5316</v>
       </c>
       <c r="J185" t="n">
-        <v>15.792</v>
+        <v>14.8848</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.2</v>
       </c>
       <c r="I186" t="n">
-        <v>0.5425</v>
+        <v>0.5098</v>
       </c>
       <c r="J186" t="n">
-        <v>15.19</v>
+        <v>14.2744</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.13</v>
       </c>
       <c r="I187" t="n">
-        <v>0.3457</v>
+        <v>0.2948</v>
       </c>
       <c r="J187" t="n">
-        <v>9.679600000000001</v>
+        <v>8.2544</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.05</v>
       </c>
       <c r="I188" t="n">
-        <v>0.1771</v>
+        <v>0.1397</v>
       </c>
       <c r="J188" t="n">
-        <v>4.9588</v>
+        <v>3.9116</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.82</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2196</v>
+        <v>-0.2005</v>
       </c>
       <c r="J189" t="n">
-        <v>-6.1488</v>
+        <v>-5.614</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.76</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.278</v>
+        <v>-0.2594</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.784</v>
+        <v>-7.2632</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.55</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4685</v>
+        <v>-0.4643</v>
       </c>
       <c r="J191" t="n">
-        <v>-13.118</v>
+        <v>-13.0004</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.37</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5534</v>
+        <v>0.5719</v>
       </c>
       <c r="J192" t="n">
-        <v>15.4952</v>
+        <v>16.0132</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.17</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2994</v>
+        <v>0.2872</v>
       </c>
       <c r="J193" t="n">
-        <v>8.3832</v>
+        <v>8.041600000000001</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.84</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.2117</v>
+        <v>-0.1911</v>
       </c>
       <c r="J194" t="n">
-        <v>-5.9276</v>
+        <v>-5.3508</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.83</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.222</v>
+        <v>-0.2015</v>
       </c>
       <c r="J195" t="n">
-        <v>-6.216</v>
+        <v>-5.642</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.78</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.2719</v>
+        <v>-0.2527</v>
       </c>
       <c r="J196" t="n">
-        <v>-7.6132</v>
+        <v>-7.0756</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.26</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3817</v>
+        <v>0.3195</v>
       </c>
       <c r="J197" t="n">
-        <v>10.6876</v>
+        <v>8.946</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.17</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2718</v>
+        <v>0.2197</v>
       </c>
       <c r="J198" t="n">
-        <v>7.6104</v>
+        <v>6.1516</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.07</v>
       </c>
       <c r="I199" t="n">
-        <v>0.1353</v>
+        <v>0.1027</v>
       </c>
       <c r="J199" t="n">
-        <v>3.7884</v>
+        <v>2.8756</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.03</v>
       </c>
       <c r="I200" t="n">
-        <v>0.0679</v>
+        <v>0.0487</v>
       </c>
       <c r="J200" t="n">
-        <v>1.9012</v>
+        <v>1.3636</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.9</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.1543</v>
+        <v>-0.1342</v>
       </c>
       <c r="J201" t="n">
-        <v>-4.3204</v>
+        <v>-3.7576</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.59</v>
       </c>
       <c r="I202" t="n">
-        <v>1.2307</v>
+        <v>1.2476</v>
       </c>
       <c r="J202" t="n">
-        <v>36.921</v>
+        <v>37.428</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.4</v>
       </c>
       <c r="I203" t="n">
-        <v>0.9530999999999999</v>
+        <v>0.9421</v>
       </c>
       <c r="J203" t="n">
-        <v>28.593</v>
+        <v>28.263</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.3</v>
       </c>
       <c r="I204" t="n">
-        <v>0.7565</v>
+        <v>0.7289</v>
       </c>
       <c r="J204" t="n">
-        <v>22.695</v>
+        <v>21.867</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.86</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4795</v>
+        <v>-0.4391</v>
       </c>
       <c r="J205" t="n">
-        <v>-14.385</v>
+        <v>-13.173</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.76</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.7124</v>
+        <v>-0.6841</v>
       </c>
       <c r="J206" t="n">
-        <v>-21.372</v>
+        <v>-20.523</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.22</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4747</v>
+        <v>0.4165</v>
       </c>
       <c r="J207" t="n">
-        <v>14.241</v>
+        <v>12.495</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.04</v>
       </c>
       <c r="I208" t="n">
-        <v>0.1288</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="J208" t="n">
-        <v>3.864</v>
+        <v>2.913</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.01</v>
       </c>
       <c r="I209" t="n">
-        <v>0.0466</v>
+        <v>0.0312</v>
       </c>
       <c r="J209" t="n">
-        <v>1.398</v>
+        <v>0.9360000000000001</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1</v>
       </c>
       <c r="I210" t="n">
-        <v>0.0027</v>
+        <v>0.0013</v>
       </c>
       <c r="J210" t="n">
-        <v>0.081</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.59</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4436</v>
+        <v>-0.4378</v>
       </c>
       <c r="J211" t="n">
-        <v>-13.308</v>
+        <v>-13.134</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>0.87</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.0968</v>
+        <v>-0.067</v>
       </c>
       <c r="J212" t="n">
-        <v>-1.8392</v>
+        <v>-1.273</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.4212</v>
+        <v>-0.4167</v>
       </c>
       <c r="J213" t="n">
-        <v>-8.002800000000001</v>
+        <v>-7.9173</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.5</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.4712</v>
+        <v>-0.4683</v>
       </c>
       <c r="J214" t="n">
-        <v>-8.9528</v>
+        <v>-8.8977</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.45</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.5149</v>
+        <v>-0.5151</v>
       </c>
       <c r="J215" t="n">
-        <v>-9.783099999999999</v>
+        <v>-9.786899999999999</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.33</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.622</v>
+        <v>-0.6362</v>
       </c>
       <c r="J216" t="n">
-        <v>-11.818</v>
+        <v>-12.0878</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.86</v>
       </c>
       <c r="I217" t="n">
-        <v>1.495</v>
+        <v>1.527</v>
       </c>
       <c r="J217" t="n">
-        <v>28.405</v>
+        <v>29.013</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.81</v>
       </c>
       <c r="I218" t="n">
-        <v>1.436</v>
+        <v>1.4647</v>
       </c>
       <c r="J218" t="n">
-        <v>27.284</v>
+        <v>27.8293</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.44</v>
       </c>
       <c r="I219" t="n">
-        <v>0.9692</v>
+        <v>0.9752</v>
       </c>
       <c r="J219" t="n">
-        <v>18.4148</v>
+        <v>18.5288</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.44</v>
       </c>
       <c r="I220" t="n">
-        <v>0.9692</v>
+        <v>0.9752</v>
       </c>
       <c r="J220" t="n">
-        <v>18.4148</v>
+        <v>18.5288</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.24</v>
       </c>
       <c r="I221" t="n">
-        <v>0.5818</v>
+        <v>0.5567</v>
       </c>
       <c r="J221" t="n">
-        <v>11.0542</v>
+        <v>10.5773</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.3</v>
       </c>
       <c r="I222" t="n">
-        <v>0.4111</v>
+        <v>0.3488</v>
       </c>
       <c r="J222" t="n">
-        <v>11.5108</v>
+        <v>9.766400000000001</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.3</v>
       </c>
       <c r="I223" t="n">
-        <v>0.4111</v>
+        <v>0.3488</v>
       </c>
       <c r="J223" t="n">
-        <v>11.5108</v>
+        <v>9.766400000000001</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.22</v>
       </c>
       <c r="I224" t="n">
-        <v>0.3213</v>
+        <v>0.267</v>
       </c>
       <c r="J224" t="n">
-        <v>8.9964</v>
+        <v>7.476</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.19</v>
       </c>
       <c r="I225" t="n">
-        <v>0.2862</v>
+        <v>0.2356</v>
       </c>
       <c r="J225" t="n">
-        <v>8.0136</v>
+        <v>6.5968</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.09</v>
       </c>
       <c r="I226" t="n">
-        <v>0.1539</v>
+        <v>0.1201</v>
       </c>
       <c r="J226" t="n">
-        <v>4.3092</v>
+        <v>3.3628</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.24</v>
       </c>
       <c r="I227" t="n">
-        <v>0.3998</v>
+        <v>0.3974</v>
       </c>
       <c r="J227" t="n">
-        <v>11.1944</v>
+        <v>11.1272</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.07</v>
       </c>
       <c r="I228" t="n">
-        <v>0.1551</v>
+        <v>0.1378</v>
       </c>
       <c r="J228" t="n">
-        <v>4.3428</v>
+        <v>3.8584</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.97</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.0563</v>
+        <v>-0.0447</v>
       </c>
       <c r="J229" t="n">
-        <v>-1.5764</v>
+        <v>-1.2516</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.82</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2291</v>
+        <v>-0.2087</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.4148</v>
+        <v>-5.8436</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.72</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3259</v>
+        <v>-0.3093</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.1252</v>
+        <v>-8.660399999999999</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>0.93</v>
       </c>
       <c r="I232" t="n">
-        <v>-0.0818</v>
+        <v>-0.0677</v>
       </c>
       <c r="J232" t="n">
-        <v>-1.9632</v>
+        <v>-1.6248</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.88</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.1428</v>
+        <v>-0.1274</v>
       </c>
       <c r="J233" t="n">
-        <v>-3.4272</v>
+        <v>-3.0576</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.72</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.303</v>
+        <v>-0.2876</v>
       </c>
       <c r="J234" t="n">
-        <v>-7.272</v>
+        <v>-6.9024</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.67</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.3481</v>
+        <v>-0.3339</v>
       </c>
       <c r="J235" t="n">
-        <v>-8.3544</v>
+        <v>-8.0136</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.5</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4989</v>
+        <v>-0.4973</v>
       </c>
       <c r="J236" t="n">
-        <v>-11.9736</v>
+        <v>-11.9352</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.72</v>
       </c>
       <c r="I237" t="n">
-        <v>1.362</v>
+        <v>1.3846</v>
       </c>
       <c r="J237" t="n">
-        <v>32.688</v>
+        <v>33.2304</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.33</v>
       </c>
       <c r="I238" t="n">
-        <v>0.7924</v>
+        <v>0.7746</v>
       </c>
       <c r="J238" t="n">
-        <v>19.0176</v>
+        <v>18.5904</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.27</v>
       </c>
       <c r="I239" t="n">
-        <v>0.6742</v>
+        <v>0.6506</v>
       </c>
       <c r="J239" t="n">
-        <v>16.1808</v>
+        <v>15.6144</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.23</v>
       </c>
       <c r="I240" t="n">
-        <v>0.5908</v>
+        <v>0.5638</v>
       </c>
       <c r="J240" t="n">
-        <v>14.1792</v>
+        <v>13.5312</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>1.18</v>
       </c>
       <c r="I241" t="n">
-        <v>0.4808</v>
+        <v>0.4505</v>
       </c>
       <c r="J241" t="n">
-        <v>11.5392</v>
+        <v>10.812</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>2.08</v>
       </c>
       <c r="I242" t="n">
-        <v>1.7267</v>
+        <v>1.7772</v>
       </c>
       <c r="J242" t="n">
-        <v>32.8073</v>
+        <v>33.7668</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.88</v>
       </c>
       <c r="I243" t="n">
-        <v>1.5012</v>
+        <v>1.5362</v>
       </c>
       <c r="J243" t="n">
-        <v>28.5228</v>
+        <v>29.1878</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.63</v>
       </c>
       <c r="I244" t="n">
-        <v>1.2111</v>
+        <v>1.2362</v>
       </c>
       <c r="J244" t="n">
-        <v>23.0109</v>
+        <v>23.4878</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.45</v>
       </c>
       <c r="I245" t="n">
-        <v>0.971</v>
+        <v>0.9802</v>
       </c>
       <c r="J245" t="n">
-        <v>18.449</v>
+        <v>18.6238</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>1.4</v>
       </c>
       <c r="I246" t="n">
-        <v>0.8822</v>
+        <v>0.8806</v>
       </c>
       <c r="J246" t="n">
-        <v>16.7618</v>
+        <v>16.7314</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.07</v>
       </c>
       <c r="I247" t="n">
-        <v>0.5026</v>
+        <v>0.573</v>
       </c>
       <c r="J247" t="n">
-        <v>9.5494</v>
+        <v>10.887</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.53</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.4342</v>
+        <v>-0.4334</v>
       </c>
       <c r="J248" t="n">
-        <v>-8.2498</v>
+        <v>-8.2346</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.32</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.619</v>
+        <v>-0.6319</v>
       </c>
       <c r="J249" t="n">
-        <v>-11.761</v>
+        <v>-12.0061</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.3</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.6374</v>
+        <v>-0.6532</v>
       </c>
       <c r="J250" t="n">
-        <v>-12.1106</v>
+        <v>-12.4108</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.13</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.7964</v>
+        <v>-0.8474</v>
       </c>
       <c r="J251" t="n">
-        <v>-15.1316</v>
+        <v>-16.1006</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.88</v>
       </c>
       <c r="I252" t="n">
-        <v>1.5163</v>
+        <v>1.5498</v>
       </c>
       <c r="J252" t="n">
-        <v>25.7771</v>
+        <v>26.3466</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.86</v>
       </c>
       <c r="I253" t="n">
-        <v>1.4929</v>
+        <v>1.525</v>
       </c>
       <c r="J253" t="n">
-        <v>25.3793</v>
+        <v>25.925</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.71</v>
       </c>
       <c r="I254" t="n">
-        <v>1.315</v>
+        <v>1.3389</v>
       </c>
       <c r="J254" t="n">
-        <v>22.355</v>
+        <v>22.7613</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.35</v>
       </c>
       <c r="I255" t="n">
-        <v>0.8022</v>
+        <v>0.7922</v>
       </c>
       <c r="J255" t="n">
-        <v>13.6374</v>
+        <v>13.4674</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>1.06</v>
       </c>
       <c r="I256" t="n">
-        <v>0.1433</v>
+        <v>0.1102</v>
       </c>
       <c r="J256" t="n">
-        <v>2.4361</v>
+        <v>1.8734</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>0.89</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.064</v>
       </c>
       <c r="J257" t="n">
-        <v>-1.5113</v>
+        <v>-1.088</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.85</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.1379</v>
+        <v>-0.1158</v>
       </c>
       <c r="J258" t="n">
-        <v>-2.3443</v>
+        <v>-1.9686</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.53</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.4514</v>
+        <v>-0.4461</v>
       </c>
       <c r="J259" t="n">
-        <v>-7.6738</v>
+        <v>-7.5837</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.48</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.4952</v>
+        <v>-0.4931</v>
       </c>
       <c r="J260" t="n">
-        <v>-8.4184</v>
+        <v>-8.3827</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.17</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.7697000000000001</v>
+        <v>-0.8158</v>
       </c>
       <c r="J261" t="n">
-        <v>-13.0849</v>
+        <v>-13.8686</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.19</v>
       </c>
       <c r="I262" t="n">
-        <v>0.3324</v>
+        <v>0.323</v>
       </c>
       <c r="J262" t="n">
-        <v>7.9776</v>
+        <v>7.752</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.06</v>
       </c>
       <c r="I263" t="n">
-        <v>0.1375</v>
+        <v>0.1205</v>
       </c>
       <c r="J263" t="n">
-        <v>3.3</v>
+        <v>2.892</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.9</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.1442</v>
+        <v>-0.125</v>
       </c>
       <c r="J264" t="n">
-        <v>-3.4608</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.89</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.1555</v>
+        <v>-0.1358</v>
       </c>
       <c r="J265" t="n">
-        <v>-3.732</v>
+        <v>-3.2592</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.8</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.2495</v>
+        <v>-0.2295</v>
       </c>
       <c r="J266" t="n">
-        <v>-5.988</v>
+        <v>-5.508</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.45</v>
       </c>
       <c r="I267" t="n">
-        <v>0.5723</v>
+        <v>0.5017</v>
       </c>
       <c r="J267" t="n">
-        <v>13.7352</v>
+        <v>12.0408</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.44</v>
       </c>
       <c r="I268" t="n">
-        <v>0.5619</v>
+        <v>0.4917</v>
       </c>
       <c r="J268" t="n">
-        <v>13.4856</v>
+        <v>11.8008</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.21</v>
       </c>
       <c r="I269" t="n">
-        <v>0.3103</v>
+        <v>0.2569</v>
       </c>
       <c r="J269" t="n">
-        <v>7.4472</v>
+        <v>6.1656</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.02</v>
       </c>
       <c r="I270" t="n">
-        <v>0.0362</v>
+        <v>0.024</v>
       </c>
       <c r="J270" t="n">
-        <v>0.8688</v>
+        <v>0.576</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.93</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.1284</v>
+        <v>-0.1102</v>
       </c>
       <c r="J271" t="n">
-        <v>-3.0816</v>
+        <v>-2.6448</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.5</v>
       </c>
       <c r="I272" t="n">
-        <v>1.0801</v>
+        <v>1.0913</v>
       </c>
       <c r="J272" t="n">
-        <v>25.9224</v>
+        <v>26.1912</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.43</v>
       </c>
       <c r="I273" t="n">
-        <v>0.9759</v>
+        <v>0.9729</v>
       </c>
       <c r="J273" t="n">
-        <v>23.4216</v>
+        <v>23.3496</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.35</v>
       </c>
       <c r="I274" t="n">
-        <v>0.8306</v>
+        <v>0.8145</v>
       </c>
       <c r="J274" t="n">
-        <v>19.9344</v>
+        <v>19.548</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.2</v>
       </c>
       <c r="I275" t="n">
-        <v>0.5275</v>
+        <v>0.4982</v>
       </c>
       <c r="J275" t="n">
-        <v>12.66</v>
+        <v>11.9568</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>1.19</v>
       </c>
       <c r="I276" t="n">
-        <v>0.5052</v>
+        <v>0.4753</v>
       </c>
       <c r="J276" t="n">
-        <v>12.1248</v>
+        <v>11.4072</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.26</v>
       </c>
       <c r="I277" t="n">
-        <v>0.6267</v>
+        <v>0.5886</v>
       </c>
       <c r="J277" t="n">
-        <v>15.0408</v>
+        <v>14.1264</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.83</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.2011</v>
+        <v>-0.1851</v>
       </c>
       <c r="J278" t="n">
-        <v>-4.8264</v>
+        <v>-4.4424</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.76</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.2688</v>
+        <v>-0.2524</v>
       </c>
       <c r="J279" t="n">
-        <v>-6.4512</v>
+        <v>-6.0576</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.62</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3959</v>
+        <v>-0.3841</v>
       </c>
       <c r="J280" t="n">
-        <v>-9.5016</v>
+        <v>-9.218400000000001</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.35</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.6302</v>
+        <v>-0.6494</v>
       </c>
       <c r="J281" t="n">
-        <v>-15.1248</v>
+        <v>-15.5856</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.76</v>
       </c>
       <c r="I282" t="n">
-        <v>1.3789</v>
+        <v>1.4045</v>
       </c>
       <c r="J282" t="n">
-        <v>26.1991</v>
+        <v>26.6855</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.6</v>
       </c>
       <c r="I283" t="n">
-        <v>1.1843</v>
+        <v>1.2042</v>
       </c>
       <c r="J283" t="n">
-        <v>22.5017</v>
+        <v>22.8798</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.56</v>
       </c>
       <c r="I284" t="n">
-        <v>1.135</v>
+        <v>1.1545</v>
       </c>
       <c r="J284" t="n">
-        <v>21.565</v>
+        <v>21.9355</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.42</v>
       </c>
       <c r="I285" t="n">
-        <v>0.9371</v>
+        <v>0.9384</v>
       </c>
       <c r="J285" t="n">
-        <v>17.8049</v>
+        <v>17.8296</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>1.36</v>
       </c>
       <c r="I286" t="n">
-        <v>0.8256</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="J286" t="n">
-        <v>15.6864</v>
+        <v>15.523</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>0.85</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.1582</v>
+        <v>-0.1411</v>
       </c>
       <c r="J287" t="n">
-        <v>-3.0058</v>
+        <v>-2.6809</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.65</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.3565</v>
+        <v>-0.3454</v>
       </c>
       <c r="J288" t="n">
-        <v>-6.7735</v>
+        <v>-6.5626</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.64</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.3649</v>
+        <v>-0.354</v>
       </c>
       <c r="J289" t="n">
-        <v>-6.9331</v>
+        <v>-6.726</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.64</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3649</v>
+        <v>-0.354</v>
       </c>
       <c r="J290" t="n">
-        <v>-6.9331</v>
+        <v>-6.726</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.48</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.5052</v>
+        <v>-0.5039</v>
       </c>
       <c r="J291" t="n">
-        <v>-9.598800000000001</v>
+        <v>-9.5741</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.81</v>
       </c>
       <c r="I292" t="n">
-        <v>1.4753</v>
+        <v>1.5054</v>
       </c>
       <c r="J292" t="n">
-        <v>32.4566</v>
+        <v>33.1188</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.42</v>
       </c>
       <c r="I293" t="n">
-        <v>0.9581</v>
+        <v>0.9528</v>
       </c>
       <c r="J293" t="n">
-        <v>21.0782</v>
+        <v>20.9616</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.22</v>
       </c>
       <c r="I294" t="n">
-        <v>0.5702</v>
+        <v>0.5424</v>
       </c>
       <c r="J294" t="n">
-        <v>12.5444</v>
+        <v>11.9328</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.21</v>
       </c>
       <c r="I295" t="n">
-        <v>0.5485</v>
+        <v>0.52</v>
       </c>
       <c r="J295" t="n">
-        <v>12.067</v>
+        <v>11.44</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.04</v>
       </c>
       <c r="I296" t="n">
-        <v>0.1146</v>
+        <v>0.0902</v>
       </c>
       <c r="J296" t="n">
-        <v>2.5212</v>
+        <v>1.9844</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>0.99</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.0115</v>
+        <v>-0.0072</v>
       </c>
       <c r="J297" t="n">
-        <v>-0.253</v>
+        <v>-0.1584</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.98</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.0296</v>
+        <v>-0.0224</v>
       </c>
       <c r="J298" t="n">
-        <v>-0.6512</v>
+        <v>-0.4928</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.0876</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="J299" t="n">
-        <v>-1.9272</v>
+        <v>-1.6368</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.86</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.1792</v>
+        <v>-0.1611</v>
       </c>
       <c r="J300" t="n">
-        <v>-3.9424</v>
+        <v>-3.5442</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.51</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.5024999999999999</v>
+        <v>-0.5026</v>
       </c>
       <c r="J301" t="n">
-        <v>-11.055</v>
+        <v>-11.0572</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.68</v>
       </c>
       <c r="I302" t="n">
-        <v>1.2977</v>
+        <v>1.3177</v>
       </c>
       <c r="J302" t="n">
-        <v>27.2517</v>
+        <v>27.6717</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.63</v>
       </c>
       <c r="I303" t="n">
-        <v>1.235</v>
+        <v>1.2529</v>
       </c>
       <c r="J303" t="n">
-        <v>25.935</v>
+        <v>26.3109</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.34</v>
       </c>
       <c r="I304" t="n">
-        <v>0.8022</v>
+        <v>0.7886</v>
       </c>
       <c r="J304" t="n">
-        <v>16.8462</v>
+        <v>16.5606</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.32</v>
       </c>
       <c r="I305" t="n">
-        <v>0.7633</v>
+        <v>0.7473</v>
       </c>
       <c r="J305" t="n">
-        <v>16.0293</v>
+        <v>15.6933</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>1.16</v>
       </c>
       <c r="I306" t="n">
-        <v>0.4226</v>
+        <v>0.3913</v>
       </c>
       <c r="J306" t="n">
-        <v>8.874599999999999</v>
+        <v>8.2173</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.04</v>
       </c>
       <c r="I307" t="n">
-        <v>0.2143</v>
+        <v>0.1886</v>
       </c>
       <c r="J307" t="n">
-        <v>4.5003</v>
+        <v>3.9606</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.79</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.2329</v>
+        <v>-0.2181</v>
       </c>
       <c r="J308" t="n">
-        <v>-4.8909</v>
+        <v>-4.5801</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.59</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.4149</v>
+        <v>-0.405</v>
       </c>
       <c r="J309" t="n">
-        <v>-8.712899999999999</v>
+        <v>-8.505000000000001</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.55</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.4503</v>
+        <v>-0.4433</v>
       </c>
       <c r="J310" t="n">
-        <v>-9.456300000000001</v>
+        <v>-9.3093</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.54</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4591</v>
+        <v>-0.453</v>
       </c>
       <c r="J311" t="n">
-        <v>-9.6411</v>
+        <v>-9.513</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.26</v>
       </c>
       <c r="I312" t="n">
-        <v>0.6905</v>
+        <v>0.657</v>
       </c>
       <c r="J312" t="n">
-        <v>20.715</v>
+        <v>19.71</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.16</v>
       </c>
       <c r="I313" t="n">
-        <v>0.4684</v>
+        <v>0.4289</v>
       </c>
       <c r="J313" t="n">
-        <v>14.052</v>
+        <v>12.867</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.12</v>
       </c>
       <c r="I314" t="n">
-        <v>0.3731</v>
+        <v>0.3348</v>
       </c>
       <c r="J314" t="n">
-        <v>11.193</v>
+        <v>10.044</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.03</v>
       </c>
       <c r="I315" t="n">
-        <v>0.1205</v>
+        <v>0.0983</v>
       </c>
       <c r="J315" t="n">
-        <v>3.615</v>
+        <v>2.949</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.96</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.1882</v>
+        <v>-0.1537</v>
       </c>
       <c r="J316" t="n">
-        <v>-5.646</v>
+        <v>-4.611</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.16</v>
       </c>
       <c r="I317" t="n">
-        <v>0.37</v>
+        <v>0.315</v>
       </c>
       <c r="J317" t="n">
-        <v>11.1</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.06</v>
       </c>
       <c r="I318" t="n">
-        <v>0.1744</v>
+        <v>0.1362</v>
       </c>
       <c r="J318" t="n">
-        <v>5.232</v>
+        <v>4.086</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.97</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.0567</v>
+        <v>-0.0448</v>
       </c>
       <c r="J319" t="n">
-        <v>-1.701</v>
+        <v>-1.344</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.87</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.1779</v>
+        <v>-0.1576</v>
       </c>
       <c r="J320" t="n">
-        <v>-5.337</v>
+        <v>-4.728</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.2401</v>
+        <v>-0.2199</v>
       </c>
       <c r="J321" t="n">
-        <v>-7.203</v>
+        <v>-6.597</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.15</v>
       </c>
       <c r="I322" t="n">
-        <v>0.2775</v>
+        <v>0.2639</v>
       </c>
       <c r="J322" t="n">
-        <v>7.4925</v>
+        <v>7.1253</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.09</v>
       </c>
       <c r="I323" t="n">
-        <v>0.1876</v>
+        <v>0.1704</v>
       </c>
       <c r="J323" t="n">
-        <v>5.0652</v>
+        <v>4.6008</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.06</v>
       </c>
       <c r="I324" t="n">
-        <v>0.138</v>
+        <v>0.121</v>
       </c>
       <c r="J324" t="n">
-        <v>3.726</v>
+        <v>3.267</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.82</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.2291</v>
+        <v>-0.2087</v>
       </c>
       <c r="J325" t="n">
-        <v>-6.1857</v>
+        <v>-5.6349</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.7</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.3444</v>
+        <v>-0.3291</v>
       </c>
       <c r="J326" t="n">
-        <v>-9.2988</v>
+        <v>-8.8857</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.38</v>
       </c>
       <c r="I327" t="n">
-        <v>0.5132</v>
+        <v>0.4443</v>
       </c>
       <c r="J327" t="n">
-        <v>13.8564</v>
+        <v>11.9961</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.2</v>
       </c>
       <c r="I328" t="n">
-        <v>0.3064</v>
+        <v>0.251</v>
       </c>
       <c r="J328" t="n">
-        <v>8.2728</v>
+        <v>6.777</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>1.06</v>
       </c>
       <c r="I329" t="n">
-        <v>0.1176</v>
+        <v>0.0887</v>
       </c>
       <c r="J329" t="n">
-        <v>3.1752</v>
+        <v>2.3949</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.97</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.0668</v>
+        <v>-0.0527</v>
       </c>
       <c r="J330" t="n">
-        <v>-1.8036</v>
+        <v>-1.4229</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.95</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.0951</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="J331" t="n">
-        <v>-2.5677</v>
+        <v>-2.1114</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.42</v>
       </c>
       <c r="I332" t="n">
-        <v>0.9842</v>
+        <v>0.9785</v>
       </c>
       <c r="J332" t="n">
-        <v>26.5734</v>
+        <v>26.4195</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.39</v>
       </c>
       <c r="I333" t="n">
-        <v>0.9303</v>
+        <v>0.9165</v>
       </c>
       <c r="J333" t="n">
-        <v>25.1181</v>
+        <v>24.7455</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.23</v>
       </c>
       <c r="I334" t="n">
-        <v>0.6086</v>
+        <v>0.5757</v>
       </c>
       <c r="J334" t="n">
-        <v>16.4322</v>
+        <v>15.5439</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.14</v>
       </c>
       <c r="I335" t="n">
-        <v>0.4099</v>
+        <v>0.3755</v>
       </c>
       <c r="J335" t="n">
-        <v>11.0673</v>
+        <v>10.1385</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.82</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.579</v>
+        <v>-0.5426</v>
       </c>
       <c r="J336" t="n">
-        <v>-15.633</v>
+        <v>-14.6502</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.21</v>
       </c>
       <c r="I337" t="n">
-        <v>0.4649</v>
+        <v>0.4075</v>
       </c>
       <c r="J337" t="n">
-        <v>12.5523</v>
+        <v>11.0025</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.12</v>
       </c>
       <c r="I338" t="n">
-        <v>0.3025</v>
+        <v>0.2517</v>
       </c>
       <c r="J338" t="n">
-        <v>8.1675</v>
+        <v>6.7959</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.97</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.0552</v>
+        <v>-0.0441</v>
       </c>
       <c r="J339" t="n">
-        <v>-1.4904</v>
+        <v>-1.1907</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.83</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.2172</v>
+        <v>-0.1969</v>
       </c>
       <c r="J340" t="n">
-        <v>-5.8644</v>
+        <v>-5.3163</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.6</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.4326</v>
+        <v>-0.4252</v>
       </c>
       <c r="J341" t="n">
-        <v>-11.6802</v>
+        <v>-11.4804</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.27</v>
       </c>
       <c r="I342" t="n">
-        <v>0.7073</v>
+        <v>0.6751</v>
       </c>
       <c r="J342" t="n">
-        <v>19.8044</v>
+        <v>18.9028</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.24</v>
       </c>
       <c r="I343" t="n">
-        <v>0.6435</v>
+        <v>0.6083</v>
       </c>
       <c r="J343" t="n">
-        <v>18.018</v>
+        <v>17.0324</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.09</v>
       </c>
       <c r="I344" t="n">
-        <v>0.2957</v>
+        <v>0.261</v>
       </c>
       <c r="J344" t="n">
-        <v>8.2796</v>
+        <v>7.308</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>1.07</v>
       </c>
       <c r="I345" t="n">
-        <v>0.2412</v>
+        <v>0.2093</v>
       </c>
       <c r="J345" t="n">
-        <v>6.7536</v>
+        <v>5.8604</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.95</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.2235</v>
+        <v>-0.1864</v>
       </c>
       <c r="J346" t="n">
-        <v>-6.258</v>
+        <v>-5.2192</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.2</v>
       </c>
       <c r="I347" t="n">
-        <v>0.446</v>
+        <v>0.3887</v>
       </c>
       <c r="J347" t="n">
-        <v>12.488</v>
+        <v>10.8836</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>1.06</v>
       </c>
       <c r="I348" t="n">
-        <v>0.1785</v>
+        <v>0.1396</v>
       </c>
       <c r="J348" t="n">
-        <v>4.998</v>
+        <v>3.9088</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.0956</v>
+        <v>-0.0799</v>
       </c>
       <c r="J349" t="n">
-        <v>-2.6768</v>
+        <v>-2.2372</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.82</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.2279</v>
+        <v>-0.2076</v>
       </c>
       <c r="J350" t="n">
-        <v>-6.3812</v>
+        <v>-5.8128</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.74</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.306</v>
+        <v>-0.2882</v>
       </c>
       <c r="J351" t="n">
-        <v>-8.568</v>
+        <v>-8.069599999999999</v>
       </c>
     </row>
     <row r="352">
@@ -16429,10 +16429,10 @@
         <v>1.79</v>
       </c>
       <c r="I352" t="n">
-        <v>1.442</v>
+        <v>1.4695</v>
       </c>
       <c r="J352" t="n">
-        <v>31.724</v>
+        <v>32.329</v>
       </c>
     </row>
     <row r="353">
@@ -16469,10 +16469,10 @@
         <v>1.57</v>
       </c>
       <c r="I353" t="n">
-        <v>1.1652</v>
+        <v>1.1803</v>
       </c>
       <c r="J353" t="n">
-        <v>25.6344</v>
+        <v>25.9666</v>
       </c>
     </row>
     <row r="354">
@@ -16509,10 +16509,10 @@
         <v>1.26</v>
       </c>
       <c r="I354" t="n">
-        <v>0.6489</v>
+        <v>0.6253</v>
       </c>
       <c r="J354" t="n">
-        <v>14.2758</v>
+        <v>13.7566</v>
       </c>
     </row>
     <row r="355">
@@ -16549,10 +16549,10 @@
         <v>1.25</v>
       </c>
       <c r="I355" t="n">
-        <v>0.6281</v>
+        <v>0.6036</v>
       </c>
       <c r="J355" t="n">
-        <v>13.8182</v>
+        <v>13.2792</v>
       </c>
     </row>
     <row r="356">
@@ -16589,10 +16589,10 @@
         <v>1.03</v>
       </c>
       <c r="I356" t="n">
-        <v>0.0747</v>
+        <v>0.0525</v>
       </c>
       <c r="J356" t="n">
-        <v>1.6434</v>
+        <v>1.155</v>
       </c>
     </row>
     <row r="357">
@@ -16629,10 +16629,10 @@
         <v>1</v>
       </c>
       <c r="I357" t="n">
-        <v>0.06</v>
+        <v>0.0561</v>
       </c>
       <c r="J357" t="n">
-        <v>1.32</v>
+        <v>1.2342</v>
       </c>
     </row>
     <row r="358">
@@ -16669,10 +16669,10 @@
         <v>0.86</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.1667</v>
+        <v>-0.1511</v>
       </c>
       <c r="J358" t="n">
-        <v>-3.6674</v>
+        <v>-3.3242</v>
       </c>
     </row>
     <row r="359">
@@ -16709,10 +16709,10 @@
         <v>0.76</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.2678</v>
+        <v>-0.252</v>
       </c>
       <c r="J359" t="n">
-        <v>-5.8916</v>
+        <v>-5.544</v>
       </c>
     </row>
     <row r="360">
@@ -16749,10 +16749,10 @@
         <v>0.66</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.3581</v>
+        <v>-0.3441</v>
       </c>
       <c r="J360" t="n">
-        <v>-7.8782</v>
+        <v>-7.5702</v>
       </c>
     </row>
     <row r="361">
@@ -16789,10 +16789,10 @@
         <v>0.46</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.5346</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="J361" t="n">
-        <v>-11.7612</v>
+        <v>-11.8316</v>
       </c>
     </row>
   </sheetData>
